--- a/KXHMONTH_August_2026_Forecast.xlsx
+++ b/KXHMONTH_August_2026_Forecast.xlsx
@@ -8,14 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/felipecardozo/Desktop/Stats/Hottest Month/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B2540746-8222-FE4B-8C98-2F738DD433BF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7CC09562-8701-3946-85C7-FB873A03FCF4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="18980" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Aug2026_Live" sheetId="1" r:id="rId1"/>
     <sheet name="ENS_members_raw" sheetId="2" r:id="rId2"/>
-    <sheet name="Fcst_log" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">Aug2026_Live!$48:$48</definedName>
@@ -38,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="261" uniqueCount="260">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="250" uniqueCount="249">
   <si>
     <t>LIVE SUMMARY  (auto-updates as you fill the daily table)</t>
   </si>
@@ -170,9 +169,6 @@
   </si>
   <si>
     <t>sd_f = LINEST std-error of  ERA5_Aug ~ ERA5_Jul + Aug_first-k   ·   σ_NOAA = √((b·sd_f)²+σ_trans²)</t>
-  </si>
-  <si>
-    <t>‘ref (offline)’ = the same regression computed from the same Block-7 rows outside Excel. sd_f uses LINEST and falls back to ref only if LINEST is unavailable — the two must agree.</t>
   </si>
   <si>
     <t>k=31: month fully observed → forecast error is 0 by definition</t>
@@ -304,9 +300,6 @@
     <t>↑ Yellow = you fill.  Cols K–O computed.  Cols P–X = engine/verification helpers (shaded).</t>
   </si>
   <si>
-    <t>BLOCK 3 — MONTH BUILD &amp; PROBABILITY (the engine)</t>
-  </si>
-  <si>
     <t>k  — observed days</t>
   </si>
   <si>
@@ -413,9 +406,6 @@
   </si>
   <si>
     <t>Different dataset &amp; threshold → basis, never arbitrage.</t>
-  </si>
-  <si>
-    <t>BLOCK 4 — MARKET &amp; PROFITABILITY  (executable prices only — never mid)</t>
   </si>
   <si>
     <t>Kalshi YES bid (¢)</t>
@@ -797,44 +787,20 @@
     <t>Member-average of per-member tail probabilities — NOT the tail of the average (Jensen: the threshold tail is convex, so averaging probabilities &gt; probability at the average).</t>
   </si>
   <si>
-    <t>FORECAST-RUN LOG — when a surge ENTERS the model (the lead-time edge)</t>
-  </si>
-  <si>
-    <t>The fundamental leads the market price by ~2–3 days (July 2026: surge entered the 15 Jul 11:40Z run; price spiked 18 Jul).</t>
-  </si>
-  <si>
-    <t>USE: a RISING remaining-days mean here = early BUY-YES signal before the tape moves.  A price spike with NO new high here = FADE signal (liquidity vacuum, not information).</t>
-  </si>
-  <si>
-    <t>Pulled (UTC)</t>
-  </si>
-  <si>
-    <t>Model</t>
-  </si>
-  <si>
-    <t>Run cycle</t>
-  </si>
-  <si>
-    <t>Remaining-days mean anomaly °C</t>
-  </si>
-  <si>
-    <t>Δ vs prior same model</t>
-  </si>
-  <si>
-    <t>Signal</t>
-  </si>
-  <si>
-    <t>Note</t>
-  </si>
-  <si>
     <t>KXHMONTH-26AUG  —  “Will August 2026 be the hottest August ever?”</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BLOCK 3 — MONTH PROBABILITY </t>
+  </si>
+  <si>
+    <t>BLOCK 4 — MARKET &amp; PROFITABILITY</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="11">
+  <numFmts count="10">
     <numFmt numFmtId="164" formatCode="0.000"/>
     <numFmt numFmtId="165" formatCode="\+0.0;\-0.0"/>
     <numFmt numFmtId="166" formatCode="0.0000"/>
@@ -845,7 +811,6 @@
     <numFmt numFmtId="172" formatCode="0.0&quot;¢&quot;"/>
     <numFmt numFmtId="173" formatCode="#,##0.0"/>
     <numFmt numFmtId="174" formatCode="0.0%"/>
-    <numFmt numFmtId="175" formatCode="\+0.000;\-0.000"/>
   </numFmts>
   <fonts count="22" x14ac:knownFonts="1">
     <font>
@@ -1059,7 +1024,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="86">
+  <cellXfs count="83">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="1" fontId="16" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
@@ -1136,9 +1101,6 @@
     <xf numFmtId="1" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="10" fontId="20" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="175" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1158,26 +1120,7 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="17">
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFDDEBF7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FF9C0006"/>
-        <name val="Arial"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="15">
     <dxf>
       <fill>
         <patternFill patternType="solid">
@@ -1634,7 +1577,7 @@
     <col min="4" max="4" width="12" customWidth="1"/>
     <col min="5" max="5" width="69.83203125" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="8.6640625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="138.6640625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="84.33203125" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="8.6640625" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="42.83203125" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="7.83203125" bestFit="1" customWidth="1"/>
@@ -1649,42 +1592,42 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:15" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="84" t="s">
-        <v>259</v>
-      </c>
-      <c r="B1" s="84"/>
-      <c r="C1" s="84"/>
-      <c r="D1" s="84"/>
-      <c r="E1" s="84"/>
-      <c r="F1" s="84"/>
-      <c r="G1" s="84"/>
-      <c r="H1" s="84"/>
-      <c r="I1" s="84"/>
-      <c r="J1" s="84"/>
-      <c r="K1" s="84"/>
-      <c r="L1" s="84"/>
-      <c r="M1" s="84"/>
-      <c r="N1" s="84"/>
-      <c r="O1" s="84"/>
+      <c r="A1" s="81" t="s">
+        <v>246</v>
+      </c>
+      <c r="B1" s="81"/>
+      <c r="C1" s="81"/>
+      <c r="D1" s="81"/>
+      <c r="E1" s="81"/>
+      <c r="F1" s="81"/>
+      <c r="G1" s="81"/>
+      <c r="H1" s="81"/>
+      <c r="I1" s="81"/>
+      <c r="J1" s="81"/>
+      <c r="K1" s="81"/>
+      <c r="L1" s="81"/>
+      <c r="M1" s="81"/>
+      <c r="N1" s="81"/>
+      <c r="O1" s="81"/>
     </row>
     <row r="2" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A2" s="82" t="s">
+      <c r="A2" s="79" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="82"/>
-      <c r="C2" s="82"/>
-      <c r="D2" s="82"/>
-      <c r="E2" s="82"/>
-      <c r="F2" s="82"/>
-      <c r="G2" s="82"/>
-      <c r="H2" s="82"/>
-      <c r="I2" s="82"/>
-      <c r="J2" s="82"/>
-      <c r="K2" s="82"/>
-      <c r="L2" s="82"/>
-      <c r="M2" s="82"/>
-      <c r="N2" s="82"/>
-      <c r="O2" s="82"/>
+      <c r="B2" s="79"/>
+      <c r="C2" s="79"/>
+      <c r="D2" s="79"/>
+      <c r="E2" s="79"/>
+      <c r="F2" s="79"/>
+      <c r="G2" s="79"/>
+      <c r="H2" s="79"/>
+      <c r="I2" s="79"/>
+      <c r="J2" s="79"/>
+      <c r="K2" s="79"/>
+      <c r="L2" s="79"/>
+      <c r="M2" s="79"/>
+      <c r="N2" s="79"/>
+      <c r="O2" s="79"/>
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
@@ -1740,147 +1683,147 @@
         <v/>
       </c>
       <c r="L4" s="3"/>
-      <c r="M4" s="83" t="str">
+      <c r="M4" s="80" t="str">
         <f>$C$134</f>
         <v>— fill daily table + ENS members —</v>
       </c>
-      <c r="N4" s="83"/>
-      <c r="O4" s="83"/>
+      <c r="N4" s="80"/>
+      <c r="O4" s="80"/>
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A5" s="78" t="s">
+      <c r="A5" s="75" t="s">
         <v>8</v>
       </c>
-      <c r="B5" s="78"/>
-      <c r="C5" s="78"/>
-      <c r="D5" s="78"/>
-      <c r="E5" s="78"/>
-      <c r="F5" s="78"/>
-      <c r="G5" s="78"/>
-      <c r="H5" s="78"/>
-      <c r="I5" s="78"/>
-      <c r="J5" s="78"/>
-      <c r="K5" s="78"/>
-      <c r="L5" s="78"/>
-      <c r="M5" s="78"/>
-      <c r="N5" s="78"/>
-      <c r="O5" s="78"/>
+      <c r="B5" s="75"/>
+      <c r="C5" s="75"/>
+      <c r="D5" s="75"/>
+      <c r="E5" s="75"/>
+      <c r="F5" s="75"/>
+      <c r="G5" s="75"/>
+      <c r="H5" s="75"/>
+      <c r="I5" s="75"/>
+      <c r="J5" s="75"/>
+      <c r="K5" s="75"/>
+      <c r="L5" s="75"/>
+      <c r="M5" s="75"/>
+      <c r="N5" s="75"/>
+      <c r="O5" s="75"/>
     </row>
     <row r="6" spans="1:15" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="80" t="s">
+      <c r="A6" s="77" t="s">
         <v>9</v>
       </c>
-      <c r="B6" s="80"/>
-      <c r="C6" s="80"/>
-      <c r="D6" s="80"/>
-      <c r="E6" s="80"/>
-      <c r="F6" s="80"/>
-      <c r="G6" s="80"/>
-      <c r="H6" s="80"/>
-      <c r="I6" s="80"/>
-      <c r="J6" s="80"/>
-      <c r="K6" s="80"/>
-      <c r="L6" s="80"/>
-      <c r="M6" s="80"/>
-      <c r="N6" s="80"/>
-      <c r="O6" s="80"/>
+      <c r="B6" s="77"/>
+      <c r="C6" s="77"/>
+      <c r="D6" s="77"/>
+      <c r="E6" s="77"/>
+      <c r="F6" s="77"/>
+      <c r="G6" s="77"/>
+      <c r="H6" s="77"/>
+      <c r="I6" s="77"/>
+      <c r="J6" s="77"/>
+      <c r="K6" s="77"/>
+      <c r="L6" s="77"/>
+      <c r="M6" s="77"/>
+      <c r="N6" s="77"/>
+      <c r="O6" s="77"/>
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A7" s="7"/>
-      <c r="C7" s="79"/>
-      <c r="D7" s="79"/>
-      <c r="E7" s="79"/>
-      <c r="F7" s="79"/>
-      <c r="G7" s="79"/>
-      <c r="H7" s="79"/>
-      <c r="I7" s="79"/>
-      <c r="J7" s="79"/>
+      <c r="C7" s="76"/>
+      <c r="D7" s="76"/>
+      <c r="E7" s="76"/>
+      <c r="F7" s="76"/>
+      <c r="G7" s="76"/>
+      <c r="H7" s="76"/>
+      <c r="I7" s="76"/>
+      <c r="J7" s="76"/>
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A8" s="7"/>
-      <c r="C8" s="79"/>
-      <c r="D8" s="79"/>
-      <c r="E8" s="79"/>
-      <c r="F8" s="79"/>
-      <c r="G8" s="79"/>
-      <c r="H8" s="79"/>
-      <c r="I8" s="79"/>
-      <c r="J8" s="79"/>
+      <c r="C8" s="76"/>
+      <c r="D8" s="76"/>
+      <c r="E8" s="76"/>
+      <c r="F8" s="76"/>
+      <c r="G8" s="76"/>
+      <c r="H8" s="76"/>
+      <c r="I8" s="76"/>
+      <c r="J8" s="76"/>
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A9" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="C9" s="79" t="s">
+      <c r="C9" s="76" t="s">
         <v>11</v>
       </c>
-      <c r="D9" s="79"/>
-      <c r="E9" s="79"/>
-      <c r="F9" s="79"/>
-      <c r="G9" s="79"/>
-      <c r="H9" s="79"/>
-      <c r="I9" s="79"/>
-      <c r="J9" s="79"/>
+      <c r="D9" s="76"/>
+      <c r="E9" s="76"/>
+      <c r="F9" s="76"/>
+      <c r="G9" s="76"/>
+      <c r="H9" s="76"/>
+      <c r="I9" s="76"/>
+      <c r="J9" s="76"/>
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A10" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="C10" s="79" t="s">
+      <c r="C10" s="76" t="s">
         <v>13</v>
       </c>
-      <c r="D10" s="79"/>
-      <c r="E10" s="79"/>
-      <c r="F10" s="79"/>
-      <c r="G10" s="79"/>
-      <c r="H10" s="79"/>
-      <c r="I10" s="79"/>
-      <c r="J10" s="79"/>
+      <c r="D10" s="76"/>
+      <c r="E10" s="76"/>
+      <c r="F10" s="76"/>
+      <c r="G10" s="76"/>
+      <c r="H10" s="76"/>
+      <c r="I10" s="76"/>
+      <c r="J10" s="76"/>
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A11" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="C11" s="79" t="s">
+      <c r="C11" s="76" t="s">
         <v>15</v>
       </c>
-      <c r="D11" s="79"/>
-      <c r="E11" s="79"/>
-      <c r="F11" s="79"/>
-      <c r="G11" s="79"/>
-      <c r="H11" s="79"/>
-      <c r="I11" s="79"/>
-      <c r="J11" s="79"/>
+      <c r="D11" s="76"/>
+      <c r="E11" s="76"/>
+      <c r="F11" s="76"/>
+      <c r="G11" s="76"/>
+      <c r="H11" s="76"/>
+      <c r="I11" s="76"/>
+      <c r="J11" s="76"/>
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A12" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="C12" s="79" t="s">
+      <c r="C12" s="76" t="s">
         <v>17</v>
       </c>
-      <c r="D12" s="79"/>
-      <c r="E12" s="79"/>
-      <c r="F12" s="79"/>
-      <c r="G12" s="79"/>
-      <c r="H12" s="79"/>
-      <c r="I12" s="79"/>
-      <c r="J12" s="79"/>
+      <c r="D12" s="76"/>
+      <c r="E12" s="76"/>
+      <c r="F12" s="76"/>
+      <c r="G12" s="76"/>
+      <c r="H12" s="76"/>
+      <c r="I12" s="76"/>
+      <c r="J12" s="76"/>
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A13" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="C13" s="81">
+      <c r="C13" s="78">
         <v>31</v>
       </c>
-      <c r="D13" s="81"/>
-      <c r="E13" s="81"/>
-      <c r="F13" s="81"/>
-      <c r="G13" s="81"/>
-      <c r="H13" s="81"/>
-      <c r="I13" s="81"/>
-      <c r="J13" s="81"/>
+      <c r="D13" s="78"/>
+      <c r="E13" s="78"/>
+      <c r="F13" s="78"/>
+      <c r="G13" s="78"/>
+      <c r="H13" s="78"/>
+      <c r="I13" s="78"/>
+      <c r="J13" s="78"/>
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A15" s="9" t="s">
@@ -1957,7 +1900,7 @@
       </c>
       <c r="C22" s="16">
         <f>INTERCEPT($C$163:$C$198,$B$163:$B$198)</f>
-        <v>0.58921187883662351</v>
+        <v>0.61648123427306367</v>
       </c>
       <c r="E22" s="12" t="s">
         <v>30</v>
@@ -1969,7 +1912,7 @@
       </c>
       <c r="C23" s="16">
         <f>SLOPE($C$163:$C$198,$B$163:$B$198)</f>
-        <v>0.96190197594864346</v>
+        <v>0.89639103934609243</v>
       </c>
       <c r="E23" s="12" t="s">
         <v>32</v>
@@ -1981,7 +1924,7 @@
       </c>
       <c r="C24" s="16">
         <f>STEYX($C$163:$C$198,$B$163:$B$198)</f>
-        <v>3.5675600287562739E-2</v>
+        <v>2.9567023118146327E-2</v>
       </c>
       <c r="E24" s="12" t="s">
         <v>34</v>
@@ -1993,7 +1936,7 @@
       </c>
       <c r="C25" s="17">
         <f>COUNT($B$163:$B$198)</f>
-        <v>36</v>
+        <v>17</v>
       </c>
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.2">
@@ -2002,7 +1945,7 @@
       </c>
       <c r="C26" s="16">
         <f>($C$17-$C$22)/$C$23</f>
-        <v>0.69215797223699982</v>
+        <v>0.71232167402379298</v>
       </c>
       <c r="E26" s="12" t="s">
         <v>37</v>
@@ -2049,7 +1992,7 @@
       </c>
       <c r="E30" s="22">
         <f>IFERROR(SQRT(($C$23*$C$30)^2+$C$24^2),"")</f>
-        <v>6.5332722491617548E-2</v>
+        <v>5.8954925085607915E-2</v>
       </c>
       <c r="G30" s="12" t="s">
         <v>43</v>
@@ -2068,11 +2011,9 @@
       </c>
       <c r="E31" s="22">
         <f>IFERROR(SQRT(($C$23*$C$31)^2+$C$24^2),"")</f>
-        <v>6.3093543618377726E-2</v>
-      </c>
-      <c r="G31" s="12" t="s">
-        <v>44</v>
-      </c>
+        <v>5.6797448364808739E-2</v>
+      </c>
+      <c r="G31" s="12"/>
     </row>
     <row r="32" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A32" s="19">
@@ -2087,7 +2028,7 @@
       </c>
       <c r="E32" s="22">
         <f>IFERROR(SQRT(($C$23*$C$32)^2+$C$24^2),"")</f>
-        <v>5.4767664864641921E-2</v>
+        <v>4.8721291310653496E-2</v>
       </c>
     </row>
     <row r="33" spans="1:24" x14ac:dyDescent="0.2">
@@ -2103,7 +2044,7 @@
       </c>
       <c r="E33" s="22">
         <f>IFERROR(SQRT(($C$23*$C$33)^2+$C$24^2),"")</f>
-        <v>5.3537553063693191E-2</v>
+        <v>4.7519110147455822E-2</v>
       </c>
     </row>
     <row r="34" spans="1:24" x14ac:dyDescent="0.2">
@@ -2119,7 +2060,7 @@
       </c>
       <c r="E34" s="22">
         <f>IFERROR(SQRT(($C$23*$C$34)^2+$C$24^2),"")</f>
-        <v>5.1560587980342333E-2</v>
+        <v>4.5581005640184497E-2</v>
       </c>
     </row>
     <row r="35" spans="1:24" x14ac:dyDescent="0.2">
@@ -2135,7 +2076,7 @@
       </c>
       <c r="E35" s="22">
         <f>IFERROR(SQRT(($C$23*$C$35)^2+$C$24^2),"")</f>
-        <v>4.1578255528578259E-2</v>
+        <v>3.5640063451231066E-2</v>
       </c>
     </row>
     <row r="36" spans="1:24" x14ac:dyDescent="0.2">
@@ -2150,15 +2091,15 @@
       </c>
       <c r="E36" s="22">
         <f>IFERROR(SQRT(($C$23*$C$36)^2+$C$24^2),"")</f>
-        <v>3.5675600287562739E-2</v>
+        <v>2.9567023118146327E-2</v>
       </c>
       <c r="G36" s="12" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="38" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A38" s="9" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B38" s="10"/>
       <c r="C38" s="10"/>
@@ -2172,40 +2113,40 @@
     </row>
     <row r="39" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A39" s="8" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C39" s="24">
         <v>1</v>
       </c>
       <c r="E39" s="12" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="40" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A40" s="8" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C40" s="25">
         <v>1.3</v>
       </c>
       <c r="E40" s="12" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="41" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A41" s="8" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C41" s="14">
         <v>1.2949999999999999</v>
       </c>
       <c r="E41" s="12" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="42" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A42" s="8" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C42" s="26">
         <v>0.58030000000000004</v>
@@ -2217,126 +2158,126 @@
         <v>5.4199999999999998E-2</v>
       </c>
       <c r="I42" s="12" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="43" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A43" s="8" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C43" s="25">
         <v>0.6</v>
       </c>
       <c r="E43" s="12" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="44" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A44" s="8" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C44" s="27">
         <f>AVERAGE($B$194:$B$198)</f>
         <v>0.50449999999999995</v>
       </c>
       <c r="E44" s="12" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="46" spans="1:24" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A46" s="77" t="s">
         <v>58</v>
       </c>
-    </row>
-    <row r="46" spans="1:24" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A46" s="80" t="s">
-        <v>59</v>
-      </c>
-      <c r="B46" s="80"/>
-      <c r="C46" s="80"/>
-      <c r="D46" s="80"/>
-      <c r="E46" s="80"/>
-      <c r="F46" s="80"/>
-      <c r="G46" s="80"/>
-      <c r="H46" s="80"/>
-      <c r="I46" s="80"/>
-      <c r="J46" s="80"/>
-      <c r="K46" s="80"/>
-      <c r="L46" s="80"/>
-      <c r="M46" s="80"/>
-      <c r="N46" s="80"/>
-      <c r="O46" s="80"/>
+      <c r="B46" s="77"/>
+      <c r="C46" s="77"/>
+      <c r="D46" s="77"/>
+      <c r="E46" s="77"/>
+      <c r="F46" s="77"/>
+      <c r="G46" s="77"/>
+      <c r="H46" s="77"/>
+      <c r="I46" s="77"/>
+      <c r="J46" s="77"/>
+      <c r="K46" s="77"/>
+      <c r="L46" s="77"/>
+      <c r="M46" s="77"/>
+      <c r="N46" s="77"/>
+      <c r="O46" s="77"/>
     </row>
     <row r="47" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A47" s="28"/>
     </row>
     <row r="48" spans="1:24" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A48" s="29" t="s">
+        <v>59</v>
+      </c>
+      <c r="B48" s="29" t="s">
         <v>60</v>
       </c>
-      <c r="B48" s="29" t="s">
+      <c r="C48" s="29" t="s">
         <v>61</v>
       </c>
-      <c r="C48" s="29" t="s">
+      <c r="D48" s="29" t="s">
         <v>62</v>
       </c>
-      <c r="D48" s="29" t="s">
+      <c r="E48" s="29" t="s">
         <v>63</v>
       </c>
-      <c r="E48" s="29" t="s">
+      <c r="F48" s="29" t="s">
         <v>64</v>
       </c>
-      <c r="F48" s="29" t="s">
+      <c r="G48" s="29" t="s">
         <v>65</v>
       </c>
-      <c r="G48" s="29" t="s">
+      <c r="H48" s="29" t="s">
         <v>66</v>
       </c>
-      <c r="H48" s="29" t="s">
+      <c r="I48" s="29" t="s">
         <v>67</v>
       </c>
-      <c r="I48" s="29" t="s">
+      <c r="J48" s="29" t="s">
         <v>68</v>
       </c>
-      <c r="J48" s="29" t="s">
+      <c r="K48" s="29" t="s">
         <v>69</v>
       </c>
-      <c r="K48" s="29" t="s">
+      <c r="L48" s="29" t="s">
         <v>70</v>
       </c>
-      <c r="L48" s="29" t="s">
+      <c r="M48" s="29" t="s">
         <v>71</v>
       </c>
-      <c r="M48" s="29" t="s">
+      <c r="N48" s="29" t="s">
         <v>72</v>
       </c>
-      <c r="N48" s="29" t="s">
+      <c r="O48" s="29" t="s">
         <v>73</v>
       </c>
-      <c r="O48" s="29" t="s">
+      <c r="P48" s="29" t="s">
         <v>74</v>
       </c>
-      <c r="P48" s="29" t="s">
+      <c r="Q48" s="29" t="s">
         <v>75</v>
       </c>
-      <c r="Q48" s="29" t="s">
+      <c r="R48" s="29" t="s">
         <v>76</v>
       </c>
-      <c r="R48" s="29" t="s">
+      <c r="S48" s="29" t="s">
         <v>77</v>
       </c>
-      <c r="S48" s="29" t="s">
+      <c r="T48" s="29" t="s">
         <v>78</v>
       </c>
-      <c r="T48" s="29" t="s">
+      <c r="U48" s="29" t="s">
         <v>79</v>
       </c>
-      <c r="U48" s="29" t="s">
+      <c r="V48" s="29" t="s">
         <v>80</v>
       </c>
-      <c r="V48" s="29" t="s">
+      <c r="W48" s="29" t="s">
         <v>81</v>
       </c>
-      <c r="W48" s="29" t="s">
+      <c r="X48" s="29" t="s">
         <v>82</v>
-      </c>
-      <c r="X48" s="29" t="s">
-        <v>83</v>
       </c>
     </row>
     <row r="49" spans="1:24" x14ac:dyDescent="0.2">
@@ -4511,880 +4452,880 @@
     </row>
     <row r="80" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A80" s="12" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="82" spans="1:15" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A82" s="80" t="s">
-        <v>85</v>
-      </c>
-      <c r="B82" s="80"/>
-      <c r="C82" s="80"/>
-      <c r="D82" s="80"/>
-      <c r="E82" s="80"/>
-      <c r="F82" s="80"/>
-      <c r="G82" s="80"/>
-      <c r="H82" s="80"/>
-      <c r="I82" s="80"/>
-      <c r="J82" s="80"/>
-      <c r="K82" s="80"/>
-      <c r="L82" s="80"/>
-      <c r="M82" s="80"/>
-      <c r="N82" s="80"/>
-      <c r="O82" s="80"/>
+      <c r="A82" s="77" t="s">
+        <v>247</v>
+      </c>
+      <c r="B82" s="77"/>
+      <c r="C82" s="77"/>
+      <c r="D82" s="77"/>
+      <c r="E82" s="77"/>
+      <c r="F82" s="77"/>
+      <c r="G82" s="77"/>
+      <c r="H82" s="77"/>
+      <c r="I82" s="77"/>
+      <c r="J82" s="77"/>
+      <c r="K82" s="77"/>
+      <c r="L82" s="77"/>
+      <c r="M82" s="77"/>
+      <c r="N82" s="77"/>
+      <c r="O82" s="77"/>
     </row>
     <row r="83" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A83" s="7" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="C83" s="36">
         <f>COUNT($B$49:$B$79)</f>
         <v>0</v>
       </c>
-      <c r="E83" s="75" t="s">
-        <v>87</v>
-      </c>
-      <c r="F83" s="75"/>
-      <c r="G83" s="75"/>
-      <c r="H83" s="75"/>
-      <c r="I83" s="75"/>
-      <c r="J83" s="75"/>
-      <c r="K83" s="75"/>
-      <c r="L83" s="75"/>
-      <c r="M83" s="75"/>
-      <c r="N83" s="75"/>
-      <c r="O83" s="75"/>
+      <c r="E83" s="72" t="s">
+        <v>85</v>
+      </c>
+      <c r="F83" s="72"/>
+      <c r="G83" s="72"/>
+      <c r="H83" s="72"/>
+      <c r="I83" s="72"/>
+      <c r="J83" s="72"/>
+      <c r="K83" s="72"/>
+      <c r="L83" s="72"/>
+      <c r="M83" s="72"/>
+      <c r="N83" s="72"/>
+      <c r="O83" s="72"/>
     </row>
     <row r="84" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A84" s="8" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="C84" s="37">
         <f>SUM($B$49:$B$79)</f>
         <v>0</v>
       </c>
-      <c r="E84" s="75" t="s">
-        <v>89</v>
-      </c>
-      <c r="F84" s="75"/>
-      <c r="G84" s="75"/>
-      <c r="H84" s="75"/>
-      <c r="I84" s="75"/>
-      <c r="J84" s="75"/>
-      <c r="K84" s="75"/>
-      <c r="L84" s="75"/>
-      <c r="M84" s="75"/>
-      <c r="N84" s="75"/>
-      <c r="O84" s="75"/>
+      <c r="E84" s="72" t="s">
+        <v>87</v>
+      </c>
+      <c r="F84" s="72"/>
+      <c r="G84" s="72"/>
+      <c r="H84" s="72"/>
+      <c r="I84" s="72"/>
+      <c r="J84" s="72"/>
+      <c r="K84" s="72"/>
+      <c r="L84" s="72"/>
+      <c r="M84" s="72"/>
+      <c r="N84" s="72"/>
+      <c r="O84" s="72"/>
     </row>
     <row r="85" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A85" s="8" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="C85" s="37" t="str">
         <f>IF($C$83=0,"",$C$84/$C$83)</f>
         <v/>
       </c>
-      <c r="E85" s="75" t="s">
-        <v>91</v>
-      </c>
-      <c r="F85" s="75"/>
-      <c r="G85" s="75"/>
-      <c r="H85" s="75"/>
-      <c r="I85" s="75"/>
-      <c r="J85" s="75"/>
-      <c r="K85" s="75"/>
-      <c r="L85" s="75"/>
-      <c r="M85" s="75"/>
-      <c r="N85" s="75"/>
-      <c r="O85" s="75"/>
+      <c r="E85" s="72" t="s">
+        <v>89</v>
+      </c>
+      <c r="F85" s="72"/>
+      <c r="G85" s="72"/>
+      <c r="H85" s="72"/>
+      <c r="I85" s="72"/>
+      <c r="J85" s="72"/>
+      <c r="K85" s="72"/>
+      <c r="L85" s="72"/>
+      <c r="M85" s="72"/>
+      <c r="N85" s="72"/>
+      <c r="O85" s="72"/>
     </row>
     <row r="86" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A86" s="8" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="C86" s="38">
         <f>$C$13-$C$83</f>
         <v>31</v>
       </c>
-      <c r="E86" s="76"/>
-      <c r="F86" s="76"/>
-      <c r="G86" s="76"/>
-      <c r="H86" s="76"/>
-      <c r="I86" s="76"/>
-      <c r="J86" s="76"/>
-      <c r="K86" s="76"/>
-      <c r="L86" s="76"/>
-      <c r="M86" s="76"/>
-      <c r="N86" s="76"/>
-      <c r="O86" s="76"/>
+      <c r="E86" s="73"/>
+      <c r="F86" s="73"/>
+      <c r="G86" s="73"/>
+      <c r="H86" s="73"/>
+      <c r="I86" s="73"/>
+      <c r="J86" s="73"/>
+      <c r="K86" s="73"/>
+      <c r="L86" s="73"/>
+      <c r="M86" s="73"/>
+      <c r="N86" s="73"/>
+      <c r="O86" s="73"/>
     </row>
     <row r="87" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A87" s="8" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="C87" s="37" t="str">
         <f>IFERROR(AVERAGE($P$49:$P$79),"")</f>
         <v/>
       </c>
-      <c r="E87" s="75" t="s">
-        <v>94</v>
-      </c>
-      <c r="F87" s="75"/>
-      <c r="G87" s="75"/>
-      <c r="H87" s="75"/>
-      <c r="I87" s="75"/>
-      <c r="J87" s="75"/>
-      <c r="K87" s="75"/>
-      <c r="L87" s="75"/>
-      <c r="M87" s="75"/>
-      <c r="N87" s="75"/>
-      <c r="O87" s="75"/>
+      <c r="E87" s="72" t="s">
+        <v>92</v>
+      </c>
+      <c r="F87" s="72"/>
+      <c r="G87" s="72"/>
+      <c r="H87" s="72"/>
+      <c r="I87" s="72"/>
+      <c r="J87" s="72"/>
+      <c r="K87" s="72"/>
+      <c r="L87" s="72"/>
+      <c r="M87" s="72"/>
+      <c r="N87" s="72"/>
+      <c r="O87" s="72"/>
     </row>
     <row r="88" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A88" s="8" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="C88" s="38">
         <f>COUNT($K$49:$K$79)</f>
         <v>0</v>
       </c>
-      <c r="E88" s="75" t="s">
-        <v>96</v>
-      </c>
-      <c r="F88" s="75"/>
-      <c r="G88" s="75"/>
-      <c r="H88" s="75"/>
-      <c r="I88" s="75"/>
-      <c r="J88" s="75"/>
-      <c r="K88" s="75"/>
-      <c r="L88" s="75"/>
-      <c r="M88" s="75"/>
-      <c r="N88" s="75"/>
-      <c r="O88" s="75"/>
+      <c r="E88" s="72" t="s">
+        <v>94</v>
+      </c>
+      <c r="F88" s="72"/>
+      <c r="G88" s="72"/>
+      <c r="H88" s="72"/>
+      <c r="I88" s="72"/>
+      <c r="J88" s="72"/>
+      <c r="K88" s="72"/>
+      <c r="L88" s="72"/>
+      <c r="M88" s="72"/>
+      <c r="N88" s="72"/>
+      <c r="O88" s="72"/>
     </row>
     <row r="89" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A89" s="7" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="C89" s="39" t="str">
         <f>IF($C$88=$C$13,SUM($K$49:$K$79)/$C$13,"")</f>
         <v/>
       </c>
-      <c r="E89" s="75" t="s">
-        <v>98</v>
-      </c>
-      <c r="F89" s="75"/>
-      <c r="G89" s="75"/>
-      <c r="H89" s="75"/>
-      <c r="I89" s="75"/>
-      <c r="J89" s="75"/>
-      <c r="K89" s="75"/>
-      <c r="L89" s="75"/>
-      <c r="M89" s="75"/>
-      <c r="N89" s="75"/>
-      <c r="O89" s="75"/>
+      <c r="E89" s="72" t="s">
+        <v>96</v>
+      </c>
+      <c r="F89" s="72"/>
+      <c r="G89" s="72"/>
+      <c r="H89" s="72"/>
+      <c r="I89" s="72"/>
+      <c r="J89" s="72"/>
+      <c r="K89" s="72"/>
+      <c r="L89" s="72"/>
+      <c r="M89" s="72"/>
+      <c r="N89" s="72"/>
+      <c r="O89" s="72"/>
     </row>
     <row r="90" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A90" s="8" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="C90" s="40">
         <f>IFERROR(INDEX($C$30:$C$36,MATCH($C$83,$A$30:$A$36,1)),INDEX($C$30:$C$36,1))</f>
         <v>5.6899999999999999E-2</v>
       </c>
-      <c r="E90" s="75" t="s">
-        <v>100</v>
-      </c>
-      <c r="F90" s="75"/>
-      <c r="G90" s="75"/>
-      <c r="H90" s="75"/>
-      <c r="I90" s="75"/>
-      <c r="J90" s="75"/>
-      <c r="K90" s="75"/>
-      <c r="L90" s="75"/>
-      <c r="M90" s="75"/>
-      <c r="N90" s="75"/>
-      <c r="O90" s="75"/>
+      <c r="E90" s="72" t="s">
+        <v>98</v>
+      </c>
+      <c r="F90" s="72"/>
+      <c r="G90" s="72"/>
+      <c r="H90" s="72"/>
+      <c r="I90" s="72"/>
+      <c r="J90" s="72"/>
+      <c r="K90" s="72"/>
+      <c r="L90" s="72"/>
+      <c r="M90" s="72"/>
+      <c r="N90" s="72"/>
+      <c r="O90" s="72"/>
     </row>
     <row r="91" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A91" s="8" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="C91" s="40" t="str">
         <f>IFERROR(AVERAGE($X$49:$X$79),"")</f>
         <v/>
       </c>
-      <c r="E91" s="76"/>
-      <c r="F91" s="76"/>
-      <c r="G91" s="76"/>
-      <c r="H91" s="76"/>
-      <c r="I91" s="76"/>
-      <c r="J91" s="76"/>
-      <c r="K91" s="76"/>
-      <c r="L91" s="76"/>
-      <c r="M91" s="76"/>
-      <c r="N91" s="76"/>
-      <c r="O91" s="76"/>
+      <c r="E91" s="73"/>
+      <c r="F91" s="73"/>
+      <c r="G91" s="73"/>
+      <c r="H91" s="73"/>
+      <c r="I91" s="73"/>
+      <c r="J91" s="73"/>
+      <c r="K91" s="73"/>
+      <c r="L91" s="73"/>
+      <c r="M91" s="73"/>
+      <c r="N91" s="73"/>
+      <c r="O91" s="73"/>
     </row>
     <row r="92" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A92" s="8" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="C92" s="40">
         <f>IFERROR($C$43*$C$91*$C$86/$C$13,0)</f>
         <v>0</v>
       </c>
-      <c r="E92" s="75" t="s">
-        <v>103</v>
-      </c>
-      <c r="F92" s="75"/>
-      <c r="G92" s="75"/>
-      <c r="H92" s="75"/>
-      <c r="I92" s="75"/>
-      <c r="J92" s="75"/>
-      <c r="K92" s="75"/>
-      <c r="L92" s="75"/>
-      <c r="M92" s="75"/>
-      <c r="N92" s="75"/>
-      <c r="O92" s="75"/>
+      <c r="E92" s="72" t="s">
+        <v>101</v>
+      </c>
+      <c r="F92" s="72"/>
+      <c r="G92" s="72"/>
+      <c r="H92" s="72"/>
+      <c r="I92" s="72"/>
+      <c r="J92" s="72"/>
+      <c r="K92" s="72"/>
+      <c r="L92" s="72"/>
+      <c r="M92" s="72"/>
+      <c r="N92" s="72"/>
+      <c r="O92" s="72"/>
     </row>
     <row r="93" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A93" s="8" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="C93" s="40">
         <f>IFERROR(SQRT($C$90^2+$C$92^2),"")</f>
         <v>5.6899999999999999E-2</v>
       </c>
-      <c r="E93" s="75" t="s">
-        <v>105</v>
-      </c>
-      <c r="F93" s="75"/>
-      <c r="G93" s="75"/>
-      <c r="H93" s="75"/>
-      <c r="I93" s="75"/>
-      <c r="J93" s="75"/>
-      <c r="K93" s="75"/>
-      <c r="L93" s="75"/>
-      <c r="M93" s="75"/>
-      <c r="N93" s="75"/>
-      <c r="O93" s="75"/>
+      <c r="E93" s="72" t="s">
+        <v>103</v>
+      </c>
+      <c r="F93" s="72"/>
+      <c r="G93" s="72"/>
+      <c r="H93" s="72"/>
+      <c r="I93" s="72"/>
+      <c r="J93" s="72"/>
+      <c r="K93" s="72"/>
+      <c r="L93" s="72"/>
+      <c r="M93" s="72"/>
+      <c r="N93" s="72"/>
+      <c r="O93" s="72"/>
     </row>
     <row r="94" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A94" s="7" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="C94" s="39" t="str">
         <f>IF($C$89="","",$C$22+$C$23*$C$89)</f>
         <v/>
       </c>
-      <c r="E94" s="75" t="s">
-        <v>107</v>
-      </c>
-      <c r="F94" s="75"/>
-      <c r="G94" s="75"/>
-      <c r="H94" s="75"/>
-      <c r="I94" s="75"/>
-      <c r="J94" s="75"/>
-      <c r="K94" s="75"/>
-      <c r="L94" s="75"/>
-      <c r="M94" s="75"/>
-      <c r="N94" s="75"/>
-      <c r="O94" s="75"/>
+      <c r="E94" s="72" t="s">
+        <v>105</v>
+      </c>
+      <c r="F94" s="72"/>
+      <c r="G94" s="72"/>
+      <c r="H94" s="72"/>
+      <c r="I94" s="72"/>
+      <c r="J94" s="72"/>
+      <c r="K94" s="72"/>
+      <c r="L94" s="72"/>
+      <c r="M94" s="72"/>
+      <c r="N94" s="72"/>
+      <c r="O94" s="72"/>
     </row>
     <row r="95" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A95" s="8" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="C95" s="40" t="str">
         <f>IF($C$89="","",SQRT(($C$23*$C$93)^2+$C$24^2))</f>
         <v/>
       </c>
-      <c r="E95" s="75" t="s">
-        <v>109</v>
-      </c>
-      <c r="F95" s="75"/>
-      <c r="G95" s="75"/>
-      <c r="H95" s="75"/>
-      <c r="I95" s="75"/>
-      <c r="J95" s="75"/>
-      <c r="K95" s="75"/>
-      <c r="L95" s="75"/>
-      <c r="M95" s="75"/>
-      <c r="N95" s="75"/>
-      <c r="O95" s="75"/>
+      <c r="E95" s="72" t="s">
+        <v>107</v>
+      </c>
+      <c r="F95" s="72"/>
+      <c r="G95" s="72"/>
+      <c r="H95" s="72"/>
+      <c r="I95" s="72"/>
+      <c r="J95" s="72"/>
+      <c r="K95" s="72"/>
+      <c r="L95" s="72"/>
+      <c r="M95" s="72"/>
+      <c r="N95" s="72"/>
+      <c r="O95" s="72"/>
     </row>
     <row r="96" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A96" s="8" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="C96" s="37" t="str">
         <f>IF($C$94="","",($C$17-$C$94)/$C$95)</f>
         <v/>
       </c>
-      <c r="E96" s="75" t="s">
-        <v>111</v>
-      </c>
-      <c r="F96" s="75"/>
-      <c r="G96" s="75"/>
-      <c r="H96" s="75"/>
-      <c r="I96" s="75"/>
-      <c r="J96" s="75"/>
-      <c r="K96" s="75"/>
-      <c r="L96" s="75"/>
-      <c r="M96" s="75"/>
-      <c r="N96" s="75"/>
-      <c r="O96" s="75"/>
+      <c r="E96" s="72" t="s">
+        <v>109</v>
+      </c>
+      <c r="F96" s="72"/>
+      <c r="G96" s="72"/>
+      <c r="H96" s="72"/>
+      <c r="I96" s="72"/>
+      <c r="J96" s="72"/>
+      <c r="K96" s="72"/>
+      <c r="L96" s="72"/>
+      <c r="M96" s="72"/>
+      <c r="N96" s="72"/>
+      <c r="O96" s="72"/>
     </row>
     <row r="97" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A97" s="8" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="C97" s="41" t="str">
         <f>IF($C$96="","",1-NORMSDIST($C$96))</f>
         <v/>
       </c>
-      <c r="E97" s="75" t="s">
-        <v>113</v>
-      </c>
-      <c r="F97" s="75"/>
-      <c r="G97" s="75"/>
-      <c r="H97" s="75"/>
-      <c r="I97" s="75"/>
-      <c r="J97" s="75"/>
-      <c r="K97" s="75"/>
-      <c r="L97" s="75"/>
-      <c r="M97" s="75"/>
-      <c r="N97" s="75"/>
-      <c r="O97" s="75"/>
+      <c r="E97" s="72" t="s">
+        <v>111</v>
+      </c>
+      <c r="F97" s="72"/>
+      <c r="G97" s="72"/>
+      <c r="H97" s="72"/>
+      <c r="I97" s="72"/>
+      <c r="J97" s="72"/>
+      <c r="K97" s="72"/>
+      <c r="L97" s="72"/>
+      <c r="M97" s="72"/>
+      <c r="N97" s="72"/>
+      <c r="O97" s="72"/>
     </row>
     <row r="98" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A98" s="8" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="C98" s="37" t="str">
         <f>IF(OR($C$83=0,$C$83&gt;=$C$13),"",($C$13*$C$26-$C$84)/($C$13-$C$83))</f>
         <v/>
       </c>
-      <c r="E98" s="75" t="s">
-        <v>115</v>
-      </c>
-      <c r="F98" s="75"/>
-      <c r="G98" s="75"/>
-      <c r="H98" s="75"/>
-      <c r="I98" s="75"/>
-      <c r="J98" s="75"/>
-      <c r="K98" s="75"/>
-      <c r="L98" s="75"/>
-      <c r="M98" s="75"/>
-      <c r="N98" s="75"/>
-      <c r="O98" s="75"/>
+      <c r="E98" s="72" t="s">
+        <v>113</v>
+      </c>
+      <c r="F98" s="72"/>
+      <c r="G98" s="72"/>
+      <c r="H98" s="72"/>
+      <c r="I98" s="72"/>
+      <c r="J98" s="72"/>
+      <c r="K98" s="72"/>
+      <c r="L98" s="72"/>
+      <c r="M98" s="72"/>
+      <c r="N98" s="72"/>
+      <c r="O98" s="72"/>
     </row>
     <row r="99" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A99" s="8" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="C99" s="41" t="str">
         <f>IF($C$94="","",NORMSDIST(($C$17-$C$94)/$C$95)-NORMSDIST(($C$18-$C$94)/$C$95))</f>
         <v/>
       </c>
-      <c r="E99" s="75" t="s">
-        <v>117</v>
-      </c>
-      <c r="F99" s="75"/>
-      <c r="G99" s="75"/>
-      <c r="H99" s="75"/>
-      <c r="I99" s="75"/>
-      <c r="J99" s="75"/>
-      <c r="K99" s="75"/>
-      <c r="L99" s="75"/>
-      <c r="M99" s="75"/>
-      <c r="N99" s="75"/>
-      <c r="O99" s="75"/>
+      <c r="E99" s="72" t="s">
+        <v>115</v>
+      </c>
+      <c r="F99" s="72"/>
+      <c r="G99" s="72"/>
+      <c r="H99" s="72"/>
+      <c r="I99" s="72"/>
+      <c r="J99" s="72"/>
+      <c r="K99" s="72"/>
+      <c r="L99" s="72"/>
+      <c r="M99" s="72"/>
+      <c r="N99" s="72"/>
+      <c r="O99" s="72"/>
     </row>
     <row r="100" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A100" s="7" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="C100" s="42" t="str">
         <f>IFERROR(ENS_members_raw!$E$64,"")</f>
         <v/>
       </c>
-      <c r="E100" s="75" t="s">
-        <v>119</v>
-      </c>
-      <c r="F100" s="75"/>
-      <c r="G100" s="75"/>
-      <c r="H100" s="75"/>
-      <c r="I100" s="75"/>
-      <c r="J100" s="75"/>
-      <c r="K100" s="75"/>
-      <c r="L100" s="75"/>
-      <c r="M100" s="75"/>
-      <c r="N100" s="75"/>
-      <c r="O100" s="75"/>
+      <c r="E100" s="72" t="s">
+        <v>117</v>
+      </c>
+      <c r="F100" s="72"/>
+      <c r="G100" s="72"/>
+      <c r="H100" s="72"/>
+      <c r="I100" s="72"/>
+      <c r="J100" s="72"/>
+      <c r="K100" s="72"/>
+      <c r="L100" s="72"/>
+      <c r="M100" s="72"/>
+      <c r="N100" s="72"/>
+      <c r="O100" s="72"/>
     </row>
     <row r="101" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A101" s="8" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="C101" s="41" t="str">
         <f>IFERROR(ENS_members_raw!$H$64,"")</f>
         <v/>
       </c>
-      <c r="E101" s="75" t="s">
-        <v>121</v>
-      </c>
-      <c r="F101" s="75"/>
-      <c r="G101" s="75"/>
-      <c r="H101" s="75"/>
-      <c r="I101" s="75"/>
-      <c r="J101" s="75"/>
-      <c r="K101" s="75"/>
-      <c r="L101" s="75"/>
-      <c r="M101" s="75"/>
-      <c r="N101" s="75"/>
-      <c r="O101" s="75"/>
+      <c r="E101" s="72" t="s">
+        <v>119</v>
+      </c>
+      <c r="F101" s="72"/>
+      <c r="G101" s="72"/>
+      <c r="H101" s="72"/>
+      <c r="I101" s="72"/>
+      <c r="J101" s="72"/>
+      <c r="K101" s="72"/>
+      <c r="L101" s="72"/>
+      <c r="M101" s="72"/>
+      <c r="N101" s="72"/>
+      <c r="O101" s="72"/>
     </row>
     <row r="103" spans="1:15" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A103" s="80" t="s">
-        <v>122</v>
-      </c>
-      <c r="B103" s="80"/>
-      <c r="C103" s="80"/>
-      <c r="D103" s="80"/>
-      <c r="E103" s="80"/>
-      <c r="F103" s="80"/>
-      <c r="G103" s="80"/>
-      <c r="H103" s="80"/>
-      <c r="I103" s="80"/>
-      <c r="J103" s="80"/>
-      <c r="K103" s="80"/>
-      <c r="L103" s="80"/>
-      <c r="M103" s="80"/>
-      <c r="N103" s="80"/>
-      <c r="O103" s="80"/>
+      <c r="A103" s="77" t="s">
+        <v>248</v>
+      </c>
+      <c r="B103" s="77"/>
+      <c r="C103" s="77"/>
+      <c r="D103" s="77"/>
+      <c r="E103" s="77"/>
+      <c r="F103" s="77"/>
+      <c r="G103" s="77"/>
+      <c r="H103" s="77"/>
+      <c r="I103" s="77"/>
+      <c r="J103" s="77"/>
+      <c r="K103" s="77"/>
+      <c r="L103" s="77"/>
+      <c r="M103" s="77"/>
+      <c r="N103" s="77"/>
+      <c r="O103" s="77"/>
     </row>
     <row r="104" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A104" s="8" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="C104" s="43"/>
-      <c r="E104" s="75" t="s">
-        <v>124</v>
-      </c>
-      <c r="F104" s="75"/>
-      <c r="G104" s="75"/>
-      <c r="H104" s="75"/>
-      <c r="I104" s="75"/>
-      <c r="J104" s="75"/>
-      <c r="K104" s="75"/>
-      <c r="L104" s="75"/>
-      <c r="M104" s="75"/>
-      <c r="N104" s="75"/>
-      <c r="O104" s="75"/>
+      <c r="E104" s="72" t="s">
+        <v>121</v>
+      </c>
+      <c r="F104" s="72"/>
+      <c r="G104" s="72"/>
+      <c r="H104" s="72"/>
+      <c r="I104" s="72"/>
+      <c r="J104" s="72"/>
+      <c r="K104" s="72"/>
+      <c r="L104" s="72"/>
+      <c r="M104" s="72"/>
+      <c r="N104" s="72"/>
+      <c r="O104" s="72"/>
     </row>
     <row r="105" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A105" s="8" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="C105" s="43"/>
-      <c r="E105" s="75" t="s">
-        <v>126</v>
-      </c>
-      <c r="F105" s="75"/>
-      <c r="G105" s="75"/>
-      <c r="H105" s="75"/>
-      <c r="I105" s="75"/>
-      <c r="J105" s="75"/>
-      <c r="K105" s="75"/>
-      <c r="L105" s="75"/>
-      <c r="M105" s="75"/>
-      <c r="N105" s="75"/>
-      <c r="O105" s="75"/>
+      <c r="E105" s="72" t="s">
+        <v>123</v>
+      </c>
+      <c r="F105" s="72"/>
+      <c r="G105" s="72"/>
+      <c r="H105" s="72"/>
+      <c r="I105" s="72"/>
+      <c r="J105" s="72"/>
+      <c r="K105" s="72"/>
+      <c r="L105" s="72"/>
+      <c r="M105" s="72"/>
+      <c r="N105" s="72"/>
+      <c r="O105" s="72"/>
     </row>
     <row r="106" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A106" s="8" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="C106" s="43"/>
-      <c r="E106" s="76"/>
-      <c r="F106" s="76"/>
-      <c r="G106" s="76"/>
-      <c r="H106" s="76"/>
-      <c r="I106" s="76"/>
-      <c r="J106" s="76"/>
-      <c r="K106" s="76"/>
-      <c r="L106" s="76"/>
-      <c r="M106" s="76"/>
-      <c r="N106" s="76"/>
-      <c r="O106" s="76"/>
+      <c r="E106" s="73"/>
+      <c r="F106" s="73"/>
+      <c r="G106" s="73"/>
+      <c r="H106" s="73"/>
+      <c r="I106" s="73"/>
+      <c r="J106" s="73"/>
+      <c r="K106" s="73"/>
+      <c r="L106" s="73"/>
+      <c r="M106" s="73"/>
+      <c r="N106" s="73"/>
+      <c r="O106" s="73"/>
     </row>
     <row r="107" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A107" s="8" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="C107" s="43"/>
-      <c r="E107" s="75" t="s">
-        <v>129</v>
-      </c>
-      <c r="F107" s="75"/>
-      <c r="G107" s="75"/>
-      <c r="H107" s="75"/>
-      <c r="I107" s="75"/>
-      <c r="J107" s="75"/>
-      <c r="K107" s="75"/>
-      <c r="L107" s="75"/>
-      <c r="M107" s="75"/>
-      <c r="N107" s="75"/>
-      <c r="O107" s="75"/>
+      <c r="E107" s="72" t="s">
+        <v>126</v>
+      </c>
+      <c r="F107" s="72"/>
+      <c r="G107" s="72"/>
+      <c r="H107" s="72"/>
+      <c r="I107" s="72"/>
+      <c r="J107" s="72"/>
+      <c r="K107" s="72"/>
+      <c r="L107" s="72"/>
+      <c r="M107" s="72"/>
+      <c r="N107" s="72"/>
+      <c r="O107" s="72"/>
     </row>
     <row r="108" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A108" s="8" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="C108" s="44"/>
-      <c r="E108" s="75" t="s">
-        <v>131</v>
-      </c>
-      <c r="F108" s="75"/>
-      <c r="G108" s="75"/>
-      <c r="H108" s="75"/>
-      <c r="I108" s="75"/>
-      <c r="J108" s="75"/>
-      <c r="K108" s="75"/>
-      <c r="L108" s="75"/>
-      <c r="M108" s="75"/>
-      <c r="N108" s="75"/>
-      <c r="O108" s="75"/>
+      <c r="E108" s="72" t="s">
+        <v>128</v>
+      </c>
+      <c r="F108" s="72"/>
+      <c r="G108" s="72"/>
+      <c r="H108" s="72"/>
+      <c r="I108" s="72"/>
+      <c r="J108" s="72"/>
+      <c r="K108" s="72"/>
+      <c r="L108" s="72"/>
+      <c r="M108" s="72"/>
+      <c r="N108" s="72"/>
+      <c r="O108" s="72"/>
     </row>
     <row r="109" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A109" s="8" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="C109" s="45"/>
-      <c r="E109" s="75" t="s">
-        <v>133</v>
-      </c>
-      <c r="F109" s="75"/>
-      <c r="G109" s="75"/>
-      <c r="H109" s="75"/>
-      <c r="I109" s="75"/>
-      <c r="J109" s="75"/>
-      <c r="K109" s="75"/>
-      <c r="L109" s="75"/>
-      <c r="M109" s="75"/>
-      <c r="N109" s="75"/>
-      <c r="O109" s="75"/>
+      <c r="E109" s="72" t="s">
+        <v>130</v>
+      </c>
+      <c r="F109" s="72"/>
+      <c r="G109" s="72"/>
+      <c r="H109" s="72"/>
+      <c r="I109" s="72"/>
+      <c r="J109" s="72"/>
+      <c r="K109" s="72"/>
+      <c r="L109" s="72"/>
+      <c r="M109" s="72"/>
+      <c r="N109" s="72"/>
+      <c r="O109" s="72"/>
     </row>
     <row r="110" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A110" s="8" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="C110" s="44"/>
-      <c r="E110" s="76"/>
-      <c r="F110" s="76"/>
-      <c r="G110" s="76"/>
-      <c r="H110" s="76"/>
-      <c r="I110" s="76"/>
-      <c r="J110" s="76"/>
-      <c r="K110" s="76"/>
-      <c r="L110" s="76"/>
-      <c r="M110" s="76"/>
-      <c r="N110" s="76"/>
-      <c r="O110" s="76"/>
+      <c r="E110" s="73"/>
+      <c r="F110" s="73"/>
+      <c r="G110" s="73"/>
+      <c r="H110" s="73"/>
+      <c r="I110" s="73"/>
+      <c r="J110" s="73"/>
+      <c r="K110" s="73"/>
+      <c r="L110" s="73"/>
+      <c r="M110" s="73"/>
+      <c r="N110" s="73"/>
+      <c r="O110" s="73"/>
     </row>
     <row r="111" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A111" s="8" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="C111" s="44"/>
-      <c r="E111" s="76"/>
-      <c r="F111" s="76"/>
-      <c r="G111" s="76"/>
-      <c r="H111" s="76"/>
-      <c r="I111" s="76"/>
-      <c r="J111" s="76"/>
-      <c r="K111" s="76"/>
-      <c r="L111" s="76"/>
-      <c r="M111" s="76"/>
-      <c r="N111" s="76"/>
-      <c r="O111" s="76"/>
+      <c r="E111" s="73"/>
+      <c r="F111" s="73"/>
+      <c r="G111" s="73"/>
+      <c r="H111" s="73"/>
+      <c r="I111" s="73"/>
+      <c r="J111" s="73"/>
+      <c r="K111" s="73"/>
+      <c r="L111" s="73"/>
+      <c r="M111" s="73"/>
+      <c r="N111" s="73"/>
+      <c r="O111" s="73"/>
     </row>
     <row r="113" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A113" s="8" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="C113" s="41" t="str">
         <f>IF($C$105="","",$C$105/100)</f>
         <v/>
       </c>
-      <c r="E113" s="75" t="s">
-        <v>137</v>
-      </c>
-      <c r="F113" s="75"/>
-      <c r="G113" s="75"/>
-      <c r="H113" s="75"/>
-      <c r="I113" s="75"/>
-      <c r="J113" s="75"/>
-      <c r="K113" s="75"/>
-      <c r="L113" s="75"/>
-      <c r="M113" s="75"/>
-      <c r="N113" s="75"/>
-      <c r="O113" s="75"/>
+      <c r="E113" s="72" t="s">
+        <v>134</v>
+      </c>
+      <c r="F113" s="72"/>
+      <c r="G113" s="72"/>
+      <c r="H113" s="72"/>
+      <c r="I113" s="72"/>
+      <c r="J113" s="72"/>
+      <c r="K113" s="72"/>
+      <c r="L113" s="72"/>
+      <c r="M113" s="72"/>
+      <c r="N113" s="72"/>
+      <c r="O113" s="72"/>
     </row>
     <row r="114" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A114" s="8" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="C114" s="41" t="str">
         <f>IF(OR($C$100="",$C$97=""),"",MIN($C$100,$C$97))</f>
         <v/>
       </c>
-      <c r="E114" s="75" t="s">
-        <v>139</v>
-      </c>
-      <c r="F114" s="75"/>
-      <c r="G114" s="75"/>
-      <c r="H114" s="75"/>
-      <c r="I114" s="75"/>
-      <c r="J114" s="75"/>
-      <c r="K114" s="75"/>
-      <c r="L114" s="75"/>
-      <c r="M114" s="75"/>
-      <c r="N114" s="75"/>
-      <c r="O114" s="75"/>
+      <c r="E114" s="72" t="s">
+        <v>136</v>
+      </c>
+      <c r="F114" s="72"/>
+      <c r="G114" s="72"/>
+      <c r="H114" s="72"/>
+      <c r="I114" s="72"/>
+      <c r="J114" s="72"/>
+      <c r="K114" s="72"/>
+      <c r="L114" s="72"/>
+      <c r="M114" s="72"/>
+      <c r="N114" s="72"/>
+      <c r="O114" s="72"/>
     </row>
     <row r="115" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A115" s="8" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="C115" s="41" t="str">
         <f>IF(OR($C$100="",$C$97=""),"",MAX($C$100,$C$97))</f>
         <v/>
       </c>
-      <c r="E115" s="75" t="s">
-        <v>141</v>
-      </c>
-      <c r="F115" s="75"/>
-      <c r="G115" s="75"/>
-      <c r="H115" s="75"/>
-      <c r="I115" s="75"/>
-      <c r="J115" s="75"/>
-      <c r="K115" s="75"/>
-      <c r="L115" s="75"/>
-      <c r="M115" s="75"/>
-      <c r="N115" s="75"/>
-      <c r="O115" s="75"/>
+      <c r="E115" s="72" t="s">
+        <v>138</v>
+      </c>
+      <c r="F115" s="72"/>
+      <c r="G115" s="72"/>
+      <c r="H115" s="72"/>
+      <c r="I115" s="72"/>
+      <c r="J115" s="72"/>
+      <c r="K115" s="72"/>
+      <c r="L115" s="72"/>
+      <c r="M115" s="72"/>
+      <c r="N115" s="72"/>
+      <c r="O115" s="72"/>
     </row>
     <row r="116" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A116" s="8" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="C116" s="46" t="str">
         <f>IF($C$114="","",$C$114*100)</f>
         <v/>
       </c>
-      <c r="E116" s="76"/>
-      <c r="F116" s="76"/>
-      <c r="G116" s="76"/>
-      <c r="H116" s="76"/>
-      <c r="I116" s="76"/>
-      <c r="J116" s="76"/>
-      <c r="K116" s="76"/>
-      <c r="L116" s="76"/>
-      <c r="M116" s="76"/>
-      <c r="N116" s="76"/>
-      <c r="O116" s="76"/>
+      <c r="E116" s="73"/>
+      <c r="F116" s="73"/>
+      <c r="G116" s="73"/>
+      <c r="H116" s="73"/>
+      <c r="I116" s="73"/>
+      <c r="J116" s="73"/>
+      <c r="K116" s="73"/>
+      <c r="L116" s="73"/>
+      <c r="M116" s="73"/>
+      <c r="N116" s="73"/>
+      <c r="O116" s="73"/>
     </row>
     <row r="117" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A117" s="8" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="C117" s="46" t="str">
         <f>IF($C$115="","",(1-$C$115)*100)</f>
         <v/>
       </c>
-      <c r="E117" s="76"/>
-      <c r="F117" s="76"/>
-      <c r="G117" s="76"/>
-      <c r="H117" s="76"/>
-      <c r="I117" s="76"/>
-      <c r="J117" s="76"/>
-      <c r="K117" s="76"/>
-      <c r="L117" s="76"/>
-      <c r="M117" s="76"/>
-      <c r="N117" s="76"/>
-      <c r="O117" s="76"/>
+      <c r="E117" s="73"/>
+      <c r="F117" s="73"/>
+      <c r="G117" s="73"/>
+      <c r="H117" s="73"/>
+      <c r="I117" s="73"/>
+      <c r="J117" s="73"/>
+      <c r="K117" s="73"/>
+      <c r="L117" s="73"/>
+      <c r="M117" s="73"/>
+      <c r="N117" s="73"/>
+      <c r="O117" s="73"/>
     </row>
     <row r="118" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A118" s="7" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="C118" s="47" t="str">
         <f>IF(OR($C$116="",$C$105=""),"",$C$116-$C$105)</f>
         <v/>
       </c>
-      <c r="E118" s="75" t="s">
-        <v>145</v>
-      </c>
-      <c r="F118" s="75"/>
-      <c r="G118" s="75"/>
-      <c r="H118" s="75"/>
-      <c r="I118" s="75"/>
-      <c r="J118" s="75"/>
-      <c r="K118" s="75"/>
-      <c r="L118" s="75"/>
-      <c r="M118" s="75"/>
-      <c r="N118" s="75"/>
-      <c r="O118" s="75"/>
+      <c r="E118" s="72" t="s">
+        <v>142</v>
+      </c>
+      <c r="F118" s="72"/>
+      <c r="G118" s="72"/>
+      <c r="H118" s="72"/>
+      <c r="I118" s="72"/>
+      <c r="J118" s="72"/>
+      <c r="K118" s="72"/>
+      <c r="L118" s="72"/>
+      <c r="M118" s="72"/>
+      <c r="N118" s="72"/>
+      <c r="O118" s="72"/>
     </row>
     <row r="119" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A119" s="7" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="C119" s="47" t="str">
         <f>IF(OR($C$117="",$C$107=""),"",$C$117-$C$107)</f>
         <v/>
       </c>
-      <c r="E119" s="75" t="s">
-        <v>145</v>
-      </c>
-      <c r="F119" s="75"/>
-      <c r="G119" s="75"/>
-      <c r="H119" s="75"/>
-      <c r="I119" s="75"/>
-      <c r="J119" s="75"/>
-      <c r="K119" s="75"/>
-      <c r="L119" s="75"/>
-      <c r="M119" s="75"/>
-      <c r="N119" s="75"/>
-      <c r="O119" s="75"/>
+      <c r="E119" s="72" t="s">
+        <v>142</v>
+      </c>
+      <c r="F119" s="72"/>
+      <c r="G119" s="72"/>
+      <c r="H119" s="72"/>
+      <c r="I119" s="72"/>
+      <c r="J119" s="72"/>
+      <c r="K119" s="72"/>
+      <c r="L119" s="72"/>
+      <c r="M119" s="72"/>
+      <c r="N119" s="72"/>
+      <c r="O119" s="72"/>
     </row>
     <row r="120" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A120" s="8" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="C120" s="48" t="str">
         <f>IF(OR($C$110="",$C$105=""),"",CEILING(0.07*$C$110*($C$105/100)*(1-$C$105/100),1))</f>
         <v/>
       </c>
-      <c r="E120" s="75" t="s">
-        <v>148</v>
-      </c>
-      <c r="F120" s="75"/>
-      <c r="G120" s="75"/>
-      <c r="H120" s="75"/>
-      <c r="I120" s="75"/>
-      <c r="J120" s="75"/>
-      <c r="K120" s="75"/>
-      <c r="L120" s="75"/>
-      <c r="M120" s="75"/>
-      <c r="N120" s="75"/>
-      <c r="O120" s="75"/>
+      <c r="E120" s="72" t="s">
+        <v>145</v>
+      </c>
+      <c r="F120" s="72"/>
+      <c r="G120" s="72"/>
+      <c r="H120" s="72"/>
+      <c r="I120" s="72"/>
+      <c r="J120" s="72"/>
+      <c r="K120" s="72"/>
+      <c r="L120" s="72"/>
+      <c r="M120" s="72"/>
+      <c r="N120" s="72"/>
+      <c r="O120" s="72"/>
     </row>
     <row r="121" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A121" s="8" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="C121" s="48" t="str">
         <f>IF(OR($C$110="",$C$107=""),"",CEILING(0.07*$C$110*($C$107/100)*(1-$C$107/100),1))</f>
         <v/>
       </c>
-      <c r="E121" s="76"/>
-      <c r="F121" s="76"/>
-      <c r="G121" s="76"/>
-      <c r="H121" s="76"/>
-      <c r="I121" s="76"/>
-      <c r="J121" s="76"/>
-      <c r="K121" s="76"/>
-      <c r="L121" s="76"/>
-      <c r="M121" s="76"/>
-      <c r="N121" s="76"/>
-      <c r="O121" s="76"/>
+      <c r="E121" s="73"/>
+      <c r="F121" s="73"/>
+      <c r="G121" s="73"/>
+      <c r="H121" s="73"/>
+      <c r="I121" s="73"/>
+      <c r="J121" s="73"/>
+      <c r="K121" s="73"/>
+      <c r="L121" s="73"/>
+      <c r="M121" s="73"/>
+      <c r="N121" s="73"/>
+      <c r="O121" s="73"/>
     </row>
     <row r="122" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A122" s="7" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="C122" s="47" t="str">
         <f>IF(OR($C$118="",$C$110="",$C$110=0),"",$C$118-$C$120/$C$110)</f>
         <v/>
       </c>
-      <c r="E122" s="76"/>
-      <c r="F122" s="76"/>
-      <c r="G122" s="76"/>
-      <c r="H122" s="76"/>
-      <c r="I122" s="76"/>
-      <c r="J122" s="76"/>
-      <c r="K122" s="76"/>
-      <c r="L122" s="76"/>
-      <c r="M122" s="76"/>
-      <c r="N122" s="76"/>
-      <c r="O122" s="76"/>
+      <c r="E122" s="73"/>
+      <c r="F122" s="73"/>
+      <c r="G122" s="73"/>
+      <c r="H122" s="73"/>
+      <c r="I122" s="73"/>
+      <c r="J122" s="73"/>
+      <c r="K122" s="73"/>
+      <c r="L122" s="73"/>
+      <c r="M122" s="73"/>
+      <c r="N122" s="73"/>
+      <c r="O122" s="73"/>
     </row>
     <row r="123" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A123" s="7" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="C123" s="47" t="str">
         <f>IF(OR($C$119="",$C$110="",$C$110=0),"",$C$119-$C$121/$C$110)</f>
         <v/>
       </c>
-      <c r="E123" s="76"/>
-      <c r="F123" s="76"/>
-      <c r="G123" s="76"/>
-      <c r="H123" s="76"/>
-      <c r="I123" s="76"/>
-      <c r="J123" s="76"/>
-      <c r="K123" s="76"/>
-      <c r="L123" s="76"/>
-      <c r="M123" s="76"/>
-      <c r="N123" s="76"/>
-      <c r="O123" s="76"/>
+      <c r="E123" s="73"/>
+      <c r="F123" s="73"/>
+      <c r="G123" s="73"/>
+      <c r="H123" s="73"/>
+      <c r="I123" s="73"/>
+      <c r="J123" s="73"/>
+      <c r="K123" s="73"/>
+      <c r="L123" s="73"/>
+      <c r="M123" s="73"/>
+      <c r="N123" s="73"/>
+      <c r="O123" s="73"/>
     </row>
     <row r="124" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A124" s="8" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="C124" s="49" t="str">
         <f>IF(OR($C$114="",$C$105=""),"",IFERROR(($C$114*((100-$C$105)/$C$105)-(1-$C$114))/((100-$C$105)/$C$105),""))</f>
         <v/>
       </c>
-      <c r="E124" s="75" t="s">
-        <v>153</v>
-      </c>
-      <c r="F124" s="75"/>
-      <c r="G124" s="75"/>
-      <c r="H124" s="75"/>
-      <c r="I124" s="75"/>
-      <c r="J124" s="75"/>
-      <c r="K124" s="75"/>
-      <c r="L124" s="75"/>
-      <c r="M124" s="75"/>
-      <c r="N124" s="75"/>
-      <c r="O124" s="75"/>
+      <c r="E124" s="72" t="s">
+        <v>150</v>
+      </c>
+      <c r="F124" s="72"/>
+      <c r="G124" s="72"/>
+      <c r="H124" s="72"/>
+      <c r="I124" s="72"/>
+      <c r="J124" s="72"/>
+      <c r="K124" s="72"/>
+      <c r="L124" s="72"/>
+      <c r="M124" s="72"/>
+      <c r="N124" s="72"/>
+      <c r="O124" s="72"/>
     </row>
     <row r="125" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A125" s="8" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="C125" s="49" t="str">
         <f>IF(OR($C$115="",$C$107=""),"",IFERROR(((1-$C$115)*((100-$C$107)/$C$107)-$C$115)/((100-$C$107)/$C$107),""))</f>
         <v/>
       </c>
-      <c r="E125" s="76"/>
-      <c r="F125" s="76"/>
-      <c r="G125" s="76"/>
-      <c r="H125" s="76"/>
-      <c r="I125" s="76"/>
-      <c r="J125" s="76"/>
-      <c r="K125" s="76"/>
-      <c r="L125" s="76"/>
-      <c r="M125" s="76"/>
-      <c r="N125" s="76"/>
-      <c r="O125" s="76"/>
+      <c r="E125" s="73"/>
+      <c r="F125" s="73"/>
+      <c r="G125" s="73"/>
+      <c r="H125" s="73"/>
+      <c r="I125" s="73"/>
+      <c r="J125" s="73"/>
+      <c r="K125" s="73"/>
+      <c r="L125" s="73"/>
+      <c r="M125" s="73"/>
+      <c r="N125" s="73"/>
+      <c r="O125" s="73"/>
     </row>
     <row r="126" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A126" s="8"/>
@@ -5392,17 +5333,17 @@
         <f>IF($C$124="","",MAX(0,$C$124/4))</f>
         <v/>
       </c>
-      <c r="E126" s="75"/>
-      <c r="F126" s="75"/>
-      <c r="G126" s="75"/>
-      <c r="H126" s="75"/>
-      <c r="I126" s="75"/>
-      <c r="J126" s="75"/>
-      <c r="K126" s="75"/>
-      <c r="L126" s="75"/>
-      <c r="M126" s="75"/>
-      <c r="N126" s="75"/>
-      <c r="O126" s="75"/>
+      <c r="E126" s="72"/>
+      <c r="F126" s="72"/>
+      <c r="G126" s="72"/>
+      <c r="H126" s="72"/>
+      <c r="I126" s="72"/>
+      <c r="J126" s="72"/>
+      <c r="K126" s="72"/>
+      <c r="L126" s="72"/>
+      <c r="M126" s="72"/>
+      <c r="N126" s="72"/>
+      <c r="O126" s="72"/>
     </row>
     <row r="127" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A127" s="8"/>
@@ -5410,195 +5351,195 @@
         <f>IF($C$125="","",MAX(0,$C$125/4))</f>
         <v/>
       </c>
-      <c r="E127" s="76"/>
-      <c r="F127" s="76"/>
-      <c r="G127" s="76"/>
-      <c r="H127" s="76"/>
-      <c r="I127" s="76"/>
-      <c r="J127" s="76"/>
-      <c r="K127" s="76"/>
-      <c r="L127" s="76"/>
-      <c r="M127" s="76"/>
-      <c r="N127" s="76"/>
-      <c r="O127" s="76"/>
+      <c r="E127" s="73"/>
+      <c r="F127" s="73"/>
+      <c r="G127" s="73"/>
+      <c r="H127" s="73"/>
+      <c r="I127" s="73"/>
+      <c r="J127" s="73"/>
+      <c r="K127" s="73"/>
+      <c r="L127" s="73"/>
+      <c r="M127" s="73"/>
+      <c r="N127" s="73"/>
+      <c r="O127" s="73"/>
     </row>
     <row r="128" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A128" s="7" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="C128" s="50" t="str">
         <f>IF(OR($C$126="",$C$109="",$C$108="",$C$105=""),"",MIN($C$126*$C$109,$C$108/3*$C$105/100,300))</f>
         <v/>
       </c>
-      <c r="E128" s="76"/>
-      <c r="F128" s="76"/>
-      <c r="G128" s="76"/>
-      <c r="H128" s="76"/>
-      <c r="I128" s="76"/>
-      <c r="J128" s="76"/>
-      <c r="K128" s="76"/>
-      <c r="L128" s="76"/>
-      <c r="M128" s="76"/>
-      <c r="N128" s="76"/>
-      <c r="O128" s="76"/>
+      <c r="E128" s="73"/>
+      <c r="F128" s="73"/>
+      <c r="G128" s="73"/>
+      <c r="H128" s="73"/>
+      <c r="I128" s="73"/>
+      <c r="J128" s="73"/>
+      <c r="K128" s="73"/>
+      <c r="L128" s="73"/>
+      <c r="M128" s="73"/>
+      <c r="N128" s="73"/>
+      <c r="O128" s="73"/>
     </row>
     <row r="129" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A129" s="7" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="C129" s="50" t="str">
         <f>IF(OR($C$127="",$C$109="",$C$108="",$C$107=""),"",MIN($C$127*$C$109,$C$108/3*$C$107/100,300))</f>
         <v/>
       </c>
-      <c r="E129" s="76"/>
-      <c r="F129" s="76"/>
-      <c r="G129" s="76"/>
-      <c r="H129" s="76"/>
-      <c r="I129" s="76"/>
-      <c r="J129" s="76"/>
-      <c r="K129" s="76"/>
-      <c r="L129" s="76"/>
-      <c r="M129" s="76"/>
-      <c r="N129" s="76"/>
-      <c r="O129" s="76"/>
+      <c r="E129" s="73"/>
+      <c r="F129" s="73"/>
+      <c r="G129" s="73"/>
+      <c r="H129" s="73"/>
+      <c r="I129" s="73"/>
+      <c r="J129" s="73"/>
+      <c r="K129" s="73"/>
+      <c r="L129" s="73"/>
+      <c r="M129" s="73"/>
+      <c r="N129" s="73"/>
+      <c r="O129" s="73"/>
     </row>
     <row r="130" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A130" s="8" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="C130" s="41" t="str">
         <f>IF(OR($C$113="",$C$100=""),"",ABS($C$113-$C$100))</f>
         <v/>
       </c>
-      <c r="E130" s="76"/>
-      <c r="F130" s="76"/>
-      <c r="G130" s="76"/>
-      <c r="H130" s="76"/>
-      <c r="I130" s="76"/>
-      <c r="J130" s="76"/>
-      <c r="K130" s="76"/>
-      <c r="L130" s="76"/>
-      <c r="M130" s="76"/>
-      <c r="N130" s="76"/>
-      <c r="O130" s="76"/>
+      <c r="E130" s="73"/>
+      <c r="F130" s="73"/>
+      <c r="G130" s="73"/>
+      <c r="H130" s="73"/>
+      <c r="I130" s="73"/>
+      <c r="J130" s="73"/>
+      <c r="K130" s="73"/>
+      <c r="L130" s="73"/>
+      <c r="M130" s="73"/>
+      <c r="N130" s="73"/>
+      <c r="O130" s="73"/>
     </row>
     <row r="131" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A131" s="7" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="C131" s="51" t="str">
         <f>IF($C$130="","",IF($C$130&gt;0.15,"◀ DIVERGENCE — investigate","ok"))</f>
         <v/>
       </c>
-      <c r="E131" s="76"/>
-      <c r="F131" s="76"/>
-      <c r="G131" s="76"/>
-      <c r="H131" s="76"/>
-      <c r="I131" s="76"/>
-      <c r="J131" s="76"/>
-      <c r="K131" s="76"/>
-      <c r="L131" s="76"/>
-      <c r="M131" s="76"/>
-      <c r="N131" s="76"/>
-      <c r="O131" s="76"/>
+      <c r="E131" s="73"/>
+      <c r="F131" s="73"/>
+      <c r="G131" s="73"/>
+      <c r="H131" s="73"/>
+      <c r="I131" s="73"/>
+      <c r="J131" s="73"/>
+      <c r="K131" s="73"/>
+      <c r="L131" s="73"/>
+      <c r="M131" s="73"/>
+      <c r="N131" s="73"/>
+      <c r="O131" s="73"/>
     </row>
     <row r="132" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A132" s="8" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="C132" s="52" t="str">
         <f>IF(OR($C$111="",$C$107=""),"",ABS($C$111)*IF($C$111&gt;=0,$C$107,$C$105)/100)</f>
         <v/>
       </c>
-      <c r="E132" s="76"/>
-      <c r="F132" s="76"/>
-      <c r="G132" s="76"/>
-      <c r="H132" s="76"/>
-      <c r="I132" s="76"/>
-      <c r="J132" s="76"/>
-      <c r="K132" s="76"/>
-      <c r="L132" s="76"/>
-      <c r="M132" s="76"/>
-      <c r="N132" s="76"/>
-      <c r="O132" s="76"/>
+      <c r="E132" s="73"/>
+      <c r="F132" s="73"/>
+      <c r="G132" s="73"/>
+      <c r="H132" s="73"/>
+      <c r="I132" s="73"/>
+      <c r="J132" s="73"/>
+      <c r="K132" s="73"/>
+      <c r="L132" s="73"/>
+      <c r="M132" s="73"/>
+      <c r="N132" s="73"/>
+      <c r="O132" s="73"/>
     </row>
     <row r="133" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A133" s="7" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="C133" s="51" t="str">
         <f>IF($C$132="","",IF($C$132&gt;300,"◀ CAP BREACHED — do not add","within cap"))</f>
         <v/>
       </c>
-      <c r="E133" s="76"/>
-      <c r="F133" s="76"/>
-      <c r="G133" s="76"/>
-      <c r="H133" s="76"/>
-      <c r="I133" s="76"/>
-      <c r="J133" s="76"/>
-      <c r="K133" s="76"/>
-      <c r="L133" s="76"/>
-      <c r="M133" s="76"/>
-      <c r="N133" s="76"/>
-      <c r="O133" s="76"/>
+      <c r="E133" s="73"/>
+      <c r="F133" s="73"/>
+      <c r="G133" s="73"/>
+      <c r="H133" s="73"/>
+      <c r="I133" s="73"/>
+      <c r="J133" s="73"/>
+      <c r="K133" s="73"/>
+      <c r="L133" s="73"/>
+      <c r="M133" s="73"/>
+      <c r="N133" s="73"/>
+      <c r="O133" s="73"/>
     </row>
     <row r="134" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A134" s="7" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="C134" s="53" t="str">
         <f>IF($C$100="","— fill daily table + ENS members —",IF($C$132&gt;300,"HALT — over $300 cap, do not add",IF(AND(ISNUMBER($C$119),$C$119&gt;=3,ISNUMBER($C$108),$C$108&gt;0),"ACCUMULATE NO (edge ≥3¢)",IF(AND(ISNUMBER($C$118),$C$118&gt;=3,ISNUMBER($C$108),$C$108&gt;0),"ACCUMULATE YES (edge ≥3¢)",IF(AND(ISNUMBER($C$130),$C$130&gt;0.15),"DIVERGENCE — check Fcst_log: fresh model high ⇒ RIDE, no new high ⇒ FADE","PASSIVE / NO TRADE (small edge or wide spread)")))))</f>
         <v>— fill daily table + ENS members —</v>
       </c>
-      <c r="E134" s="76"/>
-      <c r="F134" s="76"/>
-      <c r="G134" s="76"/>
-      <c r="H134" s="76"/>
-      <c r="I134" s="76"/>
-      <c r="J134" s="76"/>
-      <c r="K134" s="76"/>
-      <c r="L134" s="76"/>
-      <c r="M134" s="76"/>
-      <c r="N134" s="76"/>
-      <c r="O134" s="76"/>
+      <c r="E134" s="73"/>
+      <c r="F134" s="73"/>
+      <c r="G134" s="73"/>
+      <c r="H134" s="73"/>
+      <c r="I134" s="73"/>
+      <c r="J134" s="73"/>
+      <c r="K134" s="73"/>
+      <c r="L134" s="73"/>
+      <c r="M134" s="73"/>
+      <c r="N134" s="73"/>
+      <c r="O134" s="73"/>
     </row>
     <row r="136" spans="1:15" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A136" s="80" t="s">
-        <v>162</v>
-      </c>
-      <c r="B136" s="80"/>
-      <c r="C136" s="80"/>
-      <c r="D136" s="80"/>
-      <c r="E136" s="80"/>
-      <c r="F136" s="80"/>
-      <c r="G136" s="80"/>
-      <c r="H136" s="80"/>
-      <c r="I136" s="80"/>
-      <c r="J136" s="80"/>
-      <c r="K136" s="80"/>
-      <c r="L136" s="80"/>
-      <c r="M136" s="80"/>
-      <c r="N136" s="80"/>
-      <c r="O136" s="80"/>
+      <c r="A136" s="77" t="s">
+        <v>159</v>
+      </c>
+      <c r="B136" s="77"/>
+      <c r="C136" s="77"/>
+      <c r="D136" s="77"/>
+      <c r="E136" s="77"/>
+      <c r="F136" s="77"/>
+      <c r="G136" s="77"/>
+      <c r="H136" s="77"/>
+      <c r="I136" s="77"/>
+      <c r="J136" s="77"/>
+      <c r="K136" s="77"/>
+      <c r="L136" s="77"/>
+      <c r="M136" s="77"/>
+      <c r="N136" s="77"/>
+      <c r="O136" s="77"/>
     </row>
     <row r="137" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A137" s="54" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="B137" s="54"/>
       <c r="D137" s="54" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="E137" s="54" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="F137" s="54" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
     </row>
     <row r="138" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A138" s="8" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="C138" s="38">
         <f>COUNT($M$49:$M$79)</f>
@@ -5613,12 +5554,12 @@
         <v>0</v>
       </c>
       <c r="G138" s="12" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
     </row>
     <row r="139" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A139" s="8" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="C139" s="37" t="str">
         <f>IFERROR(AVERAGE($M$49:$M$79),"")</f>
@@ -5633,12 +5574,12 @@
         <v/>
       </c>
       <c r="G139" s="12" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
     </row>
     <row r="140" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A140" s="8" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="C140" s="37" t="str">
         <f>IFERROR(AVERAGE($Q$49:$Q$79),"")</f>
@@ -5655,7 +5596,7 @@
     </row>
     <row r="141" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A141" s="8" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="C141" s="37" t="str">
         <f>IFERROR(SQRT(AVERAGE($R$49:$R$79)),"")</f>
@@ -5672,7 +5613,7 @@
     </row>
     <row r="142" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A142" s="8" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="C142" s="55" t="str">
         <f>IFERROR(AVERAGE($E$49:$E$79),"")</f>
@@ -5681,31 +5622,31 @@
     </row>
     <row r="143" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A143" s="8" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="C143" s="56" t="str">
         <f>IFERROR($C$142/$C$141,"")</f>
         <v/>
       </c>
       <c r="G143" s="12" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
     </row>
     <row r="144" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A144" s="8" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="C144" s="27" t="str">
         <f>IFERROR(SQRT(AVERAGE($W$49:$W$79)),"")</f>
         <v/>
       </c>
       <c r="G144" s="12" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
     </row>
     <row r="145" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A145" s="8" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="C145" s="57" t="str">
         <f>IFERROR(1-C141/$C$144,"")</f>
@@ -5722,19 +5663,19 @@
     </row>
     <row r="147" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A147" s="7" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="C147" s="39" t="str">
         <f>IF($C$83=0,"",IFERROR((IF(ISNUMBER(INDEX($M$49:$M$79,$C$83)),INDEX($M$49:$M$79,$C$83),0)+IF(AND($C$83&gt;=2,ISNUMBER(INDEX($M$49:$M$79,MAX(1,$C$83-1)))),INDEX($M$49:$M$79,MAX(1,$C$83-1)),0)+IF(AND($C$83&gt;=3,ISNUMBER(INDEX($M$49:$M$79,MAX(1,$C$83-2)))),INDEX($M$49:$M$79,MAX(1,$C$83-2)),0))/MAX(1,IF(ISNUMBER(INDEX($M$49:$M$79,$C$83)),1,0)+IF(AND($C$83&gt;=2,ISNUMBER(INDEX($M$49:$M$79,MAX(1,$C$83-1)))),1,0)+IF(AND($C$83&gt;=3,ISNUMBER(INDEX($M$49:$M$79,MAX(1,$C$83-2)))),1,0)),""))</f>
         <v/>
       </c>
       <c r="E147" s="12" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
     </row>
     <row r="148" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A148" s="7" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="C148" s="7" t="str">
         <f>IF($C$147="","",IF(ABS($C$147)&gt;0.05,IF($C$147&gt;0,"⚠ WARN — actuals running WARM (surge risk, YES value)","⚠ WARN — actuals running COLD"),"ok"))</f>
@@ -5743,19 +5684,19 @@
     </row>
     <row r="150" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A150" s="58" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
     </row>
     <row r="151" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A151" s="8" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="C151" s="57" t="str">
         <f>IFERROR((1/$C$140)/((1/$C$140)+(1/$D$140)),"")</f>
         <v/>
       </c>
       <c r="E151" s="8" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="F151" s="57" t="str">
         <f>IFERROR((1/$D$140)/((1/$C$140)+(1/$D$140)),"")</f>
@@ -5764,12 +5705,12 @@
     </row>
     <row r="153" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A153" s="28" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
     </row>
     <row r="154" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A154" s="12" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="C154" s="12" t="str">
         <f>IF($C$138&gt;=30,"—compute now—","insufficient n")</f>
@@ -5778,7 +5719,7 @@
     </row>
     <row r="155" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A155" s="12" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="C155" s="12" t="str">
         <f>IF($C$138&gt;=30,"—compute now—","insufficient n")</f>
@@ -5787,7 +5728,7 @@
     </row>
     <row r="156" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A156" s="12" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="C156" s="12" t="str">
         <f>IF($C$138&gt;=30,"—compute now—","insufficient n")</f>
@@ -5796,7 +5737,7 @@
     </row>
     <row r="157" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A157" s="12" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="C157" s="12" t="str">
         <f>IF($C$138&gt;=30,"—compute now—","insufficient n")</f>
@@ -5804,1149 +5745,465 @@
       </c>
     </row>
     <row r="160" spans="1:18" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A160" s="80" t="s">
-        <v>190</v>
-      </c>
-      <c r="B160" s="80"/>
-      <c r="C160" s="80"/>
-      <c r="D160" s="80"/>
-      <c r="E160" s="80"/>
-      <c r="F160" s="80"/>
-      <c r="G160" s="80"/>
-      <c r="H160" s="80"/>
-      <c r="I160" s="80"/>
-      <c r="J160" s="80"/>
-      <c r="K160" s="80"/>
-      <c r="L160" s="80"/>
-      <c r="M160" s="80"/>
-      <c r="N160" s="80"/>
-      <c r="O160" s="80"/>
-      <c r="P160" s="80"/>
-      <c r="Q160" s="80"/>
-      <c r="R160" s="80"/>
+      <c r="A160" s="77" t="s">
+        <v>187</v>
+      </c>
+      <c r="B160" s="77"/>
+      <c r="C160" s="77"/>
+      <c r="D160" s="77"/>
+      <c r="E160" s="77"/>
+      <c r="F160" s="77"/>
+      <c r="G160" s="77"/>
+      <c r="H160" s="77"/>
+      <c r="I160" s="77"/>
+      <c r="J160" s="77"/>
+      <c r="K160" s="77"/>
+      <c r="L160" s="77"/>
+      <c r="M160" s="77"/>
+      <c r="N160" s="77"/>
+      <c r="O160" s="77"/>
+      <c r="P160" s="77"/>
+      <c r="Q160" s="77"/>
+      <c r="R160" s="77"/>
     </row>
     <row r="161" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A161" s="12"/>
     </row>
     <row r="162" spans="1:18" ht="27" x14ac:dyDescent="0.2">
       <c r="A162" s="59" t="s">
+        <v>188</v>
+      </c>
+      <c r="B162" s="59" t="s">
+        <v>189</v>
+      </c>
+      <c r="C162" s="59" t="s">
+        <v>190</v>
+      </c>
+      <c r="D162" s="59" t="s">
         <v>191</v>
       </c>
-      <c r="B162" s="59" t="s">
+      <c r="E162" s="59" t="s">
         <v>192</v>
       </c>
-      <c r="C162" s="59" t="s">
+      <c r="F162" s="59" t="s">
         <v>193</v>
       </c>
-      <c r="D162" s="59" t="s">
+      <c r="G162" s="59" t="s">
         <v>194</v>
       </c>
-      <c r="E162" s="59" t="s">
+      <c r="H162" s="59" t="s">
         <v>195</v>
       </c>
-      <c r="F162" s="59" t="s">
+      <c r="I162" s="59" t="s">
         <v>196</v>
       </c>
-      <c r="G162" s="59" t="s">
+      <c r="J162" s="59" t="s">
         <v>197</v>
       </c>
-      <c r="H162" s="59" t="s">
+      <c r="K162" s="59" t="s">
         <v>198</v>
       </c>
-      <c r="I162" s="59" t="s">
+      <c r="L162" s="59" t="s">
         <v>199</v>
       </c>
-      <c r="J162" s="59" t="s">
+      <c r="M162" s="59" t="s">
         <v>200</v>
       </c>
-      <c r="K162" s="59" t="s">
+      <c r="N162" s="59" t="s">
         <v>201</v>
       </c>
-      <c r="L162" s="59" t="s">
+      <c r="O162" s="59" t="s">
         <v>202</v>
       </c>
-      <c r="M162" s="59" t="s">
+      <c r="P162" s="59" t="s">
         <v>203</v>
       </c>
-      <c r="N162" s="59" t="s">
+      <c r="Q162" s="59" t="s">
         <v>204</v>
       </c>
-      <c r="O162" s="59" t="s">
+      <c r="R162" s="59" t="s">
         <v>205</v>
       </c>
-      <c r="P162" s="59" t="s">
-        <v>206</v>
-      </c>
-      <c r="Q162" s="59" t="s">
-        <v>207</v>
-      </c>
-      <c r="R162" s="59" t="s">
-        <v>208</v>
-      </c>
     </row>
     <row r="163" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A163" s="60">
-        <v>1990</v>
-      </c>
-      <c r="B163" s="61">
-        <v>-0.16470000000000001</v>
-      </c>
-      <c r="C163" s="62">
-        <v>0.33</v>
-      </c>
-      <c r="D163" s="61">
-        <v>-7.6499999999999999E-2</v>
-      </c>
-      <c r="E163" s="61">
-        <v>-7.6499999999999999E-2</v>
-      </c>
-      <c r="F163" s="61">
-        <v>-0.23699999999999999</v>
-      </c>
-      <c r="G163" s="61">
-        <v>-7.6499999999999999E-2</v>
-      </c>
-      <c r="H163" s="61">
-        <v>-0.224</v>
-      </c>
-      <c r="I163" s="61">
-        <v>-7.6499999999999999E-2</v>
-      </c>
-      <c r="J163" s="61">
-        <v>-0.23369999999999999</v>
-      </c>
-      <c r="K163" s="61">
-        <v>-7.6499999999999999E-2</v>
-      </c>
-      <c r="L163" s="61">
-        <v>-0.1789</v>
-      </c>
-      <c r="M163" s="61">
-        <v>-7.6499999999999999E-2</v>
-      </c>
-      <c r="N163" s="61">
-        <v>-0.17519999999999999</v>
-      </c>
-      <c r="O163" s="61">
-        <v>-7.6499999999999999E-2</v>
-      </c>
-      <c r="P163" s="61">
-        <v>-0.1701</v>
-      </c>
-      <c r="Q163" s="61">
-        <v>-7.6499999999999999E-2</v>
-      </c>
-      <c r="R163" s="61">
-        <v>-0.16470000000000001</v>
-      </c>
+      <c r="A163" s="60"/>
+      <c r="B163" s="61"/>
+      <c r="C163" s="62"/>
+      <c r="D163" s="61"/>
+      <c r="E163" s="61"/>
+      <c r="F163" s="61"/>
+      <c r="G163" s="61"/>
+      <c r="H163" s="61"/>
+      <c r="I163" s="61"/>
+      <c r="J163" s="61"/>
+      <c r="K163" s="61"/>
+      <c r="L163" s="61"/>
+      <c r="M163" s="61"/>
+      <c r="N163" s="61"/>
+      <c r="O163" s="61"/>
+      <c r="P163" s="61"/>
+      <c r="Q163" s="61"/>
+      <c r="R163" s="61"/>
     </row>
     <row r="164" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A164" s="60">
-        <v>1991</v>
-      </c>
-      <c r="B164" s="61">
-        <v>-0.13850000000000001</v>
-      </c>
-      <c r="C164" s="62">
-        <v>0.4</v>
-      </c>
-      <c r="D164" s="61">
-        <v>-4.6199999999999998E-2</v>
-      </c>
-      <c r="E164" s="61">
-        <v>-4.6199999999999998E-2</v>
-      </c>
-      <c r="F164" s="61">
-        <v>2.1499999999999998E-2</v>
-      </c>
-      <c r="G164" s="61">
-        <v>-4.6199999999999998E-2</v>
-      </c>
-      <c r="H164" s="61">
-        <v>-1.72E-2</v>
-      </c>
-      <c r="I164" s="61">
-        <v>-4.6199999999999998E-2</v>
-      </c>
-      <c r="J164" s="61">
-        <v>-9.4500000000000001E-2</v>
-      </c>
-      <c r="K164" s="61">
-        <v>-4.6199999999999998E-2</v>
-      </c>
-      <c r="L164" s="61">
-        <v>-0.14180000000000001</v>
-      </c>
-      <c r="M164" s="61">
-        <v>-4.6199999999999998E-2</v>
-      </c>
-      <c r="N164" s="61">
-        <v>-0.1321</v>
-      </c>
-      <c r="O164" s="61">
-        <v>-4.6199999999999998E-2</v>
-      </c>
-      <c r="P164" s="61">
-        <v>-0.13469999999999999</v>
-      </c>
-      <c r="Q164" s="61">
-        <v>-4.6199999999999998E-2</v>
-      </c>
-      <c r="R164" s="61">
-        <v>-0.13850000000000001</v>
-      </c>
+      <c r="A164" s="60"/>
+      <c r="B164" s="61"/>
+      <c r="C164" s="62"/>
+      <c r="D164" s="61"/>
+      <c r="E164" s="61"/>
+      <c r="F164" s="61"/>
+      <c r="G164" s="61"/>
+      <c r="H164" s="61"/>
+      <c r="I164" s="61"/>
+      <c r="J164" s="61"/>
+      <c r="K164" s="61"/>
+      <c r="L164" s="61"/>
+      <c r="M164" s="61"/>
+      <c r="N164" s="61"/>
+      <c r="O164" s="61"/>
+      <c r="P164" s="61"/>
+      <c r="Q164" s="61"/>
+      <c r="R164" s="61"/>
     </row>
     <row r="165" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A165" s="60">
-        <v>1992</v>
-      </c>
-      <c r="B165" s="61">
-        <v>-0.48699999999999999</v>
-      </c>
-      <c r="C165" s="62">
-        <v>0.12</v>
-      </c>
-      <c r="D165" s="61">
-        <v>-0.46010000000000001</v>
-      </c>
-      <c r="E165" s="61">
-        <v>-0.46010000000000001</v>
-      </c>
-      <c r="F165" s="61">
-        <v>-0.67700000000000005</v>
-      </c>
-      <c r="G165" s="61">
-        <v>-0.46010000000000001</v>
-      </c>
-      <c r="H165" s="61">
-        <v>-0.66420000000000001</v>
-      </c>
-      <c r="I165" s="61">
-        <v>-0.46010000000000001</v>
-      </c>
-      <c r="J165" s="61">
-        <v>-0.55769999999999997</v>
-      </c>
-      <c r="K165" s="61">
-        <v>-0.46010000000000001</v>
-      </c>
-      <c r="L165" s="61">
-        <v>-0.50749999999999995</v>
-      </c>
-      <c r="M165" s="61">
-        <v>-0.46010000000000001</v>
-      </c>
-      <c r="N165" s="61">
-        <v>-0.48220000000000002</v>
-      </c>
-      <c r="O165" s="61">
-        <v>-0.46010000000000001</v>
-      </c>
-      <c r="P165" s="61">
-        <v>-0.4894</v>
-      </c>
-      <c r="Q165" s="61">
-        <v>-0.46010000000000001</v>
-      </c>
-      <c r="R165" s="61">
-        <v>-0.48699999999999999</v>
-      </c>
+      <c r="A165" s="60"/>
+      <c r="B165" s="61"/>
+      <c r="C165" s="62"/>
+      <c r="D165" s="61"/>
+      <c r="E165" s="61"/>
+      <c r="F165" s="61"/>
+      <c r="G165" s="61"/>
+      <c r="H165" s="61"/>
+      <c r="I165" s="61"/>
+      <c r="J165" s="61"/>
+      <c r="K165" s="61"/>
+      <c r="L165" s="61"/>
+      <c r="M165" s="61"/>
+      <c r="N165" s="61"/>
+      <c r="O165" s="61"/>
+      <c r="P165" s="61"/>
+      <c r="Q165" s="61"/>
+      <c r="R165" s="61"/>
     </row>
     <row r="166" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A166" s="60">
-        <v>1993</v>
-      </c>
-      <c r="B166" s="61">
-        <v>-0.38329999999999997</v>
-      </c>
-      <c r="C166" s="62">
-        <v>0.19</v>
-      </c>
-      <c r="D166" s="61">
-        <v>-0.34889999999999999</v>
-      </c>
-      <c r="E166" s="61">
-        <v>-0.34889999999999999</v>
-      </c>
-      <c r="F166" s="61">
-        <v>-0.34300000000000003</v>
-      </c>
-      <c r="G166" s="61">
-        <v>-0.34889999999999999</v>
-      </c>
-      <c r="H166" s="61">
-        <v>-0.32219999999999999</v>
-      </c>
-      <c r="I166" s="61">
-        <v>-0.34889999999999999</v>
-      </c>
-      <c r="J166" s="61">
-        <v>-0.32350000000000001</v>
-      </c>
-      <c r="K166" s="61">
-        <v>-0.34889999999999999</v>
-      </c>
-      <c r="L166" s="61">
-        <v>-0.32950000000000002</v>
-      </c>
-      <c r="M166" s="61">
-        <v>-0.34889999999999999</v>
-      </c>
-      <c r="N166" s="61">
-        <v>-0.3301</v>
-      </c>
-      <c r="O166" s="61">
-        <v>-0.34889999999999999</v>
-      </c>
-      <c r="P166" s="61">
-        <v>-0.36</v>
-      </c>
-      <c r="Q166" s="61">
-        <v>-0.34889999999999999</v>
-      </c>
-      <c r="R166" s="61">
-        <v>-0.38329999999999997</v>
-      </c>
+      <c r="A166" s="60"/>
+      <c r="B166" s="61"/>
+      <c r="C166" s="62"/>
+      <c r="D166" s="61"/>
+      <c r="E166" s="61"/>
+      <c r="F166" s="61"/>
+      <c r="G166" s="61"/>
+      <c r="H166" s="61"/>
+      <c r="I166" s="61"/>
+      <c r="J166" s="61"/>
+      <c r="K166" s="61"/>
+      <c r="L166" s="61"/>
+      <c r="M166" s="61"/>
+      <c r="N166" s="61"/>
+      <c r="O166" s="61"/>
+      <c r="P166" s="61"/>
+      <c r="Q166" s="61"/>
+      <c r="R166" s="61"/>
     </row>
     <row r="167" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A167" s="60">
-        <v>1994</v>
-      </c>
-      <c r="B167" s="61">
-        <v>-0.3831</v>
-      </c>
-      <c r="C167" s="62">
-        <v>0.27</v>
-      </c>
-      <c r="D167" s="61">
-        <v>-0.27360000000000001</v>
-      </c>
-      <c r="E167" s="61">
-        <v>-0.27360000000000001</v>
-      </c>
-      <c r="F167" s="61">
-        <v>-0.41049999999999998</v>
-      </c>
-      <c r="G167" s="61">
-        <v>-0.27360000000000001</v>
-      </c>
-      <c r="H167" s="61">
-        <v>-0.45639999999999997</v>
-      </c>
-      <c r="I167" s="61">
-        <v>-0.27360000000000001</v>
-      </c>
-      <c r="J167" s="61">
-        <v>-0.4556</v>
-      </c>
-      <c r="K167" s="61">
-        <v>-0.27360000000000001</v>
-      </c>
-      <c r="L167" s="61">
-        <v>-0.41710000000000003</v>
-      </c>
-      <c r="M167" s="61">
-        <v>-0.27360000000000001</v>
-      </c>
-      <c r="N167" s="61">
-        <v>-0.39650000000000002</v>
-      </c>
-      <c r="O167" s="61">
-        <v>-0.27360000000000001</v>
-      </c>
-      <c r="P167" s="61">
-        <v>-0.40060000000000001</v>
-      </c>
-      <c r="Q167" s="61">
-        <v>-0.27360000000000001</v>
-      </c>
-      <c r="R167" s="61">
-        <v>-0.3831</v>
-      </c>
+      <c r="A167" s="60"/>
+      <c r="B167" s="61"/>
+      <c r="C167" s="62"/>
+      <c r="D167" s="61"/>
+      <c r="E167" s="61"/>
+      <c r="F167" s="61"/>
+      <c r="G167" s="61"/>
+      <c r="H167" s="61"/>
+      <c r="I167" s="61"/>
+      <c r="J167" s="61"/>
+      <c r="K167" s="61"/>
+      <c r="L167" s="61"/>
+      <c r="M167" s="61"/>
+      <c r="N167" s="61"/>
+      <c r="O167" s="61"/>
+      <c r="P167" s="61"/>
+      <c r="Q167" s="61"/>
+      <c r="R167" s="61"/>
     </row>
     <row r="168" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A168" s="60">
-        <v>1995</v>
-      </c>
-      <c r="B168" s="61">
-        <v>-0.10580000000000001</v>
-      </c>
-      <c r="C168" s="62">
-        <v>0.51</v>
-      </c>
-      <c r="D168" s="61">
-        <v>-0.1028</v>
-      </c>
-      <c r="E168" s="61">
-        <v>-0.1028</v>
-      </c>
-      <c r="F168" s="61">
-        <v>-1.9E-2</v>
-      </c>
-      <c r="G168" s="61">
-        <v>-0.1028</v>
-      </c>
-      <c r="H168" s="61">
-        <v>1.4E-3</v>
-      </c>
-      <c r="I168" s="61">
-        <v>-0.1028</v>
-      </c>
-      <c r="J168" s="61">
-        <v>-0.1084</v>
-      </c>
-      <c r="K168" s="61">
-        <v>-0.1028</v>
-      </c>
-      <c r="L168" s="61">
-        <v>-0.13489999999999999</v>
-      </c>
-      <c r="M168" s="61">
-        <v>-0.1028</v>
-      </c>
-      <c r="N168" s="61">
-        <v>-0.1348</v>
-      </c>
-      <c r="O168" s="61">
-        <v>-0.1028</v>
-      </c>
-      <c r="P168" s="61">
-        <v>-0.1227</v>
-      </c>
-      <c r="Q168" s="61">
-        <v>-0.1028</v>
-      </c>
-      <c r="R168" s="61">
-        <v>-0.10580000000000001</v>
-      </c>
+      <c r="A168" s="60"/>
+      <c r="B168" s="61"/>
+      <c r="C168" s="62"/>
+      <c r="D168" s="61"/>
+      <c r="E168" s="61"/>
+      <c r="F168" s="61"/>
+      <c r="G168" s="61"/>
+      <c r="H168" s="61"/>
+      <c r="I168" s="61"/>
+      <c r="J168" s="61"/>
+      <c r="K168" s="61"/>
+      <c r="L168" s="61"/>
+      <c r="M168" s="61"/>
+      <c r="N168" s="61"/>
+      <c r="O168" s="61"/>
+      <c r="P168" s="61"/>
+      <c r="Q168" s="61"/>
+      <c r="R168" s="61"/>
     </row>
     <row r="169" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A169" s="60">
-        <v>1996</v>
-      </c>
-      <c r="B169" s="61">
-        <v>-0.1104</v>
-      </c>
-      <c r="C169" s="62">
-        <v>0.43</v>
-      </c>
-      <c r="D169" s="61">
-        <v>-0.20530000000000001</v>
-      </c>
-      <c r="E169" s="61">
-        <v>-0.20530000000000001</v>
-      </c>
-      <c r="F169" s="61">
-        <v>3.1E-2</v>
-      </c>
-      <c r="G169" s="61">
-        <v>-0.20530000000000001</v>
-      </c>
-      <c r="H169" s="61">
-        <v>0.01</v>
-      </c>
-      <c r="I169" s="61">
-        <v>-0.20530000000000001</v>
-      </c>
-      <c r="J169" s="61">
-        <v>-9.11E-2</v>
-      </c>
-      <c r="K169" s="61">
-        <v>-0.20530000000000001</v>
-      </c>
-      <c r="L169" s="61">
-        <v>-0.10730000000000001</v>
-      </c>
-      <c r="M169" s="61">
-        <v>-0.20530000000000001</v>
-      </c>
-      <c r="N169" s="61">
-        <v>-0.15179999999999999</v>
-      </c>
-      <c r="O169" s="61">
-        <v>-0.20530000000000001</v>
-      </c>
-      <c r="P169" s="61">
-        <v>-0.14319999999999999</v>
-      </c>
-      <c r="Q169" s="61">
-        <v>-0.20530000000000001</v>
-      </c>
-      <c r="R169" s="61">
-        <v>-0.1104</v>
-      </c>
+      <c r="A169" s="60"/>
+      <c r="B169" s="61"/>
+      <c r="C169" s="62"/>
+      <c r="D169" s="61"/>
+      <c r="E169" s="61"/>
+      <c r="F169" s="61"/>
+      <c r="G169" s="61"/>
+      <c r="H169" s="61"/>
+      <c r="I169" s="61"/>
+      <c r="J169" s="61"/>
+      <c r="K169" s="61"/>
+      <c r="L169" s="61"/>
+      <c r="M169" s="61"/>
+      <c r="N169" s="61"/>
+      <c r="O169" s="61"/>
+      <c r="P169" s="61"/>
+      <c r="Q169" s="61"/>
+      <c r="R169" s="61"/>
     </row>
     <row r="170" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A170" s="60">
-        <v>1997</v>
-      </c>
-      <c r="B170" s="61">
-        <v>-0.13289999999999999</v>
-      </c>
-      <c r="C170" s="62">
-        <v>0.47</v>
-      </c>
-      <c r="D170" s="61">
-        <v>-0.17100000000000001</v>
-      </c>
-      <c r="E170" s="61">
-        <v>-0.17100000000000001</v>
-      </c>
-      <c r="F170" s="61">
-        <v>-7.3499999999999996E-2</v>
-      </c>
-      <c r="G170" s="61">
-        <v>-0.17100000000000001</v>
-      </c>
-      <c r="H170" s="61">
-        <v>-0.10440000000000001</v>
-      </c>
-      <c r="I170" s="61">
-        <v>-0.17100000000000001</v>
-      </c>
-      <c r="J170" s="61">
-        <v>-0.17610000000000001</v>
-      </c>
-      <c r="K170" s="61">
-        <v>-0.17100000000000001</v>
-      </c>
-      <c r="L170" s="61">
-        <v>-0.15509999999999999</v>
-      </c>
-      <c r="M170" s="61">
-        <v>-0.17100000000000001</v>
-      </c>
-      <c r="N170" s="61">
-        <v>-0.14660000000000001</v>
-      </c>
-      <c r="O170" s="61">
-        <v>-0.17100000000000001</v>
-      </c>
-      <c r="P170" s="61">
-        <v>-0.13159999999999999</v>
-      </c>
-      <c r="Q170" s="61">
-        <v>-0.17100000000000001</v>
-      </c>
-      <c r="R170" s="61">
-        <v>-0.13289999999999999</v>
-      </c>
+      <c r="A170" s="60"/>
+      <c r="B170" s="61"/>
+      <c r="C170" s="62"/>
+      <c r="D170" s="61"/>
+      <c r="E170" s="61"/>
+      <c r="F170" s="61"/>
+      <c r="G170" s="61"/>
+      <c r="H170" s="61"/>
+      <c r="I170" s="61"/>
+      <c r="J170" s="61"/>
+      <c r="K170" s="61"/>
+      <c r="L170" s="61"/>
+      <c r="M170" s="61"/>
+      <c r="N170" s="61"/>
+      <c r="O170" s="61"/>
+      <c r="P170" s="61"/>
+      <c r="Q170" s="61"/>
+      <c r="R170" s="61"/>
     </row>
     <row r="171" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A171" s="60">
-        <v>1998</v>
-      </c>
-      <c r="B171" s="61">
-        <v>0.1426</v>
-      </c>
-      <c r="C171" s="62">
-        <v>0.71</v>
-      </c>
-      <c r="D171" s="61">
-        <v>0.12280000000000001</v>
-      </c>
-      <c r="E171" s="61">
-        <v>0.12280000000000001</v>
-      </c>
-      <c r="F171" s="61">
-        <v>0.13850000000000001</v>
-      </c>
-      <c r="G171" s="61">
-        <v>0.12280000000000001</v>
-      </c>
-      <c r="H171" s="61">
-        <v>0.21659999999999999</v>
-      </c>
-      <c r="I171" s="61">
-        <v>0.12280000000000001</v>
-      </c>
-      <c r="J171" s="61">
-        <v>0.27229999999999999</v>
-      </c>
-      <c r="K171" s="61">
-        <v>0.12280000000000001</v>
-      </c>
-      <c r="L171" s="61">
-        <v>0.21390000000000001</v>
-      </c>
-      <c r="M171" s="61">
-        <v>0.12280000000000001</v>
-      </c>
-      <c r="N171" s="61">
-        <v>0.1699</v>
-      </c>
-      <c r="O171" s="61">
-        <v>0.12280000000000001</v>
-      </c>
-      <c r="P171" s="61">
-        <v>0.16600000000000001</v>
-      </c>
-      <c r="Q171" s="61">
-        <v>0.12280000000000001</v>
-      </c>
-      <c r="R171" s="61">
-        <v>0.1426</v>
-      </c>
+      <c r="A171" s="60"/>
+      <c r="B171" s="61"/>
+      <c r="C171" s="62"/>
+      <c r="D171" s="61"/>
+      <c r="E171" s="61"/>
+      <c r="F171" s="61"/>
+      <c r="G171" s="61"/>
+      <c r="H171" s="61"/>
+      <c r="I171" s="61"/>
+      <c r="J171" s="61"/>
+      <c r="K171" s="61"/>
+      <c r="L171" s="61"/>
+      <c r="M171" s="61"/>
+      <c r="N171" s="61"/>
+      <c r="O171" s="61"/>
+      <c r="P171" s="61"/>
+      <c r="Q171" s="61"/>
+      <c r="R171" s="61"/>
     </row>
     <row r="172" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A172" s="60">
-        <v>1999</v>
-      </c>
-      <c r="B172" s="61">
-        <v>-0.2364</v>
-      </c>
-      <c r="C172" s="62">
-        <v>0.38</v>
-      </c>
-      <c r="D172" s="61">
-        <v>-0.20100000000000001</v>
-      </c>
-      <c r="E172" s="61">
-        <v>-0.20100000000000001</v>
-      </c>
-      <c r="F172" s="61">
-        <v>-0.1865</v>
-      </c>
-      <c r="G172" s="61">
-        <v>-0.20100000000000001</v>
-      </c>
-      <c r="H172" s="61">
-        <v>-0.16239999999999999</v>
-      </c>
-      <c r="I172" s="61">
-        <v>-0.20100000000000001</v>
-      </c>
-      <c r="J172" s="61">
-        <v>-0.20930000000000001</v>
-      </c>
-      <c r="K172" s="61">
-        <v>-0.20100000000000001</v>
-      </c>
-      <c r="L172" s="61">
-        <v>-0.23549999999999999</v>
-      </c>
-      <c r="M172" s="61">
-        <v>-0.20100000000000001</v>
-      </c>
-      <c r="N172" s="61">
-        <v>-0.2382</v>
-      </c>
-      <c r="O172" s="61">
-        <v>-0.20100000000000001</v>
-      </c>
-      <c r="P172" s="61">
-        <v>-0.23749999999999999</v>
-      </c>
-      <c r="Q172" s="61">
-        <v>-0.20100000000000001</v>
-      </c>
-      <c r="R172" s="61">
-        <v>-0.2364</v>
-      </c>
+      <c r="A172" s="60"/>
+      <c r="B172" s="61"/>
+      <c r="C172" s="62"/>
+      <c r="D172" s="61"/>
+      <c r="E172" s="61"/>
+      <c r="F172" s="61"/>
+      <c r="G172" s="61"/>
+      <c r="H172" s="61"/>
+      <c r="I172" s="61"/>
+      <c r="J172" s="61"/>
+      <c r="K172" s="61"/>
+      <c r="L172" s="61"/>
+      <c r="M172" s="61"/>
+      <c r="N172" s="61"/>
+      <c r="O172" s="61"/>
+      <c r="P172" s="61"/>
+      <c r="Q172" s="61"/>
+      <c r="R172" s="61"/>
     </row>
     <row r="173" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A173" s="60">
-        <v>2000</v>
-      </c>
-      <c r="B173" s="61">
-        <v>-0.17380000000000001</v>
-      </c>
-      <c r="C173" s="62">
-        <v>0.44</v>
-      </c>
-      <c r="D173" s="61">
-        <v>-0.23669999999999999</v>
-      </c>
-      <c r="E173" s="61">
-        <v>-0.23669999999999999</v>
-      </c>
-      <c r="F173" s="61">
-        <v>-5.2999999999999999E-2</v>
-      </c>
-      <c r="G173" s="61">
-        <v>-0.23669999999999999</v>
-      </c>
-      <c r="H173" s="61">
-        <v>-0.15659999999999999</v>
-      </c>
-      <c r="I173" s="61">
-        <v>-0.23669999999999999</v>
-      </c>
-      <c r="J173" s="61">
-        <v>-0.18770000000000001</v>
-      </c>
-      <c r="K173" s="61">
-        <v>-0.23669999999999999</v>
-      </c>
-      <c r="L173" s="61">
-        <v>-0.2301</v>
-      </c>
-      <c r="M173" s="61">
-        <v>-0.23669999999999999</v>
-      </c>
-      <c r="N173" s="61">
-        <v>-0.23980000000000001</v>
-      </c>
-      <c r="O173" s="61">
-        <v>-0.23669999999999999</v>
-      </c>
-      <c r="P173" s="61">
-        <v>-0.21379999999999999</v>
-      </c>
-      <c r="Q173" s="61">
-        <v>-0.23669999999999999</v>
-      </c>
-      <c r="R173" s="61">
-        <v>-0.17380000000000001</v>
-      </c>
+      <c r="A173" s="60"/>
+      <c r="B173" s="61"/>
+      <c r="C173" s="62"/>
+      <c r="D173" s="61"/>
+      <c r="E173" s="61"/>
+      <c r="F173" s="61"/>
+      <c r="G173" s="61"/>
+      <c r="H173" s="61"/>
+      <c r="I173" s="61"/>
+      <c r="J173" s="61"/>
+      <c r="K173" s="61"/>
+      <c r="L173" s="61"/>
+      <c r="M173" s="61"/>
+      <c r="N173" s="61"/>
+      <c r="O173" s="61"/>
+      <c r="P173" s="61"/>
+      <c r="Q173" s="61"/>
+      <c r="R173" s="61"/>
     </row>
     <row r="174" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A174" s="60">
-        <v>2001</v>
-      </c>
-      <c r="B174" s="61">
-        <v>-4.9799999999999997E-2</v>
-      </c>
-      <c r="C174" s="62">
-        <v>0.52</v>
-      </c>
-      <c r="D174" s="61">
-        <v>-1.9400000000000001E-2</v>
-      </c>
-      <c r="E174" s="61">
-        <v>-1.9400000000000001E-2</v>
-      </c>
-      <c r="F174" s="61">
-        <v>1.4E-2</v>
-      </c>
-      <c r="G174" s="61">
-        <v>-1.9400000000000001E-2</v>
-      </c>
-      <c r="H174" s="61">
-        <v>2.92E-2</v>
-      </c>
-      <c r="I174" s="61">
-        <v>-1.9400000000000001E-2</v>
-      </c>
-      <c r="J174" s="61">
-        <v>-1.2699999999999999E-2</v>
-      </c>
-      <c r="K174" s="61">
-        <v>-1.9400000000000001E-2</v>
-      </c>
-      <c r="L174" s="61">
-        <v>-4.9099999999999998E-2</v>
-      </c>
-      <c r="M174" s="61">
-        <v>-1.9400000000000001E-2</v>
-      </c>
-      <c r="N174" s="61">
-        <v>-6.0299999999999999E-2</v>
-      </c>
-      <c r="O174" s="61">
-        <v>-1.9400000000000001E-2</v>
-      </c>
-      <c r="P174" s="61">
-        <v>-4.2299999999999997E-2</v>
-      </c>
-      <c r="Q174" s="61">
-        <v>-1.9400000000000001E-2</v>
-      </c>
-      <c r="R174" s="61">
-        <v>-4.9799999999999997E-2</v>
-      </c>
+      <c r="A174" s="60"/>
+      <c r="B174" s="61"/>
+      <c r="C174" s="62"/>
+      <c r="D174" s="61"/>
+      <c r="E174" s="61"/>
+      <c r="F174" s="61"/>
+      <c r="G174" s="61"/>
+      <c r="H174" s="61"/>
+      <c r="I174" s="61"/>
+      <c r="J174" s="61"/>
+      <c r="K174" s="61"/>
+      <c r="L174" s="61"/>
+      <c r="M174" s="61"/>
+      <c r="N174" s="61"/>
+      <c r="O174" s="61"/>
+      <c r="P174" s="61"/>
+      <c r="Q174" s="61"/>
+      <c r="R174" s="61"/>
     </row>
     <row r="175" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A175" s="60">
-        <v>2002</v>
-      </c>
-      <c r="B175" s="61">
-        <v>-4.5400000000000003E-2</v>
-      </c>
-      <c r="C175" s="62">
-        <v>0.55000000000000004</v>
-      </c>
-      <c r="D175" s="61">
-        <v>3.49E-2</v>
-      </c>
-      <c r="E175" s="61">
-        <v>3.49E-2</v>
-      </c>
-      <c r="F175" s="61">
-        <v>-0.10199999999999999</v>
-      </c>
-      <c r="G175" s="61">
-        <v>3.49E-2</v>
-      </c>
-      <c r="H175" s="61">
-        <v>-0.1386</v>
-      </c>
-      <c r="I175" s="61">
-        <v>3.49E-2</v>
-      </c>
-      <c r="J175" s="61">
-        <v>-0.1221</v>
-      </c>
-      <c r="K175" s="61">
-        <v>3.49E-2</v>
-      </c>
-      <c r="L175" s="61">
-        <v>-5.6300000000000003E-2</v>
-      </c>
-      <c r="M175" s="61">
-        <v>3.49E-2</v>
-      </c>
-      <c r="N175" s="61">
-        <v>-3.0800000000000001E-2</v>
-      </c>
-      <c r="O175" s="61">
-        <v>3.49E-2</v>
-      </c>
-      <c r="P175" s="61">
-        <v>-3.1199999999999999E-2</v>
-      </c>
-      <c r="Q175" s="61">
-        <v>3.49E-2</v>
-      </c>
-      <c r="R175" s="61">
-        <v>-4.5400000000000003E-2</v>
-      </c>
+      <c r="A175" s="60"/>
+      <c r="B175" s="61"/>
+      <c r="C175" s="62"/>
+      <c r="D175" s="61"/>
+      <c r="E175" s="61"/>
+      <c r="F175" s="61"/>
+      <c r="G175" s="61"/>
+      <c r="H175" s="61"/>
+      <c r="I175" s="61"/>
+      <c r="J175" s="61"/>
+      <c r="K175" s="61"/>
+      <c r="L175" s="61"/>
+      <c r="M175" s="61"/>
+      <c r="N175" s="61"/>
+      <c r="O175" s="61"/>
+      <c r="P175" s="61"/>
+      <c r="Q175" s="61"/>
+      <c r="R175" s="61"/>
     </row>
     <row r="176" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A176" s="60">
-        <v>2003</v>
-      </c>
-      <c r="B176" s="61">
-        <v>4.7E-2</v>
-      </c>
-      <c r="C176" s="62">
-        <v>0.62</v>
-      </c>
-      <c r="D176" s="61">
-        <v>-4.6199999999999998E-2</v>
-      </c>
-      <c r="E176" s="61">
-        <v>-4.6199999999999998E-2</v>
-      </c>
-      <c r="F176" s="61">
-        <v>5.0000000000000001E-3</v>
-      </c>
-      <c r="G176" s="61">
-        <v>-4.6199999999999998E-2</v>
-      </c>
-      <c r="H176" s="61">
-        <v>4.4600000000000001E-2</v>
-      </c>
-      <c r="I176" s="61">
-        <v>-4.6199999999999998E-2</v>
-      </c>
-      <c r="J176" s="61">
-        <v>2.01E-2</v>
-      </c>
-      <c r="K176" s="61">
-        <v>-4.6199999999999998E-2</v>
-      </c>
-      <c r="L176" s="61">
-        <v>7.7000000000000002E-3</v>
-      </c>
-      <c r="M176" s="61">
-        <v>-4.6199999999999998E-2</v>
-      </c>
-      <c r="N176" s="61">
-        <v>9.4000000000000004E-3</v>
-      </c>
-      <c r="O176" s="61">
-        <v>-4.6199999999999998E-2</v>
-      </c>
-      <c r="P176" s="61">
-        <v>3.3300000000000003E-2</v>
-      </c>
-      <c r="Q176" s="61">
-        <v>-4.6199999999999998E-2</v>
-      </c>
-      <c r="R176" s="61">
-        <v>4.7E-2</v>
-      </c>
+      <c r="A176" s="60"/>
+      <c r="B176" s="61"/>
+      <c r="C176" s="62"/>
+      <c r="D176" s="61"/>
+      <c r="E176" s="61"/>
+      <c r="F176" s="61"/>
+      <c r="G176" s="61"/>
+      <c r="H176" s="61"/>
+      <c r="I176" s="61"/>
+      <c r="J176" s="61"/>
+      <c r="K176" s="61"/>
+      <c r="L176" s="61"/>
+      <c r="M176" s="61"/>
+      <c r="N176" s="61"/>
+      <c r="O176" s="61"/>
+      <c r="P176" s="61"/>
+      <c r="Q176" s="61"/>
+      <c r="R176" s="61"/>
     </row>
     <row r="177" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A177" s="60">
-        <v>2004</v>
-      </c>
-      <c r="B177" s="61">
-        <v>-0.1605</v>
-      </c>
-      <c r="C177" s="62">
-        <v>0.48</v>
-      </c>
-      <c r="D177" s="61">
-        <v>-0.27479999999999999</v>
-      </c>
-      <c r="E177" s="61">
-        <v>-0.27479999999999999</v>
-      </c>
-      <c r="F177" s="61">
-        <v>-0.26350000000000001</v>
-      </c>
-      <c r="G177" s="61">
-        <v>-0.27479999999999999</v>
-      </c>
-      <c r="H177" s="61">
-        <v>-0.254</v>
-      </c>
-      <c r="I177" s="61">
-        <v>-0.27479999999999999</v>
-      </c>
-      <c r="J177" s="61">
-        <v>-0.2571</v>
-      </c>
-      <c r="K177" s="61">
-        <v>-0.27479999999999999</v>
-      </c>
-      <c r="L177" s="61">
-        <v>-0.1981</v>
-      </c>
-      <c r="M177" s="61">
-        <v>-0.27479999999999999</v>
-      </c>
-      <c r="N177" s="61">
-        <v>-0.1676</v>
-      </c>
-      <c r="O177" s="61">
-        <v>-0.27479999999999999</v>
-      </c>
-      <c r="P177" s="61">
-        <v>-0.17519999999999999</v>
-      </c>
-      <c r="Q177" s="61">
-        <v>-0.27479999999999999</v>
-      </c>
-      <c r="R177" s="61">
-        <v>-0.1605</v>
-      </c>
+      <c r="A177" s="60"/>
+      <c r="B177" s="61"/>
+      <c r="C177" s="62"/>
+      <c r="D177" s="61"/>
+      <c r="E177" s="61"/>
+      <c r="F177" s="61"/>
+      <c r="G177" s="61"/>
+      <c r="H177" s="61"/>
+      <c r="I177" s="61"/>
+      <c r="J177" s="61"/>
+      <c r="K177" s="61"/>
+      <c r="L177" s="61"/>
+      <c r="M177" s="61"/>
+      <c r="N177" s="61"/>
+      <c r="O177" s="61"/>
+      <c r="P177" s="61"/>
+      <c r="Q177" s="61"/>
+      <c r="R177" s="61"/>
     </row>
     <row r="178" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A178" s="60">
-        <v>2005</v>
-      </c>
-      <c r="B178" s="61">
-        <v>3.0800000000000001E-2</v>
-      </c>
-      <c r="C178" s="62">
-        <v>0.57999999999999996</v>
-      </c>
-      <c r="D178" s="61">
-        <v>8.6300000000000002E-2</v>
-      </c>
-      <c r="E178" s="61">
-        <v>8.6300000000000002E-2</v>
-      </c>
-      <c r="F178" s="61">
-        <v>2.35E-2</v>
-      </c>
-      <c r="G178" s="61">
-        <v>8.6300000000000002E-2</v>
-      </c>
-      <c r="H178" s="61">
-        <v>4.6600000000000003E-2</v>
-      </c>
-      <c r="I178" s="61">
-        <v>8.6300000000000002E-2</v>
-      </c>
-      <c r="J178" s="61">
-        <v>-2.5999999999999999E-3</v>
-      </c>
-      <c r="K178" s="61">
-        <v>8.6300000000000002E-2</v>
-      </c>
-      <c r="L178" s="61">
-        <v>-1.9199999999999998E-2</v>
-      </c>
-      <c r="M178" s="61">
-        <v>8.6300000000000002E-2</v>
-      </c>
-      <c r="N178" s="61">
-        <v>1.7999999999999999E-2</v>
-      </c>
-      <c r="O178" s="61">
-        <v>8.6300000000000002E-2</v>
-      </c>
-      <c r="P178" s="61">
-        <v>1.9400000000000001E-2</v>
-      </c>
-      <c r="Q178" s="61">
-        <v>8.6300000000000002E-2</v>
-      </c>
-      <c r="R178" s="61">
-        <v>3.0800000000000001E-2</v>
-      </c>
+      <c r="A178" s="60"/>
+      <c r="B178" s="61"/>
+      <c r="C178" s="62"/>
+      <c r="D178" s="61"/>
+      <c r="E178" s="61"/>
+      <c r="F178" s="61"/>
+      <c r="G178" s="61"/>
+      <c r="H178" s="61"/>
+      <c r="I178" s="61"/>
+      <c r="J178" s="61"/>
+      <c r="K178" s="61"/>
+      <c r="L178" s="61"/>
+      <c r="M178" s="61"/>
+      <c r="N178" s="61"/>
+      <c r="O178" s="61"/>
+      <c r="P178" s="61"/>
+      <c r="Q178" s="61"/>
+      <c r="R178" s="61"/>
     </row>
     <row r="179" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A179" s="60">
-        <v>2006</v>
-      </c>
-      <c r="B179" s="61">
-        <v>7.2099999999999997E-2</v>
-      </c>
-      <c r="C179" s="62">
-        <v>0.68</v>
-      </c>
-      <c r="D179" s="61">
-        <v>4.3E-3</v>
-      </c>
-      <c r="E179" s="61">
-        <v>4.3E-3</v>
-      </c>
-      <c r="F179" s="61">
-        <v>8.6999999999999994E-2</v>
-      </c>
-      <c r="G179" s="61">
-        <v>4.3E-3</v>
-      </c>
-      <c r="H179" s="61">
-        <v>0.1242</v>
-      </c>
-      <c r="I179" s="61">
-        <v>4.3E-3</v>
-      </c>
-      <c r="J179" s="61">
-        <v>0.1152</v>
-      </c>
-      <c r="K179" s="61">
-        <v>4.3E-3</v>
-      </c>
-      <c r="L179" s="61">
-        <v>0.1159</v>
-      </c>
-      <c r="M179" s="61">
-        <v>4.3E-3</v>
-      </c>
-      <c r="N179" s="61">
-        <v>0.1103</v>
-      </c>
-      <c r="O179" s="61">
-        <v>4.3E-3</v>
-      </c>
-      <c r="P179" s="61">
-        <v>9.8400000000000001E-2</v>
-      </c>
-      <c r="Q179" s="61">
-        <v>4.3E-3</v>
-      </c>
-      <c r="R179" s="61">
-        <v>7.2099999999999997E-2</v>
-      </c>
+      <c r="A179" s="60"/>
+      <c r="B179" s="61"/>
+      <c r="C179" s="62"/>
+      <c r="D179" s="61"/>
+      <c r="E179" s="61"/>
+      <c r="F179" s="61"/>
+      <c r="G179" s="61"/>
+      <c r="H179" s="61"/>
+      <c r="I179" s="61"/>
+      <c r="J179" s="61"/>
+      <c r="K179" s="61"/>
+      <c r="L179" s="61"/>
+      <c r="M179" s="61"/>
+      <c r="N179" s="61"/>
+      <c r="O179" s="61"/>
+      <c r="P179" s="61"/>
+      <c r="Q179" s="61"/>
+      <c r="R179" s="61"/>
     </row>
     <row r="180" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A180" s="60">
-        <v>2007</v>
-      </c>
-      <c r="B180" s="61">
-        <v>-1.77E-2</v>
-      </c>
-      <c r="C180" s="62">
-        <v>0.56000000000000005</v>
-      </c>
-      <c r="D180" s="61">
-        <v>7.4000000000000003E-3</v>
-      </c>
-      <c r="E180" s="61">
-        <v>7.4000000000000003E-3</v>
-      </c>
-      <c r="F180" s="61">
-        <v>6.7500000000000004E-2</v>
-      </c>
-      <c r="G180" s="61">
-        <v>7.4000000000000003E-3</v>
-      </c>
-      <c r="H180" s="61">
-        <v>1.24E-2</v>
-      </c>
-      <c r="I180" s="61">
-        <v>7.4000000000000003E-3</v>
-      </c>
-      <c r="J180" s="61">
-        <v>-8.6999999999999994E-3</v>
-      </c>
-      <c r="K180" s="61">
-        <v>7.4000000000000003E-3</v>
-      </c>
-      <c r="L180" s="61">
-        <v>-1.6899999999999998E-2</v>
-      </c>
-      <c r="M180" s="61">
-        <v>7.4000000000000003E-3</v>
-      </c>
-      <c r="N180" s="61">
-        <v>-3.3799999999999997E-2</v>
-      </c>
-      <c r="O180" s="61">
-        <v>7.4000000000000003E-3</v>
-      </c>
-      <c r="P180" s="61">
-        <v>-2.9700000000000001E-2</v>
-      </c>
-      <c r="Q180" s="61">
-        <v>7.4000000000000003E-3</v>
-      </c>
-      <c r="R180" s="61">
-        <v>-1.77E-2</v>
-      </c>
+      <c r="A180" s="60"/>
+      <c r="B180" s="61"/>
+      <c r="C180" s="62"/>
+      <c r="D180" s="61"/>
+      <c r="E180" s="61"/>
+      <c r="F180" s="61"/>
+      <c r="G180" s="61"/>
+      <c r="H180" s="61"/>
+      <c r="I180" s="61"/>
+      <c r="J180" s="61"/>
+      <c r="K180" s="61"/>
+      <c r="L180" s="61"/>
+      <c r="M180" s="61"/>
+      <c r="N180" s="61"/>
+      <c r="O180" s="61"/>
+      <c r="P180" s="61"/>
+      <c r="Q180" s="61"/>
+      <c r="R180" s="61"/>
     </row>
     <row r="181" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A181" s="60">
-        <v>2008</v>
-      </c>
-      <c r="B181" s="61">
-        <v>-7.7899999999999997E-2</v>
-      </c>
-      <c r="C181" s="62">
-        <v>0.52</v>
-      </c>
-      <c r="D181" s="61">
-        <v>-2.2499999999999999E-2</v>
-      </c>
-      <c r="E181" s="61">
-        <v>-2.2499999999999999E-2</v>
-      </c>
-      <c r="F181" s="61">
-        <v>5.8999999999999997E-2</v>
-      </c>
-      <c r="G181" s="61">
-        <v>-2.2499999999999999E-2</v>
-      </c>
-      <c r="H181" s="61">
-        <v>5.0000000000000001E-3</v>
-      </c>
-      <c r="I181" s="61">
-        <v>-2.2499999999999999E-2</v>
-      </c>
-      <c r="J181" s="61">
-        <v>-5.7200000000000001E-2</v>
-      </c>
-      <c r="K181" s="61">
-        <v>-2.2499999999999999E-2</v>
-      </c>
-      <c r="L181" s="61">
-        <v>-6.5600000000000006E-2</v>
-      </c>
-      <c r="M181" s="61">
-        <v>-2.2499999999999999E-2</v>
-      </c>
-      <c r="N181" s="61">
-        <v>-6.3200000000000006E-2</v>
-      </c>
-      <c r="O181" s="61">
-        <v>-2.2499999999999999E-2</v>
-      </c>
-      <c r="P181" s="61">
-        <v>-6.8400000000000002E-2</v>
-      </c>
-      <c r="Q181" s="61">
-        <v>-2.2499999999999999E-2</v>
-      </c>
-      <c r="R181" s="61">
-        <v>-7.7899999999999997E-2</v>
-      </c>
+      <c r="A181" s="60"/>
+      <c r="B181" s="61"/>
+      <c r="C181" s="62"/>
+      <c r="D181" s="61"/>
+      <c r="E181" s="61"/>
+      <c r="F181" s="61"/>
+      <c r="G181" s="61"/>
+      <c r="H181" s="61"/>
+      <c r="I181" s="61"/>
+      <c r="J181" s="61"/>
+      <c r="K181" s="61"/>
+      <c r="L181" s="61"/>
+      <c r="M181" s="61"/>
+      <c r="N181" s="61"/>
+      <c r="O181" s="61"/>
+      <c r="P181" s="61"/>
+      <c r="Q181" s="61"/>
+      <c r="R181" s="61"/>
     </row>
     <row r="182" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A182" s="60">
@@ -7904,266 +7161,266 @@
       <c r="A200" s="12"/>
     </row>
     <row r="202" spans="1:18" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A202" s="80" t="s">
-        <v>209</v>
-      </c>
-      <c r="B202" s="80"/>
-      <c r="C202" s="80"/>
-      <c r="D202" s="80"/>
-      <c r="E202" s="80"/>
-      <c r="F202" s="80"/>
-      <c r="G202" s="80"/>
-      <c r="H202" s="80"/>
-      <c r="I202" s="80"/>
-      <c r="J202" s="80"/>
-      <c r="K202" s="80"/>
-      <c r="L202" s="80"/>
-      <c r="M202" s="80"/>
-      <c r="N202" s="80"/>
-      <c r="O202" s="80"/>
-      <c r="P202" s="80"/>
-      <c r="Q202" s="80"/>
-      <c r="R202" s="80"/>
+      <c r="A202" s="77" t="s">
+        <v>206</v>
+      </c>
+      <c r="B202" s="77"/>
+      <c r="C202" s="77"/>
+      <c r="D202" s="77"/>
+      <c r="E202" s="77"/>
+      <c r="F202" s="77"/>
+      <c r="G202" s="77"/>
+      <c r="H202" s="77"/>
+      <c r="I202" s="77"/>
+      <c r="J202" s="77"/>
+      <c r="K202" s="77"/>
+      <c r="L202" s="77"/>
+      <c r="M202" s="77"/>
+      <c r="N202" s="77"/>
+      <c r="O202" s="77"/>
+      <c r="P202" s="77"/>
+      <c r="Q202" s="77"/>
+      <c r="R202" s="77"/>
     </row>
     <row r="203" spans="1:18" ht="26" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A203" s="7" t="s">
-        <v>210</v>
-      </c>
-      <c r="B203" s="77" t="s">
-        <v>211</v>
-      </c>
-      <c r="C203" s="77"/>
-      <c r="D203" s="77"/>
-      <c r="E203" s="77"/>
-      <c r="F203" s="77"/>
-      <c r="G203" s="77"/>
-      <c r="H203" s="77"/>
-      <c r="I203" s="77"/>
-      <c r="J203" s="77"/>
-      <c r="K203" s="77"/>
-      <c r="L203" s="77"/>
-      <c r="M203" s="77"/>
-      <c r="N203" s="77"/>
-      <c r="O203" s="77"/>
-      <c r="P203" s="77"/>
-      <c r="Q203" s="77"/>
-      <c r="R203" s="77"/>
+        <v>207</v>
+      </c>
+      <c r="B203" s="74" t="s">
+        <v>208</v>
+      </c>
+      <c r="C203" s="74"/>
+      <c r="D203" s="74"/>
+      <c r="E203" s="74"/>
+      <c r="F203" s="74"/>
+      <c r="G203" s="74"/>
+      <c r="H203" s="74"/>
+      <c r="I203" s="74"/>
+      <c r="J203" s="74"/>
+      <c r="K203" s="74"/>
+      <c r="L203" s="74"/>
+      <c r="M203" s="74"/>
+      <c r="N203" s="74"/>
+      <c r="O203" s="74"/>
+      <c r="P203" s="74"/>
+      <c r="Q203" s="74"/>
+      <c r="R203" s="74"/>
     </row>
     <row r="204" spans="1:18" ht="26" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A204" s="7" t="s">
-        <v>212</v>
-      </c>
-      <c r="B204" s="77" t="s">
-        <v>213</v>
-      </c>
-      <c r="C204" s="77"/>
-      <c r="D204" s="77"/>
-      <c r="E204" s="77"/>
-      <c r="F204" s="77"/>
-      <c r="G204" s="77"/>
-      <c r="H204" s="77"/>
-      <c r="I204" s="77"/>
-      <c r="J204" s="77"/>
-      <c r="K204" s="77"/>
-      <c r="L204" s="77"/>
-      <c r="M204" s="77"/>
-      <c r="N204" s="77"/>
-      <c r="O204" s="77"/>
-      <c r="P204" s="77"/>
-      <c r="Q204" s="77"/>
-      <c r="R204" s="77"/>
+        <v>209</v>
+      </c>
+      <c r="B204" s="74" t="s">
+        <v>210</v>
+      </c>
+      <c r="C204" s="74"/>
+      <c r="D204" s="74"/>
+      <c r="E204" s="74"/>
+      <c r="F204" s="74"/>
+      <c r="G204" s="74"/>
+      <c r="H204" s="74"/>
+      <c r="I204" s="74"/>
+      <c r="J204" s="74"/>
+      <c r="K204" s="74"/>
+      <c r="L204" s="74"/>
+      <c r="M204" s="74"/>
+      <c r="N204" s="74"/>
+      <c r="O204" s="74"/>
+      <c r="P204" s="74"/>
+      <c r="Q204" s="74"/>
+      <c r="R204" s="74"/>
     </row>
     <row r="205" spans="1:18" ht="26" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A205" s="7" t="s">
-        <v>214</v>
-      </c>
-      <c r="B205" s="77" t="s">
-        <v>215</v>
-      </c>
-      <c r="C205" s="77"/>
-      <c r="D205" s="77"/>
-      <c r="E205" s="77"/>
-      <c r="F205" s="77"/>
-      <c r="G205" s="77"/>
-      <c r="H205" s="77"/>
-      <c r="I205" s="77"/>
-      <c r="J205" s="77"/>
-      <c r="K205" s="77"/>
-      <c r="L205" s="77"/>
-      <c r="M205" s="77"/>
-      <c r="N205" s="77"/>
-      <c r="O205" s="77"/>
-      <c r="P205" s="77"/>
-      <c r="Q205" s="77"/>
-      <c r="R205" s="77"/>
+        <v>211</v>
+      </c>
+      <c r="B205" s="74" t="s">
+        <v>212</v>
+      </c>
+      <c r="C205" s="74"/>
+      <c r="D205" s="74"/>
+      <c r="E205" s="74"/>
+      <c r="F205" s="74"/>
+      <c r="G205" s="74"/>
+      <c r="H205" s="74"/>
+      <c r="I205" s="74"/>
+      <c r="J205" s="74"/>
+      <c r="K205" s="74"/>
+      <c r="L205" s="74"/>
+      <c r="M205" s="74"/>
+      <c r="N205" s="74"/>
+      <c r="O205" s="74"/>
+      <c r="P205" s="74"/>
+      <c r="Q205" s="74"/>
+      <c r="R205" s="74"/>
     </row>
     <row r="206" spans="1:18" ht="26" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A206" s="7" t="s">
-        <v>216</v>
-      </c>
-      <c r="B206" s="77" t="s">
-        <v>217</v>
-      </c>
-      <c r="C206" s="77"/>
-      <c r="D206" s="77"/>
-      <c r="E206" s="77"/>
-      <c r="F206" s="77"/>
-      <c r="G206" s="77"/>
-      <c r="H206" s="77"/>
-      <c r="I206" s="77"/>
-      <c r="J206" s="77"/>
-      <c r="K206" s="77"/>
-      <c r="L206" s="77"/>
-      <c r="M206" s="77"/>
-      <c r="N206" s="77"/>
-      <c r="O206" s="77"/>
-      <c r="P206" s="77"/>
-      <c r="Q206" s="77"/>
-      <c r="R206" s="77"/>
+        <v>213</v>
+      </c>
+      <c r="B206" s="74" t="s">
+        <v>214</v>
+      </c>
+      <c r="C206" s="74"/>
+      <c r="D206" s="74"/>
+      <c r="E206" s="74"/>
+      <c r="F206" s="74"/>
+      <c r="G206" s="74"/>
+      <c r="H206" s="74"/>
+      <c r="I206" s="74"/>
+      <c r="J206" s="74"/>
+      <c r="K206" s="74"/>
+      <c r="L206" s="74"/>
+      <c r="M206" s="74"/>
+      <c r="N206" s="74"/>
+      <c r="O206" s="74"/>
+      <c r="P206" s="74"/>
+      <c r="Q206" s="74"/>
+      <c r="R206" s="74"/>
     </row>
     <row r="207" spans="1:18" ht="26" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A207" s="7" t="s">
-        <v>218</v>
-      </c>
-      <c r="B207" s="77" t="s">
-        <v>219</v>
-      </c>
-      <c r="C207" s="77"/>
-      <c r="D207" s="77"/>
-      <c r="E207" s="77"/>
-      <c r="F207" s="77"/>
-      <c r="G207" s="77"/>
-      <c r="H207" s="77"/>
-      <c r="I207" s="77"/>
-      <c r="J207" s="77"/>
-      <c r="K207" s="77"/>
-      <c r="L207" s="77"/>
-      <c r="M207" s="77"/>
-      <c r="N207" s="77"/>
-      <c r="O207" s="77"/>
-      <c r="P207" s="77"/>
-      <c r="Q207" s="77"/>
-      <c r="R207" s="77"/>
+        <v>215</v>
+      </c>
+      <c r="B207" s="74" t="s">
+        <v>216</v>
+      </c>
+      <c r="C207" s="74"/>
+      <c r="D207" s="74"/>
+      <c r="E207" s="74"/>
+      <c r="F207" s="74"/>
+      <c r="G207" s="74"/>
+      <c r="H207" s="74"/>
+      <c r="I207" s="74"/>
+      <c r="J207" s="74"/>
+      <c r="K207" s="74"/>
+      <c r="L207" s="74"/>
+      <c r="M207" s="74"/>
+      <c r="N207" s="74"/>
+      <c r="O207" s="74"/>
+      <c r="P207" s="74"/>
+      <c r="Q207" s="74"/>
+      <c r="R207" s="74"/>
     </row>
     <row r="208" spans="1:18" ht="26" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A208" s="7" t="s">
-        <v>220</v>
-      </c>
-      <c r="B208" s="77" t="s">
-        <v>221</v>
-      </c>
-      <c r="C208" s="77"/>
-      <c r="D208" s="77"/>
-      <c r="E208" s="77"/>
-      <c r="F208" s="77"/>
-      <c r="G208" s="77"/>
-      <c r="H208" s="77"/>
-      <c r="I208" s="77"/>
-      <c r="J208" s="77"/>
-      <c r="K208" s="77"/>
-      <c r="L208" s="77"/>
-      <c r="M208" s="77"/>
-      <c r="N208" s="77"/>
-      <c r="O208" s="77"/>
-      <c r="P208" s="77"/>
-      <c r="Q208" s="77"/>
-      <c r="R208" s="77"/>
+        <v>217</v>
+      </c>
+      <c r="B208" s="74" t="s">
+        <v>218</v>
+      </c>
+      <c r="C208" s="74"/>
+      <c r="D208" s="74"/>
+      <c r="E208" s="74"/>
+      <c r="F208" s="74"/>
+      <c r="G208" s="74"/>
+      <c r="H208" s="74"/>
+      <c r="I208" s="74"/>
+      <c r="J208" s="74"/>
+      <c r="K208" s="74"/>
+      <c r="L208" s="74"/>
+      <c r="M208" s="74"/>
+      <c r="N208" s="74"/>
+      <c r="O208" s="74"/>
+      <c r="P208" s="74"/>
+      <c r="Q208" s="74"/>
+      <c r="R208" s="74"/>
     </row>
     <row r="209" spans="1:18" ht="26" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A209" s="7" t="s">
-        <v>222</v>
-      </c>
-      <c r="B209" s="77" t="s">
-        <v>223</v>
-      </c>
-      <c r="C209" s="77"/>
-      <c r="D209" s="77"/>
-      <c r="E209" s="77"/>
-      <c r="F209" s="77"/>
-      <c r="G209" s="77"/>
-      <c r="H209" s="77"/>
-      <c r="I209" s="77"/>
-      <c r="J209" s="77"/>
-      <c r="K209" s="77"/>
-      <c r="L209" s="77"/>
-      <c r="M209" s="77"/>
-      <c r="N209" s="77"/>
-      <c r="O209" s="77"/>
-      <c r="P209" s="77"/>
-      <c r="Q209" s="77"/>
-      <c r="R209" s="77"/>
+        <v>219</v>
+      </c>
+      <c r="B209" s="74" t="s">
+        <v>220</v>
+      </c>
+      <c r="C209" s="74"/>
+      <c r="D209" s="74"/>
+      <c r="E209" s="74"/>
+      <c r="F209" s="74"/>
+      <c r="G209" s="74"/>
+      <c r="H209" s="74"/>
+      <c r="I209" s="74"/>
+      <c r="J209" s="74"/>
+      <c r="K209" s="74"/>
+      <c r="L209" s="74"/>
+      <c r="M209" s="74"/>
+      <c r="N209" s="74"/>
+      <c r="O209" s="74"/>
+      <c r="P209" s="74"/>
+      <c r="Q209" s="74"/>
+      <c r="R209" s="74"/>
     </row>
     <row r="210" spans="1:18" ht="26" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A210" s="7" t="s">
-        <v>224</v>
-      </c>
-      <c r="B210" s="77" t="s">
-        <v>225</v>
-      </c>
-      <c r="C210" s="77"/>
-      <c r="D210" s="77"/>
-      <c r="E210" s="77"/>
-      <c r="F210" s="77"/>
-      <c r="G210" s="77"/>
-      <c r="H210" s="77"/>
-      <c r="I210" s="77"/>
-      <c r="J210" s="77"/>
-      <c r="K210" s="77"/>
-      <c r="L210" s="77"/>
-      <c r="M210" s="77"/>
-      <c r="N210" s="77"/>
-      <c r="O210" s="77"/>
-      <c r="P210" s="77"/>
-      <c r="Q210" s="77"/>
-      <c r="R210" s="77"/>
+        <v>221</v>
+      </c>
+      <c r="B210" s="74" t="s">
+        <v>222</v>
+      </c>
+      <c r="C210" s="74"/>
+      <c r="D210" s="74"/>
+      <c r="E210" s="74"/>
+      <c r="F210" s="74"/>
+      <c r="G210" s="74"/>
+      <c r="H210" s="74"/>
+      <c r="I210" s="74"/>
+      <c r="J210" s="74"/>
+      <c r="K210" s="74"/>
+      <c r="L210" s="74"/>
+      <c r="M210" s="74"/>
+      <c r="N210" s="74"/>
+      <c r="O210" s="74"/>
+      <c r="P210" s="74"/>
+      <c r="Q210" s="74"/>
+      <c r="R210" s="74"/>
     </row>
     <row r="211" spans="1:18" ht="26" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A211" s="7" t="s">
-        <v>226</v>
-      </c>
-      <c r="B211" s="77" t="s">
-        <v>227</v>
-      </c>
-      <c r="C211" s="77"/>
-      <c r="D211" s="77"/>
-      <c r="E211" s="77"/>
-      <c r="F211" s="77"/>
-      <c r="G211" s="77"/>
-      <c r="H211" s="77"/>
-      <c r="I211" s="77"/>
-      <c r="J211" s="77"/>
-      <c r="K211" s="77"/>
-      <c r="L211" s="77"/>
-      <c r="M211" s="77"/>
-      <c r="N211" s="77"/>
-      <c r="O211" s="77"/>
-      <c r="P211" s="77"/>
-      <c r="Q211" s="77"/>
-      <c r="R211" s="77"/>
+        <v>223</v>
+      </c>
+      <c r="B211" s="74" t="s">
+        <v>224</v>
+      </c>
+      <c r="C211" s="74"/>
+      <c r="D211" s="74"/>
+      <c r="E211" s="74"/>
+      <c r="F211" s="74"/>
+      <c r="G211" s="74"/>
+      <c r="H211" s="74"/>
+      <c r="I211" s="74"/>
+      <c r="J211" s="74"/>
+      <c r="K211" s="74"/>
+      <c r="L211" s="74"/>
+      <c r="M211" s="74"/>
+      <c r="N211" s="74"/>
+      <c r="O211" s="74"/>
+      <c r="P211" s="74"/>
+      <c r="Q211" s="74"/>
+      <c r="R211" s="74"/>
     </row>
     <row r="212" spans="1:18" ht="26" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A212" s="7" t="s">
-        <v>228</v>
-      </c>
-      <c r="B212" s="77" t="s">
-        <v>229</v>
-      </c>
-      <c r="C212" s="77"/>
-      <c r="D212" s="77"/>
-      <c r="E212" s="77"/>
-      <c r="F212" s="77"/>
-      <c r="G212" s="77"/>
-      <c r="H212" s="77"/>
-      <c r="I212" s="77"/>
-      <c r="J212" s="77"/>
-      <c r="K212" s="77"/>
-      <c r="L212" s="77"/>
-      <c r="M212" s="77"/>
-      <c r="N212" s="77"/>
-      <c r="O212" s="77"/>
-      <c r="P212" s="77"/>
-      <c r="Q212" s="77"/>
-      <c r="R212" s="77"/>
+        <v>225</v>
+      </c>
+      <c r="B212" s="74" t="s">
+        <v>226</v>
+      </c>
+      <c r="C212" s="74"/>
+      <c r="D212" s="74"/>
+      <c r="E212" s="74"/>
+      <c r="F212" s="74"/>
+      <c r="G212" s="74"/>
+      <c r="H212" s="74"/>
+      <c r="I212" s="74"/>
+      <c r="J212" s="74"/>
+      <c r="K212" s="74"/>
+      <c r="L212" s="74"/>
+      <c r="M212" s="74"/>
+      <c r="N212" s="74"/>
+      <c r="O212" s="74"/>
+      <c r="P212" s="74"/>
+      <c r="Q212" s="74"/>
+      <c r="R212" s="74"/>
     </row>
     <row r="214" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A214" s="12"/>
@@ -8249,65 +7506,65 @@
     <mergeCell ref="E98:O98"/>
   </mergeCells>
   <conditionalFormatting sqref="C97">
-    <cfRule type="cellIs" dxfId="16" priority="8" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="14" priority="8" operator="greaterThanOrEqual">
       <formula>0.35</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="15" priority="9" operator="between">
+    <cfRule type="cellIs" dxfId="13" priority="9" operator="between">
       <formula>0.15</formula>
       <formula>0.35</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="14" priority="10" operator="lessThan">
+    <cfRule type="cellIs" dxfId="12" priority="10" operator="lessThan">
       <formula>0.15</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C100">
-    <cfRule type="cellIs" dxfId="13" priority="5" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="11" priority="5" operator="greaterThanOrEqual">
       <formula>0.35</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="12" priority="6" operator="between">
+    <cfRule type="cellIs" dxfId="10" priority="6" operator="between">
       <formula>0.15</formula>
       <formula>0.35</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="11" priority="7" operator="lessThan">
+    <cfRule type="cellIs" dxfId="9" priority="7" operator="lessThan">
       <formula>0.15</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C118:C119">
-    <cfRule type="cellIs" dxfId="10" priority="1" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="8" priority="1" operator="greaterThanOrEqual">
       <formula>3</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="9" priority="2" operator="lessThanOrEqual">
+    <cfRule type="cellIs" dxfId="7" priority="2" operator="lessThanOrEqual">
       <formula>-3</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C131">
-    <cfRule type="expression" dxfId="8" priority="13">
+    <cfRule type="expression" dxfId="6" priority="13">
       <formula>ISNUMBER(SEARCH("DIVERGENCE",$C$131))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C133">
-    <cfRule type="expression" dxfId="7" priority="11">
+    <cfRule type="expression" dxfId="5" priority="11">
       <formula>ISNUMBER(SEARCH("BREACH",$C$133))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C134">
-    <cfRule type="expression" dxfId="6" priority="14">
+    <cfRule type="expression" dxfId="4" priority="14">
       <formula>ISNUMBER(SEARCH("ACCUMULATE",$C$134))</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="5" priority="15">
+    <cfRule type="expression" dxfId="3" priority="15">
       <formula>ISNUMBER(SEARCH("HALT",$C$134))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C148">
-    <cfRule type="expression" dxfId="4" priority="12">
+    <cfRule type="expression" dxfId="2" priority="12">
       <formula>ISNUMBER(SEARCH("WARN",$C$148))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M49:O79">
-    <cfRule type="cellIs" dxfId="3" priority="16" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="1" priority="16" operator="greaterThan">
       <formula>0.05</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="2" priority="17" operator="lessThan">
+    <cfRule type="cellIs" dxfId="0" priority="17" operator="lessThan">
       <formula>-0.05</formula>
     </cfRule>
   </conditionalFormatting>
@@ -8329,51 +7586,51 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="17" x14ac:dyDescent="0.2">
-      <c r="A1" s="85" t="s">
-        <v>230</v>
-      </c>
-      <c r="B1" s="76"/>
-      <c r="C1" s="76"/>
-      <c r="D1" s="76"/>
-      <c r="E1" s="76"/>
-      <c r="F1" s="76"/>
-      <c r="G1" s="76"/>
-      <c r="H1" s="76"/>
+      <c r="A1" s="82" t="s">
+        <v>227</v>
+      </c>
+      <c r="B1" s="73"/>
+      <c r="C1" s="73"/>
+      <c r="D1" s="73"/>
+      <c r="E1" s="73"/>
+      <c r="F1" s="73"/>
+      <c r="G1" s="73"/>
+      <c r="H1" s="73"/>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A2" s="63" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A3" s="64" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="59" t="s">
+        <v>230</v>
+      </c>
+      <c r="B5" s="59" t="s">
+        <v>231</v>
+      </c>
+      <c r="C5" s="59" t="s">
+        <v>232</v>
+      </c>
+      <c r="D5" s="59" t="s">
         <v>233</v>
       </c>
-      <c r="B5" s="59" t="s">
+      <c r="E5" s="59" t="s">
         <v>234</v>
       </c>
-      <c r="C5" s="59" t="s">
+      <c r="F5" s="59" t="s">
         <v>235</v>
       </c>
-      <c r="D5" s="59" t="s">
+      <c r="G5" s="59" t="s">
         <v>236</v>
       </c>
-      <c r="E5" s="59" t="s">
+      <c r="H5" s="59" t="s">
         <v>237</v>
-      </c>
-      <c r="F5" s="59" t="s">
-        <v>238</v>
-      </c>
-      <c r="G5" s="59" t="s">
-        <v>239</v>
-      </c>
-      <c r="H5" s="59" t="s">
-        <v>240</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.2">
@@ -9908,7 +9165,7 @@
     </row>
     <row r="58" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A58" s="7" t="s">
-        <v>241</v>
+        <v>238</v>
       </c>
       <c r="B58" s="17">
         <f>COUNT($B$6:$B$56)</f>
@@ -9917,7 +9174,7 @@
     </row>
     <row r="59" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A59" s="8" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="B59" s="55" t="str">
         <f>IFERROR(MEDIAN($B$6:$B$56),"")</f>
@@ -9926,7 +9183,7 @@
     </row>
     <row r="60" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A60" s="8" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
       <c r="B60" s="55">
         <f>IFERROR(MIN($B$6:$B$56),"")</f>
@@ -9939,7 +9196,7 @@
     </row>
     <row r="61" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A61" s="8" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="B61" s="55" t="str">
         <f>IFERROR(STDEV($B$6:$B$56),"")</f>
@@ -9948,7 +9205,7 @@
     </row>
     <row r="62" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A62" s="8" t="s">
-        <v>245</v>
+        <v>242</v>
       </c>
       <c r="B62" s="17">
         <f>IFERROR(SUM($F$6:$F$56),"")</f>
@@ -9957,14 +9214,14 @@
     </row>
     <row r="64" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A64" s="70" t="s">
-        <v>246</v>
+        <v>243</v>
       </c>
       <c r="E64" s="71" t="str">
         <f>IFERROR(AVERAGE($E$6:$E$56),"")</f>
         <v/>
       </c>
       <c r="G64" s="7" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="H64" s="71" t="str">
         <f>IFERROR(AVERAGE($H$6:$H$56),"")</f>
@@ -9973,7 +9230,7 @@
     </row>
     <row r="66" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A66" s="63" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
     </row>
   </sheetData>
@@ -9982,1875 +9239,4 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:G125"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
-  <cols>
-    <col min="1" max="1" width="20" customWidth="1"/>
-    <col min="2" max="2" width="16" customWidth="1"/>
-    <col min="3" max="3" width="11" customWidth="1"/>
-    <col min="4" max="4" width="26" customWidth="1"/>
-    <col min="5" max="5" width="20" customWidth="1"/>
-    <col min="6" max="6" width="30" customWidth="1"/>
-    <col min="7" max="7" width="40" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:7" ht="17" x14ac:dyDescent="0.2">
-      <c r="A1" s="85" t="s">
-        <v>249</v>
-      </c>
-      <c r="B1" s="76"/>
-      <c r="C1" s="76"/>
-      <c r="D1" s="76"/>
-      <c r="E1" s="76"/>
-      <c r="F1" s="76"/>
-      <c r="G1" s="76"/>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A2" s="63" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A3" s="64" t="s">
-        <v>251</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A5" s="59" t="s">
-        <v>252</v>
-      </c>
-      <c r="B5" s="59" t="s">
-        <v>253</v>
-      </c>
-      <c r="C5" s="59" t="s">
-        <v>254</v>
-      </c>
-      <c r="D5" s="59" t="s">
-        <v>255</v>
-      </c>
-      <c r="E5" s="59" t="s">
-        <v>256</v>
-      </c>
-      <c r="F5" s="59" t="s">
-        <v>257</v>
-      </c>
-      <c r="G5" s="59" t="s">
-        <v>258</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A6" s="72"/>
-      <c r="B6" s="72"/>
-      <c r="C6" s="72"/>
-      <c r="D6" s="31"/>
-      <c r="E6" s="73"/>
-      <c r="F6" s="74" t="str">
-        <f t="shared" ref="F6:F37" si="0">IF($E6="","",IF($E6&gt;0.03,"▲ SURGE ENTERING — early YES signal",IF($E6&lt;-0.03,"▼ COOLING — NO side strengthens","flat")))</f>
-        <v/>
-      </c>
-      <c r="G6" s="72"/>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A7" s="72"/>
-      <c r="B7" s="72"/>
-      <c r="C7" s="72"/>
-      <c r="D7" s="31"/>
-      <c r="E7" s="73" t="str">
-        <f>IF($D7="","",IFERROR($D7-LOOKUP(2,1/($B$6:$B6=$B7),$D$6:$D6),""))</f>
-        <v/>
-      </c>
-      <c r="F7" s="74" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G7" s="72"/>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A8" s="72"/>
-      <c r="B8" s="72"/>
-      <c r="C8" s="72"/>
-      <c r="D8" s="31"/>
-      <c r="E8" s="73" t="str">
-        <f>IF($D8="","",IFERROR($D8-LOOKUP(2,1/($B$6:$B7=$B8),$D$6:$D7),""))</f>
-        <v/>
-      </c>
-      <c r="F8" s="74" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G8" s="72"/>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A9" s="72"/>
-      <c r="B9" s="72"/>
-      <c r="C9" s="72"/>
-      <c r="D9" s="31"/>
-      <c r="E9" s="73" t="str">
-        <f>IF($D9="","",IFERROR($D9-LOOKUP(2,1/($B$6:$B8=$B9),$D$6:$D8),""))</f>
-        <v/>
-      </c>
-      <c r="F9" s="74" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G9" s="72"/>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A10" s="72"/>
-      <c r="B10" s="72"/>
-      <c r="C10" s="72"/>
-      <c r="D10" s="31"/>
-      <c r="E10" s="73" t="str">
-        <f>IF($D10="","",IFERROR($D10-LOOKUP(2,1/($B$6:$B9=$B10),$D$6:$D9),""))</f>
-        <v/>
-      </c>
-      <c r="F10" s="74" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G10" s="72"/>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A11" s="72"/>
-      <c r="B11" s="72"/>
-      <c r="C11" s="72"/>
-      <c r="D11" s="31"/>
-      <c r="E11" s="73" t="str">
-        <f>IF($D11="","",IFERROR($D11-LOOKUP(2,1/($B$6:$B10=$B11),$D$6:$D10),""))</f>
-        <v/>
-      </c>
-      <c r="F11" s="74" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G11" s="72"/>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A12" s="72"/>
-      <c r="B12" s="72"/>
-      <c r="C12" s="72"/>
-      <c r="D12" s="31"/>
-      <c r="E12" s="73" t="str">
-        <f>IF($D12="","",IFERROR($D12-LOOKUP(2,1/($B$6:$B11=$B12),$D$6:$D11),""))</f>
-        <v/>
-      </c>
-      <c r="F12" s="74" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G12" s="72"/>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A13" s="72"/>
-      <c r="B13" s="72"/>
-      <c r="C13" s="72"/>
-      <c r="D13" s="31"/>
-      <c r="E13" s="73" t="str">
-        <f>IF($D13="","",IFERROR($D13-LOOKUP(2,1/($B$6:$B12=$B13),$D$6:$D12),""))</f>
-        <v/>
-      </c>
-      <c r="F13" s="74" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G13" s="72"/>
-    </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A14" s="72"/>
-      <c r="B14" s="72"/>
-      <c r="C14" s="72"/>
-      <c r="D14" s="31"/>
-      <c r="E14" s="73" t="str">
-        <f>IF($D14="","",IFERROR($D14-LOOKUP(2,1/($B$6:$B13=$B14),$D$6:$D13),""))</f>
-        <v/>
-      </c>
-      <c r="F14" s="74" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G14" s="72"/>
-    </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A15" s="72"/>
-      <c r="B15" s="72"/>
-      <c r="C15" s="72"/>
-      <c r="D15" s="31"/>
-      <c r="E15" s="73" t="str">
-        <f>IF($D15="","",IFERROR($D15-LOOKUP(2,1/($B$6:$B14=$B15),$D$6:$D14),""))</f>
-        <v/>
-      </c>
-      <c r="F15" s="74" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G15" s="72"/>
-    </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A16" s="72"/>
-      <c r="B16" s="72"/>
-      <c r="C16" s="72"/>
-      <c r="D16" s="31"/>
-      <c r="E16" s="73" t="str">
-        <f>IF($D16="","",IFERROR($D16-LOOKUP(2,1/($B$6:$B15=$B16),$D$6:$D15),""))</f>
-        <v/>
-      </c>
-      <c r="F16" s="74" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G16" s="72"/>
-    </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A17" s="72"/>
-      <c r="B17" s="72"/>
-      <c r="C17" s="72"/>
-      <c r="D17" s="31"/>
-      <c r="E17" s="73" t="str">
-        <f>IF($D17="","",IFERROR($D17-LOOKUP(2,1/($B$6:$B16=$B17),$D$6:$D16),""))</f>
-        <v/>
-      </c>
-      <c r="F17" s="74" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G17" s="72"/>
-    </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A18" s="72"/>
-      <c r="B18" s="72"/>
-      <c r="C18" s="72"/>
-      <c r="D18" s="31"/>
-      <c r="E18" s="73" t="str">
-        <f>IF($D18="","",IFERROR($D18-LOOKUP(2,1/($B$6:$B17=$B18),$D$6:$D17),""))</f>
-        <v/>
-      </c>
-      <c r="F18" s="74" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G18" s="72"/>
-    </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A19" s="72"/>
-      <c r="B19" s="72"/>
-      <c r="C19" s="72"/>
-      <c r="D19" s="31"/>
-      <c r="E19" s="73" t="str">
-        <f>IF($D19="","",IFERROR($D19-LOOKUP(2,1/($B$6:$B18=$B19),$D$6:$D18),""))</f>
-        <v/>
-      </c>
-      <c r="F19" s="74" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G19" s="72"/>
-    </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A20" s="72"/>
-      <c r="B20" s="72"/>
-      <c r="C20" s="72"/>
-      <c r="D20" s="31"/>
-      <c r="E20" s="73" t="str">
-        <f>IF($D20="","",IFERROR($D20-LOOKUP(2,1/($B$6:$B19=$B20),$D$6:$D19),""))</f>
-        <v/>
-      </c>
-      <c r="F20" s="74" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G20" s="72"/>
-    </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A21" s="72"/>
-      <c r="B21" s="72"/>
-      <c r="C21" s="72"/>
-      <c r="D21" s="31"/>
-      <c r="E21" s="73" t="str">
-        <f>IF($D21="","",IFERROR($D21-LOOKUP(2,1/($B$6:$B20=$B21),$D$6:$D20),""))</f>
-        <v/>
-      </c>
-      <c r="F21" s="74" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G21" s="72"/>
-    </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A22" s="72"/>
-      <c r="B22" s="72"/>
-      <c r="C22" s="72"/>
-      <c r="D22" s="31"/>
-      <c r="E22" s="73" t="str">
-        <f>IF($D22="","",IFERROR($D22-LOOKUP(2,1/($B$6:$B21=$B22),$D$6:$D21),""))</f>
-        <v/>
-      </c>
-      <c r="F22" s="74" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G22" s="72"/>
-    </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A23" s="72"/>
-      <c r="B23" s="72"/>
-      <c r="C23" s="72"/>
-      <c r="D23" s="31"/>
-      <c r="E23" s="73" t="str">
-        <f>IF($D23="","",IFERROR($D23-LOOKUP(2,1/($B$6:$B22=$B23),$D$6:$D22),""))</f>
-        <v/>
-      </c>
-      <c r="F23" s="74" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G23" s="72"/>
-    </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A24" s="72"/>
-      <c r="B24" s="72"/>
-      <c r="C24" s="72"/>
-      <c r="D24" s="31"/>
-      <c r="E24" s="73" t="str">
-        <f>IF($D24="","",IFERROR($D24-LOOKUP(2,1/($B$6:$B23=$B24),$D$6:$D23),""))</f>
-        <v/>
-      </c>
-      <c r="F24" s="74" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G24" s="72"/>
-    </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A25" s="72"/>
-      <c r="B25" s="72"/>
-      <c r="C25" s="72"/>
-      <c r="D25" s="31"/>
-      <c r="E25" s="73" t="str">
-        <f>IF($D25="","",IFERROR($D25-LOOKUP(2,1/($B$6:$B24=$B25),$D$6:$D24),""))</f>
-        <v/>
-      </c>
-      <c r="F25" s="74" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G25" s="72"/>
-    </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A26" s="72"/>
-      <c r="B26" s="72"/>
-      <c r="C26" s="72"/>
-      <c r="D26" s="31"/>
-      <c r="E26" s="73" t="str">
-        <f>IF($D26="","",IFERROR($D26-LOOKUP(2,1/($B$6:$B25=$B26),$D$6:$D25),""))</f>
-        <v/>
-      </c>
-      <c r="F26" s="74" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G26" s="72"/>
-    </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A27" s="72"/>
-      <c r="B27" s="72"/>
-      <c r="C27" s="72"/>
-      <c r="D27" s="31"/>
-      <c r="E27" s="73" t="str">
-        <f>IF($D27="","",IFERROR($D27-LOOKUP(2,1/($B$6:$B26=$B27),$D$6:$D26),""))</f>
-        <v/>
-      </c>
-      <c r="F27" s="74" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G27" s="72"/>
-    </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A28" s="72"/>
-      <c r="B28" s="72"/>
-      <c r="C28" s="72"/>
-      <c r="D28" s="31"/>
-      <c r="E28" s="73" t="str">
-        <f>IF($D28="","",IFERROR($D28-LOOKUP(2,1/($B$6:$B27=$B28),$D$6:$D27),""))</f>
-        <v/>
-      </c>
-      <c r="F28" s="74" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G28" s="72"/>
-    </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A29" s="72"/>
-      <c r="B29" s="72"/>
-      <c r="C29" s="72"/>
-      <c r="D29" s="31"/>
-      <c r="E29" s="73" t="str">
-        <f>IF($D29="","",IFERROR($D29-LOOKUP(2,1/($B$6:$B28=$B29),$D$6:$D28),""))</f>
-        <v/>
-      </c>
-      <c r="F29" s="74" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G29" s="72"/>
-    </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A30" s="72"/>
-      <c r="B30" s="72"/>
-      <c r="C30" s="72"/>
-      <c r="D30" s="31"/>
-      <c r="E30" s="73" t="str">
-        <f>IF($D30="","",IFERROR($D30-LOOKUP(2,1/($B$6:$B29=$B30),$D$6:$D29),""))</f>
-        <v/>
-      </c>
-      <c r="F30" s="74" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G30" s="72"/>
-    </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A31" s="72"/>
-      <c r="B31" s="72"/>
-      <c r="C31" s="72"/>
-      <c r="D31" s="31"/>
-      <c r="E31" s="73" t="str">
-        <f>IF($D31="","",IFERROR($D31-LOOKUP(2,1/($B$6:$B30=$B31),$D$6:$D30),""))</f>
-        <v/>
-      </c>
-      <c r="F31" s="74" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G31" s="72"/>
-    </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A32" s="72"/>
-      <c r="B32" s="72"/>
-      <c r="C32" s="72"/>
-      <c r="D32" s="31"/>
-      <c r="E32" s="73" t="str">
-        <f>IF($D32="","",IFERROR($D32-LOOKUP(2,1/($B$6:$B31=$B32),$D$6:$D31),""))</f>
-        <v/>
-      </c>
-      <c r="F32" s="74" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G32" s="72"/>
-    </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A33" s="72"/>
-      <c r="B33" s="72"/>
-      <c r="C33" s="72"/>
-      <c r="D33" s="31"/>
-      <c r="E33" s="73" t="str">
-        <f>IF($D33="","",IFERROR($D33-LOOKUP(2,1/($B$6:$B32=$B33),$D$6:$D32),""))</f>
-        <v/>
-      </c>
-      <c r="F33" s="74" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G33" s="72"/>
-    </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A34" s="72"/>
-      <c r="B34" s="72"/>
-      <c r="C34" s="72"/>
-      <c r="D34" s="31"/>
-      <c r="E34" s="73" t="str">
-        <f>IF($D34="","",IFERROR($D34-LOOKUP(2,1/($B$6:$B33=$B34),$D$6:$D33),""))</f>
-        <v/>
-      </c>
-      <c r="F34" s="74" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G34" s="72"/>
-    </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A35" s="72"/>
-      <c r="B35" s="72"/>
-      <c r="C35" s="72"/>
-      <c r="D35" s="31"/>
-      <c r="E35" s="73" t="str">
-        <f>IF($D35="","",IFERROR($D35-LOOKUP(2,1/($B$6:$B34=$B35),$D$6:$D34),""))</f>
-        <v/>
-      </c>
-      <c r="F35" s="74" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G35" s="72"/>
-    </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A36" s="72"/>
-      <c r="B36" s="72"/>
-      <c r="C36" s="72"/>
-      <c r="D36" s="31"/>
-      <c r="E36" s="73" t="str">
-        <f>IF($D36="","",IFERROR($D36-LOOKUP(2,1/($B$6:$B35=$B36),$D$6:$D35),""))</f>
-        <v/>
-      </c>
-      <c r="F36" s="74" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G36" s="72"/>
-    </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A37" s="72"/>
-      <c r="B37" s="72"/>
-      <c r="C37" s="72"/>
-      <c r="D37" s="31"/>
-      <c r="E37" s="73" t="str">
-        <f>IF($D37="","",IFERROR($D37-LOOKUP(2,1/($B$6:$B36=$B37),$D$6:$D36),""))</f>
-        <v/>
-      </c>
-      <c r="F37" s="74" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G37" s="72"/>
-    </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A38" s="72"/>
-      <c r="B38" s="72"/>
-      <c r="C38" s="72"/>
-      <c r="D38" s="31"/>
-      <c r="E38" s="73" t="str">
-        <f>IF($D38="","",IFERROR($D38-LOOKUP(2,1/($B$6:$B37=$B38),$D$6:$D37),""))</f>
-        <v/>
-      </c>
-      <c r="F38" s="74" t="str">
-        <f t="shared" ref="F38:F69" si="1">IF($E38="","",IF($E38&gt;0.03,"▲ SURGE ENTERING — early YES signal",IF($E38&lt;-0.03,"▼ COOLING — NO side strengthens","flat")))</f>
-        <v/>
-      </c>
-      <c r="G38" s="72"/>
-    </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A39" s="72"/>
-      <c r="B39" s="72"/>
-      <c r="C39" s="72"/>
-      <c r="D39" s="31"/>
-      <c r="E39" s="73" t="str">
-        <f>IF($D39="","",IFERROR($D39-LOOKUP(2,1/($B$6:$B38=$B39),$D$6:$D38),""))</f>
-        <v/>
-      </c>
-      <c r="F39" s="74" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="G39" s="72"/>
-    </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A40" s="72"/>
-      <c r="B40" s="72"/>
-      <c r="C40" s="72"/>
-      <c r="D40" s="31"/>
-      <c r="E40" s="73" t="str">
-        <f>IF($D40="","",IFERROR($D40-LOOKUP(2,1/($B$6:$B39=$B40),$D$6:$D39),""))</f>
-        <v/>
-      </c>
-      <c r="F40" s="74" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="G40" s="72"/>
-    </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A41" s="72"/>
-      <c r="B41" s="72"/>
-      <c r="C41" s="72"/>
-      <c r="D41" s="31"/>
-      <c r="E41" s="73" t="str">
-        <f>IF($D41="","",IFERROR($D41-LOOKUP(2,1/($B$6:$B40=$B41),$D$6:$D40),""))</f>
-        <v/>
-      </c>
-      <c r="F41" s="74" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="G41" s="72"/>
-    </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A42" s="72"/>
-      <c r="B42" s="72"/>
-      <c r="C42" s="72"/>
-      <c r="D42" s="31"/>
-      <c r="E42" s="73" t="str">
-        <f>IF($D42="","",IFERROR($D42-LOOKUP(2,1/($B$6:$B41=$B42),$D$6:$D41),""))</f>
-        <v/>
-      </c>
-      <c r="F42" s="74" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="G42" s="72"/>
-    </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A43" s="72"/>
-      <c r="B43" s="72"/>
-      <c r="C43" s="72"/>
-      <c r="D43" s="31"/>
-      <c r="E43" s="73" t="str">
-        <f>IF($D43="","",IFERROR($D43-LOOKUP(2,1/($B$6:$B42=$B43),$D$6:$D42),""))</f>
-        <v/>
-      </c>
-      <c r="F43" s="74" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="G43" s="72"/>
-    </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A44" s="72"/>
-      <c r="B44" s="72"/>
-      <c r="C44" s="72"/>
-      <c r="D44" s="31"/>
-      <c r="E44" s="73" t="str">
-        <f>IF($D44="","",IFERROR($D44-LOOKUP(2,1/($B$6:$B43=$B44),$D$6:$D43),""))</f>
-        <v/>
-      </c>
-      <c r="F44" s="74" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="G44" s="72"/>
-    </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A45" s="72"/>
-      <c r="B45" s="72"/>
-      <c r="C45" s="72"/>
-      <c r="D45" s="31"/>
-      <c r="E45" s="73" t="str">
-        <f>IF($D45="","",IFERROR($D45-LOOKUP(2,1/($B$6:$B44=$B45),$D$6:$D44),""))</f>
-        <v/>
-      </c>
-      <c r="F45" s="74" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="G45" s="72"/>
-    </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A46" s="72"/>
-      <c r="B46" s="72"/>
-      <c r="C46" s="72"/>
-      <c r="D46" s="31"/>
-      <c r="E46" s="73" t="str">
-        <f>IF($D46="","",IFERROR($D46-LOOKUP(2,1/($B$6:$B45=$B46),$D$6:$D45),""))</f>
-        <v/>
-      </c>
-      <c r="F46" s="74" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="G46" s="72"/>
-    </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A47" s="72"/>
-      <c r="B47" s="72"/>
-      <c r="C47" s="72"/>
-      <c r="D47" s="31"/>
-      <c r="E47" s="73" t="str">
-        <f>IF($D47="","",IFERROR($D47-LOOKUP(2,1/($B$6:$B46=$B47),$D$6:$D46),""))</f>
-        <v/>
-      </c>
-      <c r="F47" s="74" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="G47" s="72"/>
-    </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A48" s="72"/>
-      <c r="B48" s="72"/>
-      <c r="C48" s="72"/>
-      <c r="D48" s="31"/>
-      <c r="E48" s="73" t="str">
-        <f>IF($D48="","",IFERROR($D48-LOOKUP(2,1/($B$6:$B47=$B48),$D$6:$D47),""))</f>
-        <v/>
-      </c>
-      <c r="F48" s="74" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="G48" s="72"/>
-    </row>
-    <row r="49" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A49" s="72"/>
-      <c r="B49" s="72"/>
-      <c r="C49" s="72"/>
-      <c r="D49" s="31"/>
-      <c r="E49" s="73" t="str">
-        <f>IF($D49="","",IFERROR($D49-LOOKUP(2,1/($B$6:$B48=$B49),$D$6:$D48),""))</f>
-        <v/>
-      </c>
-      <c r="F49" s="74" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="G49" s="72"/>
-    </row>
-    <row r="50" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A50" s="72"/>
-      <c r="B50" s="72"/>
-      <c r="C50" s="72"/>
-      <c r="D50" s="31"/>
-      <c r="E50" s="73" t="str">
-        <f>IF($D50="","",IFERROR($D50-LOOKUP(2,1/($B$6:$B49=$B50),$D$6:$D49),""))</f>
-        <v/>
-      </c>
-      <c r="F50" s="74" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="G50" s="72"/>
-    </row>
-    <row r="51" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A51" s="72"/>
-      <c r="B51" s="72"/>
-      <c r="C51" s="72"/>
-      <c r="D51" s="31"/>
-      <c r="E51" s="73" t="str">
-        <f>IF($D51="","",IFERROR($D51-LOOKUP(2,1/($B$6:$B50=$B51),$D$6:$D50),""))</f>
-        <v/>
-      </c>
-      <c r="F51" s="74" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="G51" s="72"/>
-    </row>
-    <row r="52" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A52" s="72"/>
-      <c r="B52" s="72"/>
-      <c r="C52" s="72"/>
-      <c r="D52" s="31"/>
-      <c r="E52" s="73" t="str">
-        <f>IF($D52="","",IFERROR($D52-LOOKUP(2,1/($B$6:$B51=$B52),$D$6:$D51),""))</f>
-        <v/>
-      </c>
-      <c r="F52" s="74" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="G52" s="72"/>
-    </row>
-    <row r="53" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A53" s="72"/>
-      <c r="B53" s="72"/>
-      <c r="C53" s="72"/>
-      <c r="D53" s="31"/>
-      <c r="E53" s="73" t="str">
-        <f>IF($D53="","",IFERROR($D53-LOOKUP(2,1/($B$6:$B52=$B53),$D$6:$D52),""))</f>
-        <v/>
-      </c>
-      <c r="F53" s="74" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="G53" s="72"/>
-    </row>
-    <row r="54" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A54" s="72"/>
-      <c r="B54" s="72"/>
-      <c r="C54" s="72"/>
-      <c r="D54" s="31"/>
-      <c r="E54" s="73" t="str">
-        <f>IF($D54="","",IFERROR($D54-LOOKUP(2,1/($B$6:$B53=$B54),$D$6:$D53),""))</f>
-        <v/>
-      </c>
-      <c r="F54" s="74" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="G54" s="72"/>
-    </row>
-    <row r="55" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A55" s="72"/>
-      <c r="B55" s="72"/>
-      <c r="C55" s="72"/>
-      <c r="D55" s="31"/>
-      <c r="E55" s="73" t="str">
-        <f>IF($D55="","",IFERROR($D55-LOOKUP(2,1/($B$6:$B54=$B55),$D$6:$D54),""))</f>
-        <v/>
-      </c>
-      <c r="F55" s="74" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="G55" s="72"/>
-    </row>
-    <row r="56" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A56" s="72"/>
-      <c r="B56" s="72"/>
-      <c r="C56" s="72"/>
-      <c r="D56" s="31"/>
-      <c r="E56" s="73" t="str">
-        <f>IF($D56="","",IFERROR($D56-LOOKUP(2,1/($B$6:$B55=$B56),$D$6:$D55),""))</f>
-        <v/>
-      </c>
-      <c r="F56" s="74" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="G56" s="72"/>
-    </row>
-    <row r="57" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A57" s="72"/>
-      <c r="B57" s="72"/>
-      <c r="C57" s="72"/>
-      <c r="D57" s="31"/>
-      <c r="E57" s="73" t="str">
-        <f>IF($D57="","",IFERROR($D57-LOOKUP(2,1/($B$6:$B56=$B57),$D$6:$D56),""))</f>
-        <v/>
-      </c>
-      <c r="F57" s="74" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="G57" s="72"/>
-    </row>
-    <row r="58" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A58" s="72"/>
-      <c r="B58" s="72"/>
-      <c r="C58" s="72"/>
-      <c r="D58" s="31"/>
-      <c r="E58" s="73" t="str">
-        <f>IF($D58="","",IFERROR($D58-LOOKUP(2,1/($B$6:$B57=$B58),$D$6:$D57),""))</f>
-        <v/>
-      </c>
-      <c r="F58" s="74" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="G58" s="72"/>
-    </row>
-    <row r="59" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A59" s="72"/>
-      <c r="B59" s="72"/>
-      <c r="C59" s="72"/>
-      <c r="D59" s="31"/>
-      <c r="E59" s="73" t="str">
-        <f>IF($D59="","",IFERROR($D59-LOOKUP(2,1/($B$6:$B58=$B59),$D$6:$D58),""))</f>
-        <v/>
-      </c>
-      <c r="F59" s="74" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="G59" s="72"/>
-    </row>
-    <row r="60" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A60" s="72"/>
-      <c r="B60" s="72"/>
-      <c r="C60" s="72"/>
-      <c r="D60" s="31"/>
-      <c r="E60" s="73" t="str">
-        <f>IF($D60="","",IFERROR($D60-LOOKUP(2,1/($B$6:$B59=$B60),$D$6:$D59),""))</f>
-        <v/>
-      </c>
-      <c r="F60" s="74" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="G60" s="72"/>
-    </row>
-    <row r="61" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A61" s="72"/>
-      <c r="B61" s="72"/>
-      <c r="C61" s="72"/>
-      <c r="D61" s="31"/>
-      <c r="E61" s="73" t="str">
-        <f>IF($D61="","",IFERROR($D61-LOOKUP(2,1/($B$6:$B60=$B61),$D$6:$D60),""))</f>
-        <v/>
-      </c>
-      <c r="F61" s="74" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="G61" s="72"/>
-    </row>
-    <row r="62" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A62" s="72"/>
-      <c r="B62" s="72"/>
-      <c r="C62" s="72"/>
-      <c r="D62" s="31"/>
-      <c r="E62" s="73" t="str">
-        <f>IF($D62="","",IFERROR($D62-LOOKUP(2,1/($B$6:$B61=$B62),$D$6:$D61),""))</f>
-        <v/>
-      </c>
-      <c r="F62" s="74" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="G62" s="72"/>
-    </row>
-    <row r="63" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A63" s="72"/>
-      <c r="B63" s="72"/>
-      <c r="C63" s="72"/>
-      <c r="D63" s="31"/>
-      <c r="E63" s="73" t="str">
-        <f>IF($D63="","",IFERROR($D63-LOOKUP(2,1/($B$6:$B62=$B63),$D$6:$D62),""))</f>
-        <v/>
-      </c>
-      <c r="F63" s="74" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="G63" s="72"/>
-    </row>
-    <row r="64" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A64" s="72"/>
-      <c r="B64" s="72"/>
-      <c r="C64" s="72"/>
-      <c r="D64" s="31"/>
-      <c r="E64" s="73" t="str">
-        <f>IF($D64="","",IFERROR($D64-LOOKUP(2,1/($B$6:$B63=$B64),$D$6:$D63),""))</f>
-        <v/>
-      </c>
-      <c r="F64" s="74" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="G64" s="72"/>
-    </row>
-    <row r="65" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A65" s="72"/>
-      <c r="B65" s="72"/>
-      <c r="C65" s="72"/>
-      <c r="D65" s="31"/>
-      <c r="E65" s="73" t="str">
-        <f>IF($D65="","",IFERROR($D65-LOOKUP(2,1/($B$6:$B64=$B65),$D$6:$D64),""))</f>
-        <v/>
-      </c>
-      <c r="F65" s="74" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="G65" s="72"/>
-    </row>
-    <row r="66" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A66" s="72"/>
-      <c r="B66" s="72"/>
-      <c r="C66" s="72"/>
-      <c r="D66" s="31"/>
-      <c r="E66" s="73" t="str">
-        <f>IF($D66="","",IFERROR($D66-LOOKUP(2,1/($B$6:$B65=$B66),$D$6:$D65),""))</f>
-        <v/>
-      </c>
-      <c r="F66" s="74" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="G66" s="72"/>
-    </row>
-    <row r="67" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A67" s="72"/>
-      <c r="B67" s="72"/>
-      <c r="C67" s="72"/>
-      <c r="D67" s="31"/>
-      <c r="E67" s="73" t="str">
-        <f>IF($D67="","",IFERROR($D67-LOOKUP(2,1/($B$6:$B66=$B67),$D$6:$D66),""))</f>
-        <v/>
-      </c>
-      <c r="F67" s="74" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="G67" s="72"/>
-    </row>
-    <row r="68" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A68" s="72"/>
-      <c r="B68" s="72"/>
-      <c r="C68" s="72"/>
-      <c r="D68" s="31"/>
-      <c r="E68" s="73" t="str">
-        <f>IF($D68="","",IFERROR($D68-LOOKUP(2,1/($B$6:$B67=$B68),$D$6:$D67),""))</f>
-        <v/>
-      </c>
-      <c r="F68" s="74" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="G68" s="72"/>
-    </row>
-    <row r="69" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A69" s="72"/>
-      <c r="B69" s="72"/>
-      <c r="C69" s="72"/>
-      <c r="D69" s="31"/>
-      <c r="E69" s="73" t="str">
-        <f>IF($D69="","",IFERROR($D69-LOOKUP(2,1/($B$6:$B68=$B69),$D$6:$D68),""))</f>
-        <v/>
-      </c>
-      <c r="F69" s="74" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="G69" s="72"/>
-    </row>
-    <row r="70" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A70" s="72"/>
-      <c r="B70" s="72"/>
-      <c r="C70" s="72"/>
-      <c r="D70" s="31"/>
-      <c r="E70" s="73" t="str">
-        <f>IF($D70="","",IFERROR($D70-LOOKUP(2,1/($B$6:$B69=$B70),$D$6:$D69),""))</f>
-        <v/>
-      </c>
-      <c r="F70" s="74" t="str">
-        <f t="shared" ref="F70:F101" si="2">IF($E70="","",IF($E70&gt;0.03,"▲ SURGE ENTERING — early YES signal",IF($E70&lt;-0.03,"▼ COOLING — NO side strengthens","flat")))</f>
-        <v/>
-      </c>
-      <c r="G70" s="72"/>
-    </row>
-    <row r="71" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A71" s="72"/>
-      <c r="B71" s="72"/>
-      <c r="C71" s="72"/>
-      <c r="D71" s="31"/>
-      <c r="E71" s="73" t="str">
-        <f>IF($D71="","",IFERROR($D71-LOOKUP(2,1/($B$6:$B70=$B71),$D$6:$D70),""))</f>
-        <v/>
-      </c>
-      <c r="F71" s="74" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="G71" s="72"/>
-    </row>
-    <row r="72" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A72" s="72"/>
-      <c r="B72" s="72"/>
-      <c r="C72" s="72"/>
-      <c r="D72" s="31"/>
-      <c r="E72" s="73" t="str">
-        <f>IF($D72="","",IFERROR($D72-LOOKUP(2,1/($B$6:$B71=$B72),$D$6:$D71),""))</f>
-        <v/>
-      </c>
-      <c r="F72" s="74" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="G72" s="72"/>
-    </row>
-    <row r="73" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A73" s="72"/>
-      <c r="B73" s="72"/>
-      <c r="C73" s="72"/>
-      <c r="D73" s="31"/>
-      <c r="E73" s="73" t="str">
-        <f>IF($D73="","",IFERROR($D73-LOOKUP(2,1/($B$6:$B72=$B73),$D$6:$D72),""))</f>
-        <v/>
-      </c>
-      <c r="F73" s="74" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="G73" s="72"/>
-    </row>
-    <row r="74" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A74" s="72"/>
-      <c r="B74" s="72"/>
-      <c r="C74" s="72"/>
-      <c r="D74" s="31"/>
-      <c r="E74" s="73" t="str">
-        <f>IF($D74="","",IFERROR($D74-LOOKUP(2,1/($B$6:$B73=$B74),$D$6:$D73),""))</f>
-        <v/>
-      </c>
-      <c r="F74" s="74" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="G74" s="72"/>
-    </row>
-    <row r="75" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A75" s="72"/>
-      <c r="B75" s="72"/>
-      <c r="C75" s="72"/>
-      <c r="D75" s="31"/>
-      <c r="E75" s="73" t="str">
-        <f>IF($D75="","",IFERROR($D75-LOOKUP(2,1/($B$6:$B74=$B75),$D$6:$D74),""))</f>
-        <v/>
-      </c>
-      <c r="F75" s="74" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="G75" s="72"/>
-    </row>
-    <row r="76" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A76" s="72"/>
-      <c r="B76" s="72"/>
-      <c r="C76" s="72"/>
-      <c r="D76" s="31"/>
-      <c r="E76" s="73" t="str">
-        <f>IF($D76="","",IFERROR($D76-LOOKUP(2,1/($B$6:$B75=$B76),$D$6:$D75),""))</f>
-        <v/>
-      </c>
-      <c r="F76" s="74" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="G76" s="72"/>
-    </row>
-    <row r="77" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A77" s="72"/>
-      <c r="B77" s="72"/>
-      <c r="C77" s="72"/>
-      <c r="D77" s="31"/>
-      <c r="E77" s="73" t="str">
-        <f>IF($D77="","",IFERROR($D77-LOOKUP(2,1/($B$6:$B76=$B77),$D$6:$D76),""))</f>
-        <v/>
-      </c>
-      <c r="F77" s="74" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="G77" s="72"/>
-    </row>
-    <row r="78" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A78" s="72"/>
-      <c r="B78" s="72"/>
-      <c r="C78" s="72"/>
-      <c r="D78" s="31"/>
-      <c r="E78" s="73" t="str">
-        <f>IF($D78="","",IFERROR($D78-LOOKUP(2,1/($B$6:$B77=$B78),$D$6:$D77),""))</f>
-        <v/>
-      </c>
-      <c r="F78" s="74" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="G78" s="72"/>
-    </row>
-    <row r="79" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A79" s="72"/>
-      <c r="B79" s="72"/>
-      <c r="C79" s="72"/>
-      <c r="D79" s="31"/>
-      <c r="E79" s="73" t="str">
-        <f>IF($D79="","",IFERROR($D79-LOOKUP(2,1/($B$6:$B78=$B79),$D$6:$D78),""))</f>
-        <v/>
-      </c>
-      <c r="F79" s="74" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="G79" s="72"/>
-    </row>
-    <row r="80" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A80" s="72"/>
-      <c r="B80" s="72"/>
-      <c r="C80" s="72"/>
-      <c r="D80" s="31"/>
-      <c r="E80" s="73" t="str">
-        <f>IF($D80="","",IFERROR($D80-LOOKUP(2,1/($B$6:$B79=$B80),$D$6:$D79),""))</f>
-        <v/>
-      </c>
-      <c r="F80" s="74" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="G80" s="72"/>
-    </row>
-    <row r="81" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A81" s="72"/>
-      <c r="B81" s="72"/>
-      <c r="C81" s="72"/>
-      <c r="D81" s="31"/>
-      <c r="E81" s="73" t="str">
-        <f>IF($D81="","",IFERROR($D81-LOOKUP(2,1/($B$6:$B80=$B81),$D$6:$D80),""))</f>
-        <v/>
-      </c>
-      <c r="F81" s="74" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="G81" s="72"/>
-    </row>
-    <row r="82" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A82" s="72"/>
-      <c r="B82" s="72"/>
-      <c r="C82" s="72"/>
-      <c r="D82" s="31"/>
-      <c r="E82" s="73" t="str">
-        <f>IF($D82="","",IFERROR($D82-LOOKUP(2,1/($B$6:$B81=$B82),$D$6:$D81),""))</f>
-        <v/>
-      </c>
-      <c r="F82" s="74" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="G82" s="72"/>
-    </row>
-    <row r="83" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A83" s="72"/>
-      <c r="B83" s="72"/>
-      <c r="C83" s="72"/>
-      <c r="D83" s="31"/>
-      <c r="E83" s="73" t="str">
-        <f>IF($D83="","",IFERROR($D83-LOOKUP(2,1/($B$6:$B82=$B83),$D$6:$D82),""))</f>
-        <v/>
-      </c>
-      <c r="F83" s="74" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="G83" s="72"/>
-    </row>
-    <row r="84" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A84" s="72"/>
-      <c r="B84" s="72"/>
-      <c r="C84" s="72"/>
-      <c r="D84" s="31"/>
-      <c r="E84" s="73" t="str">
-        <f>IF($D84="","",IFERROR($D84-LOOKUP(2,1/($B$6:$B83=$B84),$D$6:$D83),""))</f>
-        <v/>
-      </c>
-      <c r="F84" s="74" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="G84" s="72"/>
-    </row>
-    <row r="85" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A85" s="72"/>
-      <c r="B85" s="72"/>
-      <c r="C85" s="72"/>
-      <c r="D85" s="31"/>
-      <c r="E85" s="73" t="str">
-        <f>IF($D85="","",IFERROR($D85-LOOKUP(2,1/($B$6:$B84=$B85),$D$6:$D84),""))</f>
-        <v/>
-      </c>
-      <c r="F85" s="74" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="G85" s="72"/>
-    </row>
-    <row r="86" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A86" s="72"/>
-      <c r="B86" s="72"/>
-      <c r="C86" s="72"/>
-      <c r="D86" s="31"/>
-      <c r="E86" s="73" t="str">
-        <f>IF($D86="","",IFERROR($D86-LOOKUP(2,1/($B$6:$B85=$B86),$D$6:$D85),""))</f>
-        <v/>
-      </c>
-      <c r="F86" s="74" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="G86" s="72"/>
-    </row>
-    <row r="87" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A87" s="72"/>
-      <c r="B87" s="72"/>
-      <c r="C87" s="72"/>
-      <c r="D87" s="31"/>
-      <c r="E87" s="73" t="str">
-        <f>IF($D87="","",IFERROR($D87-LOOKUP(2,1/($B$6:$B86=$B87),$D$6:$D86),""))</f>
-        <v/>
-      </c>
-      <c r="F87" s="74" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="G87" s="72"/>
-    </row>
-    <row r="88" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A88" s="72"/>
-      <c r="B88" s="72"/>
-      <c r="C88" s="72"/>
-      <c r="D88" s="31"/>
-      <c r="E88" s="73" t="str">
-        <f>IF($D88="","",IFERROR($D88-LOOKUP(2,1/($B$6:$B87=$B88),$D$6:$D87),""))</f>
-        <v/>
-      </c>
-      <c r="F88" s="74" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="G88" s="72"/>
-    </row>
-    <row r="89" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A89" s="72"/>
-      <c r="B89" s="72"/>
-      <c r="C89" s="72"/>
-      <c r="D89" s="31"/>
-      <c r="E89" s="73" t="str">
-        <f>IF($D89="","",IFERROR($D89-LOOKUP(2,1/($B$6:$B88=$B89),$D$6:$D88),""))</f>
-        <v/>
-      </c>
-      <c r="F89" s="74" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="G89" s="72"/>
-    </row>
-    <row r="90" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A90" s="72"/>
-      <c r="B90" s="72"/>
-      <c r="C90" s="72"/>
-      <c r="D90" s="31"/>
-      <c r="E90" s="73" t="str">
-        <f>IF($D90="","",IFERROR($D90-LOOKUP(2,1/($B$6:$B89=$B90),$D$6:$D89),""))</f>
-        <v/>
-      </c>
-      <c r="F90" s="74" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="G90" s="72"/>
-    </row>
-    <row r="91" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A91" s="72"/>
-      <c r="B91" s="72"/>
-      <c r="C91" s="72"/>
-      <c r="D91" s="31"/>
-      <c r="E91" s="73" t="str">
-        <f>IF($D91="","",IFERROR($D91-LOOKUP(2,1/($B$6:$B90=$B91),$D$6:$D90),""))</f>
-        <v/>
-      </c>
-      <c r="F91" s="74" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="G91" s="72"/>
-    </row>
-    <row r="92" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A92" s="72"/>
-      <c r="B92" s="72"/>
-      <c r="C92" s="72"/>
-      <c r="D92" s="31"/>
-      <c r="E92" s="73" t="str">
-        <f>IF($D92="","",IFERROR($D92-LOOKUP(2,1/($B$6:$B91=$B92),$D$6:$D91),""))</f>
-        <v/>
-      </c>
-      <c r="F92" s="74" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="G92" s="72"/>
-    </row>
-    <row r="93" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A93" s="72"/>
-      <c r="B93" s="72"/>
-      <c r="C93" s="72"/>
-      <c r="D93" s="31"/>
-      <c r="E93" s="73" t="str">
-        <f>IF($D93="","",IFERROR($D93-LOOKUP(2,1/($B$6:$B92=$B93),$D$6:$D92),""))</f>
-        <v/>
-      </c>
-      <c r="F93" s="74" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="G93" s="72"/>
-    </row>
-    <row r="94" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A94" s="72"/>
-      <c r="B94" s="72"/>
-      <c r="C94" s="72"/>
-      <c r="D94" s="31"/>
-      <c r="E94" s="73" t="str">
-        <f>IF($D94="","",IFERROR($D94-LOOKUP(2,1/($B$6:$B93=$B94),$D$6:$D93),""))</f>
-        <v/>
-      </c>
-      <c r="F94" s="74" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="G94" s="72"/>
-    </row>
-    <row r="95" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A95" s="72"/>
-      <c r="B95" s="72"/>
-      <c r="C95" s="72"/>
-      <c r="D95" s="31"/>
-      <c r="E95" s="73" t="str">
-        <f>IF($D95="","",IFERROR($D95-LOOKUP(2,1/($B$6:$B94=$B95),$D$6:$D94),""))</f>
-        <v/>
-      </c>
-      <c r="F95" s="74" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="G95" s="72"/>
-    </row>
-    <row r="96" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A96" s="72"/>
-      <c r="B96" s="72"/>
-      <c r="C96" s="72"/>
-      <c r="D96" s="31"/>
-      <c r="E96" s="73" t="str">
-        <f>IF($D96="","",IFERROR($D96-LOOKUP(2,1/($B$6:$B95=$B96),$D$6:$D95),""))</f>
-        <v/>
-      </c>
-      <c r="F96" s="74" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="G96" s="72"/>
-    </row>
-    <row r="97" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A97" s="72"/>
-      <c r="B97" s="72"/>
-      <c r="C97" s="72"/>
-      <c r="D97" s="31"/>
-      <c r="E97" s="73" t="str">
-        <f>IF($D97="","",IFERROR($D97-LOOKUP(2,1/($B$6:$B96=$B97),$D$6:$D96),""))</f>
-        <v/>
-      </c>
-      <c r="F97" s="74" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="G97" s="72"/>
-    </row>
-    <row r="98" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A98" s="72"/>
-      <c r="B98" s="72"/>
-      <c r="C98" s="72"/>
-      <c r="D98" s="31"/>
-      <c r="E98" s="73" t="str">
-        <f>IF($D98="","",IFERROR($D98-LOOKUP(2,1/($B$6:$B97=$B98),$D$6:$D97),""))</f>
-        <v/>
-      </c>
-      <c r="F98" s="74" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="G98" s="72"/>
-    </row>
-    <row r="99" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A99" s="72"/>
-      <c r="B99" s="72"/>
-      <c r="C99" s="72"/>
-      <c r="D99" s="31"/>
-      <c r="E99" s="73" t="str">
-        <f>IF($D99="","",IFERROR($D99-LOOKUP(2,1/($B$6:$B98=$B99),$D$6:$D98),""))</f>
-        <v/>
-      </c>
-      <c r="F99" s="74" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="G99" s="72"/>
-    </row>
-    <row r="100" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A100" s="72"/>
-      <c r="B100" s="72"/>
-      <c r="C100" s="72"/>
-      <c r="D100" s="31"/>
-      <c r="E100" s="73" t="str">
-        <f>IF($D100="","",IFERROR($D100-LOOKUP(2,1/($B$6:$B99=$B100),$D$6:$D99),""))</f>
-        <v/>
-      </c>
-      <c r="F100" s="74" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="G100" s="72"/>
-    </row>
-    <row r="101" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A101" s="72"/>
-      <c r="B101" s="72"/>
-      <c r="C101" s="72"/>
-      <c r="D101" s="31"/>
-      <c r="E101" s="73" t="str">
-        <f>IF($D101="","",IFERROR($D101-LOOKUP(2,1/($B$6:$B100=$B101),$D$6:$D100),""))</f>
-        <v/>
-      </c>
-      <c r="F101" s="74" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="G101" s="72"/>
-    </row>
-    <row r="102" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A102" s="72"/>
-      <c r="B102" s="72"/>
-      <c r="C102" s="72"/>
-      <c r="D102" s="31"/>
-      <c r="E102" s="73" t="str">
-        <f>IF($D102="","",IFERROR($D102-LOOKUP(2,1/($B$6:$B101=$B102),$D$6:$D101),""))</f>
-        <v/>
-      </c>
-      <c r="F102" s="74" t="str">
-        <f t="shared" ref="F102:F125" si="3">IF($E102="","",IF($E102&gt;0.03,"▲ SURGE ENTERING — early YES signal",IF($E102&lt;-0.03,"▼ COOLING — NO side strengthens","flat")))</f>
-        <v/>
-      </c>
-      <c r="G102" s="72"/>
-    </row>
-    <row r="103" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A103" s="72"/>
-      <c r="B103" s="72"/>
-      <c r="C103" s="72"/>
-      <c r="D103" s="31"/>
-      <c r="E103" s="73" t="str">
-        <f>IF($D103="","",IFERROR($D103-LOOKUP(2,1/($B$6:$B102=$B103),$D$6:$D102),""))</f>
-        <v/>
-      </c>
-      <c r="F103" s="74" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="G103" s="72"/>
-    </row>
-    <row r="104" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A104" s="72"/>
-      <c r="B104" s="72"/>
-      <c r="C104" s="72"/>
-      <c r="D104" s="31"/>
-      <c r="E104" s="73" t="str">
-        <f>IF($D104="","",IFERROR($D104-LOOKUP(2,1/($B$6:$B103=$B104),$D$6:$D103),""))</f>
-        <v/>
-      </c>
-      <c r="F104" s="74" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="G104" s="72"/>
-    </row>
-    <row r="105" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A105" s="72"/>
-      <c r="B105" s="72"/>
-      <c r="C105" s="72"/>
-      <c r="D105" s="31"/>
-      <c r="E105" s="73" t="str">
-        <f>IF($D105="","",IFERROR($D105-LOOKUP(2,1/($B$6:$B104=$B105),$D$6:$D104),""))</f>
-        <v/>
-      </c>
-      <c r="F105" s="74" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="G105" s="72"/>
-    </row>
-    <row r="106" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A106" s="72"/>
-      <c r="B106" s="72"/>
-      <c r="C106" s="72"/>
-      <c r="D106" s="31"/>
-      <c r="E106" s="73" t="str">
-        <f>IF($D106="","",IFERROR($D106-LOOKUP(2,1/($B$6:$B105=$B106),$D$6:$D105),""))</f>
-        <v/>
-      </c>
-      <c r="F106" s="74" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="G106" s="72"/>
-    </row>
-    <row r="107" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A107" s="72"/>
-      <c r="B107" s="72"/>
-      <c r="C107" s="72"/>
-      <c r="D107" s="31"/>
-      <c r="E107" s="73" t="str">
-        <f>IF($D107="","",IFERROR($D107-LOOKUP(2,1/($B$6:$B106=$B107),$D$6:$D106),""))</f>
-        <v/>
-      </c>
-      <c r="F107" s="74" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="G107" s="72"/>
-    </row>
-    <row r="108" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A108" s="72"/>
-      <c r="B108" s="72"/>
-      <c r="C108" s="72"/>
-      <c r="D108" s="31"/>
-      <c r="E108" s="73" t="str">
-        <f>IF($D108="","",IFERROR($D108-LOOKUP(2,1/($B$6:$B107=$B108),$D$6:$D107),""))</f>
-        <v/>
-      </c>
-      <c r="F108" s="74" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="G108" s="72"/>
-    </row>
-    <row r="109" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A109" s="72"/>
-      <c r="B109" s="72"/>
-      <c r="C109" s="72"/>
-      <c r="D109" s="31"/>
-      <c r="E109" s="73" t="str">
-        <f>IF($D109="","",IFERROR($D109-LOOKUP(2,1/($B$6:$B108=$B109),$D$6:$D108),""))</f>
-        <v/>
-      </c>
-      <c r="F109" s="74" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="G109" s="72"/>
-    </row>
-    <row r="110" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A110" s="72"/>
-      <c r="B110" s="72"/>
-      <c r="C110" s="72"/>
-      <c r="D110" s="31"/>
-      <c r="E110" s="73" t="str">
-        <f>IF($D110="","",IFERROR($D110-LOOKUP(2,1/($B$6:$B109=$B110),$D$6:$D109),""))</f>
-        <v/>
-      </c>
-      <c r="F110" s="74" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="G110" s="72"/>
-    </row>
-    <row r="111" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A111" s="72"/>
-      <c r="B111" s="72"/>
-      <c r="C111" s="72"/>
-      <c r="D111" s="31"/>
-      <c r="E111" s="73" t="str">
-        <f>IF($D111="","",IFERROR($D111-LOOKUP(2,1/($B$6:$B110=$B111),$D$6:$D110),""))</f>
-        <v/>
-      </c>
-      <c r="F111" s="74" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="G111" s="72"/>
-    </row>
-    <row r="112" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A112" s="72"/>
-      <c r="B112" s="72"/>
-      <c r="C112" s="72"/>
-      <c r="D112" s="31"/>
-      <c r="E112" s="73" t="str">
-        <f>IF($D112="","",IFERROR($D112-LOOKUP(2,1/($B$6:$B111=$B112),$D$6:$D111),""))</f>
-        <v/>
-      </c>
-      <c r="F112" s="74" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="G112" s="72"/>
-    </row>
-    <row r="113" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A113" s="72"/>
-      <c r="B113" s="72"/>
-      <c r="C113" s="72"/>
-      <c r="D113" s="31"/>
-      <c r="E113" s="73" t="str">
-        <f>IF($D113="","",IFERROR($D113-LOOKUP(2,1/($B$6:$B112=$B113),$D$6:$D112),""))</f>
-        <v/>
-      </c>
-      <c r="F113" s="74" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="G113" s="72"/>
-    </row>
-    <row r="114" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A114" s="72"/>
-      <c r="B114" s="72"/>
-      <c r="C114" s="72"/>
-      <c r="D114" s="31"/>
-      <c r="E114" s="73" t="str">
-        <f>IF($D114="","",IFERROR($D114-LOOKUP(2,1/($B$6:$B113=$B114),$D$6:$D113),""))</f>
-        <v/>
-      </c>
-      <c r="F114" s="74" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="G114" s="72"/>
-    </row>
-    <row r="115" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A115" s="72"/>
-      <c r="B115" s="72"/>
-      <c r="C115" s="72"/>
-      <c r="D115" s="31"/>
-      <c r="E115" s="73" t="str">
-        <f>IF($D115="","",IFERROR($D115-LOOKUP(2,1/($B$6:$B114=$B115),$D$6:$D114),""))</f>
-        <v/>
-      </c>
-      <c r="F115" s="74" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="G115" s="72"/>
-    </row>
-    <row r="116" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A116" s="72"/>
-      <c r="B116" s="72"/>
-      <c r="C116" s="72"/>
-      <c r="D116" s="31"/>
-      <c r="E116" s="73" t="str">
-        <f>IF($D116="","",IFERROR($D116-LOOKUP(2,1/($B$6:$B115=$B116),$D$6:$D115),""))</f>
-        <v/>
-      </c>
-      <c r="F116" s="74" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="G116" s="72"/>
-    </row>
-    <row r="117" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A117" s="72"/>
-      <c r="B117" s="72"/>
-      <c r="C117" s="72"/>
-      <c r="D117" s="31"/>
-      <c r="E117" s="73" t="str">
-        <f>IF($D117="","",IFERROR($D117-LOOKUP(2,1/($B$6:$B116=$B117),$D$6:$D116),""))</f>
-        <v/>
-      </c>
-      <c r="F117" s="74" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="G117" s="72"/>
-    </row>
-    <row r="118" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A118" s="72"/>
-      <c r="B118" s="72"/>
-      <c r="C118" s="72"/>
-      <c r="D118" s="31"/>
-      <c r="E118" s="73" t="str">
-        <f>IF($D118="","",IFERROR($D118-LOOKUP(2,1/($B$6:$B117=$B118),$D$6:$D117),""))</f>
-        <v/>
-      </c>
-      <c r="F118" s="74" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="G118" s="72"/>
-    </row>
-    <row r="119" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A119" s="72"/>
-      <c r="B119" s="72"/>
-      <c r="C119" s="72"/>
-      <c r="D119" s="31"/>
-      <c r="E119" s="73" t="str">
-        <f>IF($D119="","",IFERROR($D119-LOOKUP(2,1/($B$6:$B118=$B119),$D$6:$D118),""))</f>
-        <v/>
-      </c>
-      <c r="F119" s="74" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="G119" s="72"/>
-    </row>
-    <row r="120" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A120" s="72"/>
-      <c r="B120" s="72"/>
-      <c r="C120" s="72"/>
-      <c r="D120" s="31"/>
-      <c r="E120" s="73" t="str">
-        <f>IF($D120="","",IFERROR($D120-LOOKUP(2,1/($B$6:$B119=$B120),$D$6:$D119),""))</f>
-        <v/>
-      </c>
-      <c r="F120" s="74" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="G120" s="72"/>
-    </row>
-    <row r="121" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A121" s="72"/>
-      <c r="B121" s="72"/>
-      <c r="C121" s="72"/>
-      <c r="D121" s="31"/>
-      <c r="E121" s="73" t="str">
-        <f>IF($D121="","",IFERROR($D121-LOOKUP(2,1/($B$6:$B120=$B121),$D$6:$D120),""))</f>
-        <v/>
-      </c>
-      <c r="F121" s="74" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="G121" s="72"/>
-    </row>
-    <row r="122" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A122" s="72"/>
-      <c r="B122" s="72"/>
-      <c r="C122" s="72"/>
-      <c r="D122" s="31"/>
-      <c r="E122" s="73" t="str">
-        <f>IF($D122="","",IFERROR($D122-LOOKUP(2,1/($B$6:$B121=$B122),$D$6:$D121),""))</f>
-        <v/>
-      </c>
-      <c r="F122" s="74" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="G122" s="72"/>
-    </row>
-    <row r="123" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A123" s="72"/>
-      <c r="B123" s="72"/>
-      <c r="C123" s="72"/>
-      <c r="D123" s="31"/>
-      <c r="E123" s="73" t="str">
-        <f>IF($D123="","",IFERROR($D123-LOOKUP(2,1/($B$6:$B122=$B123),$D$6:$D122),""))</f>
-        <v/>
-      </c>
-      <c r="F123" s="74" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="G123" s="72"/>
-    </row>
-    <row r="124" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A124" s="72"/>
-      <c r="B124" s="72"/>
-      <c r="C124" s="72"/>
-      <c r="D124" s="31"/>
-      <c r="E124" s="73" t="str">
-        <f>IF($D124="","",IFERROR($D124-LOOKUP(2,1/($B$6:$B123=$B124),$D$6:$D123),""))</f>
-        <v/>
-      </c>
-      <c r="F124" s="74" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="G124" s="72"/>
-    </row>
-    <row r="125" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A125" s="72"/>
-      <c r="B125" s="72"/>
-      <c r="C125" s="72"/>
-      <c r="D125" s="31"/>
-      <c r="E125" s="73" t="str">
-        <f>IF($D125="","",IFERROR($D125-LOOKUP(2,1/($B$6:$B124=$B125),$D$6:$D124),""))</f>
-        <v/>
-      </c>
-      <c r="F125" s="74" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="G125" s="72"/>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:G1"/>
-  </mergeCells>
-  <conditionalFormatting sqref="F6:F125">
-    <cfRule type="expression" dxfId="1" priority="1">
-      <formula>ISNUMBER(SEARCH("SURGE",F6))</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="0" priority="2">
-      <formula>ISNUMBER(SEARCH("COOLING",F6))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
 </file>